--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -14,11 +14,11 @@
     <sheet name="Misc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AS$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AN$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AO$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1673,19 +1673,19 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.050031252</v>
+        <v>1.050006898</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.01</v>
+        <v>1.009</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>33.4</v>
+        <v>30.1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>12</v>
@@ -1704,7 +1704,8 @@
           <t>For v2:
 More hopstand and late hops
 Whc lax yeast
-Larger portion pilsener malt</t>
+Larger portion pilsener malt
+Used American Pale Ale water profile</t>
         </is>
       </c>
     </row>
@@ -1768,8 +1769,72 @@
       </c>
       <c r="P20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>American IPA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>All Grain</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Jonas</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2019-03-08</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1.065578044</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Easy drink beer with tropical notes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P20"/>
+  <autoFilter ref="A1:P21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1780,7 +1845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS74"/>
+  <dimension ref="A1:AT76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1828,6 +1893,7 @@
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="10" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2054,6 +2120,11 @@
       <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>notInRecipe</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>addAfterBoil</t>
         </is>
       </c>
     </row>
@@ -2160,6 +2231,7 @@
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2272,6 +2344,7 @@
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2378,6 +2451,7 @@
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2484,6 +2558,7 @@
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2590,6 +2665,7 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2696,6 +2772,7 @@
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2829,6 +2906,7 @@
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2907,6 +2985,7 @@
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2985,6 +3064,7 @@
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3085,6 +3165,7 @@
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3163,6 +3244,7 @@
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3264,6 +3346,7 @@
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3391,6 +3474,7 @@
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3489,6 +3573,7 @@
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3598,6 +3683,7 @@
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3706,6 +3792,7 @@
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3812,6 +3899,7 @@
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3922,6 +4010,7 @@
       </c>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4023,6 +4112,7 @@
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4097,6 +4187,7 @@
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4198,6 +4289,7 @@
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4325,6 +4417,7 @@
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr"/>
       <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4403,6 +4496,7 @@
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4481,6 +4575,7 @@
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
       <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4608,6 +4703,7 @@
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="inlineStr"/>
       <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4741,6 +4837,7 @@
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr"/>
       <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4849,6 +4946,7 @@
       </c>
       <c r="AR28" t="inlineStr"/>
       <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4955,6 +5053,7 @@
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5033,6 +5132,7 @@
       <c r="AQ30" t="inlineStr"/>
       <c r="AR30" t="inlineStr"/>
       <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5139,6 +5239,7 @@
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5217,6 +5318,7 @@
       <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="inlineStr"/>
       <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5318,6 +5420,7 @@
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr"/>
       <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5439,6 +5542,7 @@
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="inlineStr"/>
       <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5540,6 +5644,7 @@
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5646,6 +5751,7 @@
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5774,6 +5880,7 @@
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr"/>
       <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5877,6 +5984,7 @@
       </c>
       <c r="AR38" t="inlineStr"/>
       <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5982,6 +6090,7 @@
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="inlineStr"/>
       <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6111,6 +6220,7 @@
       </c>
       <c r="AR40" t="inlineStr"/>
       <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6240,6 +6350,7 @@
         <v>1</v>
       </c>
       <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6344,6 +6455,7 @@
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="inlineStr"/>
       <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6456,6 +6568,7 @@
       <c r="AQ43" t="inlineStr"/>
       <c r="AR43" t="inlineStr"/>
       <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6530,6 +6643,7 @@
       <c r="AQ44" t="inlineStr"/>
       <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6648,6 +6762,7 @@
       </c>
       <c r="AR45" t="inlineStr"/>
       <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6760,6 +6875,7 @@
       <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6868,6 +6984,7 @@
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="inlineStr"/>
       <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6969,6 +7086,7 @@
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="inlineStr"/>
       <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7096,6 +7214,7 @@
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="inlineStr"/>
       <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7208,6 +7327,7 @@
       <c r="AQ50" t="inlineStr"/>
       <c r="AR50" t="inlineStr"/>
       <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7314,6 +7434,7 @@
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7392,6 +7513,7 @@
       <c r="AQ52" t="inlineStr"/>
       <c r="AR52" t="inlineStr"/>
       <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7470,6 +7592,7 @@
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr"/>
       <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7570,6 +7693,7 @@
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="inlineStr"/>
       <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7685,6 +7809,7 @@
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr"/>
       <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7786,6 +7911,7 @@
       <c r="AS56" t="b">
         <v>0</v>
       </c>
+      <c r="AT56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7894,6 +8020,7 @@
       </c>
       <c r="AR57" t="inlineStr"/>
       <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8002,6 +8129,7 @@
       <c r="AQ58" t="inlineStr"/>
       <c r="AR58" t="inlineStr"/>
       <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8111,6 +8239,7 @@
       </c>
       <c r="AR59" t="inlineStr"/>
       <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8189,6 +8318,7 @@
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8267,6 +8397,7 @@
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8367,6 +8498,7 @@
       <c r="AQ62" t="inlineStr"/>
       <c r="AR62" t="inlineStr"/>
       <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8475,6 +8607,7 @@
       </c>
       <c r="AR63" t="inlineStr"/>
       <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8578,6 +8711,7 @@
         <v>0</v>
       </c>
       <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8679,6 +8813,7 @@
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8800,6 +8935,7 @@
       <c r="AQ66" t="inlineStr"/>
       <c r="AR66" t="inlineStr"/>
       <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8905,6 +9041,7 @@
       <c r="AQ67" t="inlineStr"/>
       <c r="AR67" t="inlineStr"/>
       <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8924,98 +9061,71 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>default-0aa30343c0c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7MQ6Noi2PwgQW8SivnCh6TS5Y4oFMA</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1777108187}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1777108187050</v>
+        <v>1781339591476</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="P68" t="n">
-        <v>1</v>
+        <v>2.45</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S68" t="n">
-        <v>76</v>
-      </c>
-      <c r="U68" t="n">
-        <v>81</v>
-      </c>
-      <c r="V68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X68" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Swaen Pilsner</t>
+        </is>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH68" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ68" t="n">
         <v>80</v>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>Swaen Ale</t>
-        </is>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="AH68" t="n">
-        <v>61.16</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>1.037</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>80.13</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>11.5</v>
       </c>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr">
@@ -9033,6 +9143,7 @@
       <c r="AQ68" t="inlineStr"/>
       <c r="AR68" t="inlineStr"/>
       <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9052,52 +9163,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1777108192684</v>
+        <v>1781339591852</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X69" t="b">
         <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>7.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE69" t="b">
@@ -9110,13 +9221,13 @@
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>36.7</v>
+        <v>15.15</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.0368</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ69" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr">
@@ -9132,10 +9243,9 @@
       <c r="AO69" t="inlineStr"/>
       <c r="AP69" t="inlineStr"/>
       <c r="AQ69" t="inlineStr"/>
-      <c r="AR69" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR69" t="inlineStr"/>
       <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9155,75 +9265,91 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1776345994305</v>
+        <v>1781339591050</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S70" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>80</v>
+      </c>
+      <c r="V70" t="n">
+        <v>80</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X70" t="b">
         <v>0</v>
       </c>
+      <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>2</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>2.14</v>
+        <v>9.09</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ70" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr">
@@ -9241,16 +9367,17 @@
       <c r="AQ70" t="inlineStr"/>
       <c r="AR70" t="inlineStr"/>
       <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9258,52 +9385,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="n">
-        <v>0</v>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1781339589491</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="P71" t="n">
-        <v>1.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.8527919</v>
-      </c>
-      <c r="S71" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X71" t="b">
         <v>0</v>
       </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>4.5</v>
+      <c r="Z71" t="n">
+        <v>1.36</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® Extra Pale</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE71" t="b">
@@ -9311,30 +9440,27 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>68.18000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.038</v>
+        <v>1.034</v>
       </c>
       <c r="AJ71" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>10.1</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
@@ -9347,6 +9473,7 @@
       <c r="AQ71" t="inlineStr"/>
       <c r="AR71" t="inlineStr"/>
       <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9367,7 +9494,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -9378,21 +9505,21 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="P72" t="n">
         <v>1.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.9593909</v>
+        <v>1.8527919</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X72" t="b">
@@ -9409,7 +9536,7 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Clear Choice Malt ® Extra Pale</t>
         </is>
       </c>
       <c r="AE72" t="b">
@@ -9417,7 +9544,7 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
@@ -9426,16 +9553,16 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>22.73</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ72" t="n">
-        <v>80</v>
+        <v>81.5</v>
       </c>
       <c r="AK72" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr">
@@ -9453,6 +9580,7 @@
       <c r="AQ72" t="inlineStr"/>
       <c r="AR72" t="inlineStr"/>
       <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9470,75 +9598,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>1706434202728</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>2.10.5</t>
-        </is>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>3.9593909</v>
+      </c>
+      <c r="S73" t="n">
+        <v>50</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X73" t="b">
         <v>0</v>
       </c>
-      <c r="Z73" t="n">
-        <v>-2.29</v>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+        </is>
+      </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>6.82</v>
+        <v>22.73</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.036</v>
+        <v>1.037</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>9.6</v>
       </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
@@ -9549,10 +9685,9 @@
       <c r="AO73" t="inlineStr"/>
       <c r="AP73" t="inlineStr"/>
       <c r="AQ73" t="inlineStr"/>
-      <c r="AR73" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR73" t="inlineStr"/>
       <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9572,108 +9707,73 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>default-4c1345c</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1712314604140</v>
+        <v>1706434202728</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
+          <t>2.10.5</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q74" t="n">
         <v>2</v>
       </c>
-      <c r="L74" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X74" t="b">
         <v>0</v>
       </c>
-      <c r="Y74" t="n">
-        <v>0</v>
-      </c>
       <c r="Z74" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>4</v>
+        <v>-2.29</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
-        </is>
-      </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>2.27</v>
+        <v>6.82</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL74" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
+        <v>1.036</v>
+      </c>
+      <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
@@ -9684,11 +9784,245 @@
       <c r="AO74" t="inlineStr"/>
       <c r="AP74" t="inlineStr"/>
       <c r="AQ74" t="inlineStr"/>
-      <c r="AR74" t="inlineStr"/>
+      <c r="AR74" t="b">
+        <v>0</v>
+      </c>
       <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>First lager</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>default-4c1345c</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1712314604140</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="X75" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AH75" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Weyermann</t>
+        </is>
+      </c>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr"/>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="n">
+        <v>3</v>
+      </c>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Pale Malt, Maris Otter</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH76" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.03795</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Maris Otter</t>
+        </is>
+      </c>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="inlineStr"/>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS74"/>
+  <autoFilter ref="A1:AT76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9699,7 +10033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN60"/>
+  <dimension ref="A1:AO64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9707,7 +10041,7 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -9742,6 +10076,7 @@
     <col width="11" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9943,6 +10278,11 @@
       <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>day</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>_editFlag</t>
         </is>
       </c>
     </row>
@@ -10029,6 +10369,7 @@
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10133,6 +10474,7 @@
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10217,6 +10559,7 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10301,6 +10644,7 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10373,6 +10717,7 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10445,6 +10790,7 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10539,6 +10885,7 @@
       </c>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10633,6 +10980,7 @@
       </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10727,6 +11075,7 @@
       </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10835,6 +11184,7 @@
       </c>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10943,6 +11293,7 @@
       </c>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11051,6 +11402,7 @@
       </c>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11159,6 +11511,7 @@
       </c>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11267,6 +11620,7 @@
       </c>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11371,6 +11725,7 @@
       </c>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11478,6 +11833,7 @@
       </c>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11572,6 +11928,7 @@
       </c>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11656,6 +12013,7 @@
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11764,6 +12122,7 @@
       </c>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11872,6 +12231,7 @@
       </c>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11980,6 +12340,7 @@
       </c>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12088,6 +12449,7 @@
       </c>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12172,6 +12534,7 @@
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12266,6 +12629,7 @@
       </c>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12373,6 +12737,7 @@
       </c>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12481,6 +12846,7 @@
       </c>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12589,6 +12955,7 @@
       </c>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12697,6 +13064,7 @@
       </c>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12791,6 +13159,7 @@
       </c>
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12885,6 +13254,7 @@
       </c>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12992,6 +13362,7 @@
         <v>0</v>
       </c>
       <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13096,6 +13467,7 @@
       </c>
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13204,6 +13576,7 @@
       </c>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13316,6 +13689,7 @@
       <c r="AN35" t="n">
         <v>4</v>
       </c>
+      <c r="AO35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -13424,6 +13798,7 @@
       <c r="AN36" t="n">
         <v>4</v>
       </c>
+      <c r="AO36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13508,6 +13883,7 @@
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13616,6 +13992,7 @@
       </c>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13710,6 +14087,7 @@
       </c>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13804,6 +14182,7 @@
       </c>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13900,6 +14279,7 @@
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13994,6 +14374,7 @@
       </c>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14087,6 +14468,7 @@
         <v>-100</v>
       </c>
       <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14159,6 +14541,7 @@
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14253,6 +14636,7 @@
       </c>
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14360,6 +14744,7 @@
       </c>
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14432,6 +14817,7 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14539,6 +14925,7 @@
       </c>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14636,6 +15023,7 @@
       </c>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14708,6 +15096,7 @@
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14782,6 +15171,7 @@
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -14856,6 +15246,7 @@
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
       <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -14882,7 +15273,7 @@
         <v>6.3</v>
       </c>
       <c r="H53" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J53" t="n">
         <v>3.5</v>
@@ -14894,7 +15285,7 @@
         <v>30</v>
       </c>
       <c r="Q53" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -14963,6 +15354,7 @@
       </c>
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -14989,11 +15381,11 @@
         <v>5.5</v>
       </c>
       <c r="H54" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -15008,7 +15400,7 @@
       </c>
       <c r="X54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -15035,6 +15427,7 @@
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15065,7 +15458,7 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -15080,7 +15473,7 @@
       </c>
       <c r="X55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -15107,6 +15500,7 @@
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15126,22 +15520,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>default-58d2b845</t>
+          <t>default-bc4774ae</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="H56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Cascade</t>
+          <t>Centennial</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
@@ -15151,8 +15545,11 @@
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="n">
+        <v>76</v>
+      </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -15161,12 +15558,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Bittering</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -15177,8 +15574,8 @@
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15253,16 +15650,17 @@
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="inlineStr"/>
       <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -15272,36 +15670,33 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>default-bc4774ae</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H58" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>3.2</v>
+        <v>19.2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Centennial</t>
+          <t>Hallertauer Mittelfrueh</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="n">
-        <v>76</v>
-      </c>
       <c r="Z58" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -15310,12 +15705,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Bittering</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -15326,7 +15721,9 @@
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15353,11 +15750,11 @@
         <v>4</v>
       </c>
       <c r="H59" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>19.2</v>
+        <v>2.3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -15372,7 +15769,7 @@
       </c>
       <c r="X59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -15399,16 +15796,17 @@
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr"/>
       <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -15418,44 +15816,51 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>new-51wCf6O7CNR123kNt0aqW8Oah49aNp</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H60" t="n">
-        <v>10</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>2.3</v>
-      </c>
+        <v>14.7</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
+          <t>Citra</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>Pellet</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Aroma</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>Boil</t>
@@ -15463,6 +15868,7 @@
       </c>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="inlineStr"/>
@@ -15471,9 +15877,343 @@
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>new-51wCf6O7CNR123kNt0aqW8Oah49aNp</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>12</v>
+      </c>
+      <c r="H61" t="n">
+        <v>60</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Citra</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>new-51wCf6O7CNR123kNt0aqW8Oah49aNp</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>12</v>
+      </c>
+      <c r="H62" t="n">
+        <v>80</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Citra</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>new-51wCf6O7CNR123kNt0aqW8Oah49aNp</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>12</v>
+      </c>
+      <c r="H63" t="n">
+        <v>60</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Citra</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>new-51wCf6O7CNR123kNt0aqW8Oah49aNp</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1764889200000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>12</v>
+      </c>
+      <c r="H64" t="n">
+        <v>60</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Citra</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Dry Hop</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO64" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN60"/>
+  <autoFilter ref="A1:AO64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15484,7 +16224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL20"/>
+  <dimension ref="A1:AL21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -17749,8 +18489,103 @@
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Yeast</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>default-016efc</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>81</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>American ale yeast producing well balanced beers with low diacetyl and a very clean, crisp end palate. Forms a firm foam head and presents a very good ability to stay in suspension during fermentation.</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Fermentis</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>28</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>16</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Safale American</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>US-05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>pkg</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL20"/>
+  <autoFilter ref="A1:AL21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17761,7 +18596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB106"/>
+  <dimension ref="A1:AB119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -25905,26 +26740,26 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-2302b0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1781339598782</v>
+        <v>1781339599069</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -25932,17 +26767,18 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="b">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>44</v>
+        <v>94.5</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Baking Soda (NaHCO3)</t>
         </is>
       </c>
       <c r="Q96" t="b">
@@ -25989,26 +26825,26 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1781339597373</v>
+        <v>1781339598782</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -26016,18 +26852,17 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>941.2</v>
+        <v>44</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q97" t="b">
@@ -26074,26 +26909,26 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1781339599470</v>
+        <v>1781339597373</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -26101,20 +26936,18 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
-      </c>
-      <c r="L98" t="n">
-        <v>80</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>342.5</v>
+        <v>941.2</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q98" t="b">
@@ -26127,7 +26960,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -26161,69 +26994,70 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1775809151504</v>
+        <v>1781339599470</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>5</v>
-      </c>
-      <c r="L99" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L99" t="n">
+        <v>80</v>
+      </c>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>342.5</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P99" t="n">
-        <v>10</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U99" t="b">
+        <v>1</v>
+      </c>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
@@ -26247,26 +27081,26 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>default-yn-wln1000</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
+          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1775809134067</v>
+        <v>1775809151504</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -26274,18 +27108,18 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="b">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Yeast Nutrient (WLN1000)</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -26296,7 +27130,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -26310,15 +27144,7 @@
         </is>
       </c>
       <c r="U100" t="inlineStr"/>
-      <c r="V100" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
-We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
-        </is>
-      </c>
+      <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -26326,12 +27152,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -26341,53 +27167,56 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>default-bk9j78</t>
+          <t>default-yn-wln1000</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1PMknHJZdv0oQ7VqqIQ2rbYXMm9N5D</t>
+          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 260000000, "_seconds": 1712314610}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1712314610260</v>
+        <v>1775809134067</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="b">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>-5</v>
+        <v>80</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Canning Salt (NaCl)</t>
-        </is>
+          <t>Yeast Nutrient (WLN1000)</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
       </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -26397,16 +27226,19 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U101" t="b">
-        <v>1</v>
-      </c>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
+We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
+        </is>
+      </c>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr"/>
       <c r="AB101" t="inlineStr"/>
@@ -26429,26 +27261,26 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-bk9j78</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>lwPgFpUrns6MH8XqOw1PIDi3cAnGBV</t>
+          <t>1PMknHJZdv0oQ7VqqIQ2rbYXMm9N5D</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 450000000, "_seconds": 1712314609}</t>
+          <t>{"_nanoseconds": 260000000, "_seconds": 1712314610}</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1712314609450</v>
+        <v>1712314610260</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -26456,18 +27288,18 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Canning Salt (NaCl)</t>
         </is>
       </c>
       <c r="Q102" t="b">
@@ -26491,6 +27323,9 @@
       <c r="U102" t="b">
         <v>1</v>
       </c>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr"/>
@@ -26514,47 +27349,45 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Wtg8GXKfWxQjJGGYxmK7mUYTRcgSh9</t>
+          <t>lwPgFpUrns6MH8XqOw1PIDi3cAnGBV</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 450000000, "_seconds": 1712314609}</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1706434207828</v>
+        <v>1712314609450</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2.10.5</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>3</v>
-      </c>
-      <c r="L103" t="n">
-        <v>80</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="b">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q103" t="b">
@@ -26567,7 +27400,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -26578,9 +27411,6 @@
       <c r="U103" t="b">
         <v>1</v>
       </c>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr"/>
@@ -26602,49 +27432,75 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Wtg8GXKfWxQjJGGYxmK7mUYTRcgSh9</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>1706434207828</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2.10.5</t>
+        </is>
+      </c>
       <c r="K104" t="n">
-        <v>5</v>
-      </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L104" t="n">
+        <v>80</v>
+      </c>
+      <c r="M104" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-4</v>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
-        </is>
-      </c>
-      <c r="P104" t="n">
-        <v>15</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q104" t="b">
+        <v>0</v>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U104" t="b">
         <v>1</v>
       </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr"/>
@@ -26666,63 +27522,41 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
-        <v>1712314613742</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-6bc446</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L105" t="inlineStr"/>
-      <c r="M105" t="b">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>-11</v>
-      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Biofine Clear</t>
         </is>
       </c>
       <c r="P105" t="n">
         <v>15</v>
       </c>
       <c r="Q105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -26754,63 +27588,66 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>n39qcIsSvY0mhj8mb0KhJHE9df0bXd</t>
+          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 300000000, "_seconds": 1704369578}</t>
+          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1704369578300</v>
+        <v>1712314613742</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="b">
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>15</v>
       </c>
       <c r="Q106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="U106" t="inlineStr"/>
@@ -26819,8 +27656,865 @@
       <c r="AA106" t="inlineStr"/>
       <c r="AB106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>First lager</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>default-90c63c</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>n39qcIsSvY0mhj8mb0KhJHE9df0bXd</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 300000000, "_seconds": 1704369578}</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>1704369578300</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2.10.4</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>5</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Gelatin</t>
+        </is>
+      </c>
+      <c r="Q107" t="b">
+        <v>1</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Fining</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Calcium Chloride</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>10</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Epsom Salt (MgSO4)</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Gypsum (Calcium Sulfate)</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="L111" t="n">
+        <v>80</v>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q111" t="b">
+        <v>0</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U111" t="b">
+        <v>1</v>
+      </c>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Salt</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L113" t="n">
+        <v>80</v>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q113" t="b">
+        <v>0</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Sparge</t>
+        </is>
+      </c>
+      <c r="U113" t="b">
+        <v>1</v>
+      </c>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Calcium Chloride</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Epsom Salt (MgSO4)</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Gypsum (Calcium Sulfate)</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Salt</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>new-TUfxqCta0ITj3uHT8vfAbVIfLtzqyA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>2</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Protafloc</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Fining</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>tbsp</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Smash - Citra</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>new-Xe5CxkyeaTwnbVay8pIU6ai8XycVKB</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>2</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Yeast Nutrient</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>tsp</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB106"/>
+  <autoFilter ref="A1:AB119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -14,11 +14,11 @@
     <sheet name="Misc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AO$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AO$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1833,8 +1833,75 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>All Grain</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ernst Gouws</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1.04757289</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>First attempt at saison. 
+Using farmhouse yeast. 
+Start at 24 and freerise / slow rise to 28 hopefully to get more flavor from the yeast. 
+Table sugar to get it dryer.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P21"/>
+  <autoFilter ref="A1:P22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1845,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT76"/>
+  <dimension ref="A1:AT79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10021,8 +10088,304 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1781339591476</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Swaen Pilsner</t>
+        </is>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH77" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="inlineStr"/>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1781339591852</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X78" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>Swaen Vienna</t>
+        </is>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>1.03588</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>78</v>
+      </c>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="inlineStr"/>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>default-132c22b</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>1772634460383</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2.20.2</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="X79" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Sugar, Table (Sucrose)</t>
+        </is>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>Sugar</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr"/>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT76"/>
+  <autoFilter ref="A1:AT79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10033,7 +10396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO64"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -16212,8 +16575,350 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>default-NrD3kYzu8ONSucGjXgHxRcgSUwk2aK</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K65" t="n">
+        <v>11</v>
+      </c>
+      <c r="L65" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M65" t="n">
+        <v>17</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="S65" t="n">
+        <v>33</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Saaz</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Saaz is the famous aroma landrace variety originating in the Czech area of the same name. It has very mild, pleasant noble hoppy notes perfectly suited for and defines the Czech-style pilsner beers.
+Pedigree Czech landrace variety Aroma Classic noble aroma hop with long and strong tradition associated with classic pilsner beer.</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
+      <c r="Z65" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 967000000, "_seconds": 1775807186}</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>wgmsfM7hAArpDzCYHBWiW6iwLQheal</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 703000000, "_seconds": 1781070146}</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
+        <v>1781070146703</v>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL65" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>10</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr"/>
+      <c r="Z66" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
+        </is>
+      </c>
+      <c r="AJ66" t="n">
+        <v>1781339595684</v>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL66" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>default-NrD3kYzu8ONSucGjXgHxRcgSUwk2aK</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H67" t="n">
+        <v>20</v>
+      </c>
+      <c r="J67" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K67" t="n">
+        <v>11</v>
+      </c>
+      <c r="L67" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M67" t="n">
+        <v>17</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>33</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Saaz</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Saaz is the famous aroma landrace variety originating in the Czech area of the same name. It has very mild, pleasant noble hoppy notes perfectly suited for and defines the Czech-style pilsner beers.
+Pedigree Czech landrace variety Aroma Classic noble aroma hop with long and strong tradition associated with classic pilsner beer.</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr"/>
+      <c r="Z67" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 967000000, "_seconds": 1775807186}</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>wgmsfM7hAArpDzCYHBWiW6iwLQheal</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 703000000, "_seconds": 1781070146}</t>
+        </is>
+      </c>
+      <c r="AJ67" t="n">
+        <v>1781070146703</v>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL67" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO64"/>
+  <autoFilter ref="A1:AO67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16224,7 +16929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL21"/>
+  <dimension ref="A1:AL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -18584,8 +19289,133 @@
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Yeast</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>default-8FqpUdhfVGoKyF5z0R03cRiQBTlTqo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>default-lallemand-koln</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>80</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Vigorous fermentation that can be completed in 5 days</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Lallemand (LalBrew)</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>13</v>
+      </c>
+      <c r="S22" t="n">
+        <v>30</v>
+      </c>
+      <c r="U22" t="n">
+        <v>20</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Farmhouse</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>pkg</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>kölsch-style, neutral ales</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 856000000, "_seconds": 1784057989}</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>ExrXBelZBDAWJ8Bul57dLy2OgQdtkF</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 856000000, "_seconds": 1784057989}</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1784057989856</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL22" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL21"/>
+  <autoFilter ref="A1:AL22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18596,7 +19426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB119"/>
+  <dimension ref="A1:AB126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -28513,8 +29343,609 @@
       <c r="AA119" t="inlineStr"/>
       <c r="AB119" t="inlineStr"/>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>default-2302b0</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>1781339599069</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="b">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Baking Soda (NaHCO3)</t>
+        </is>
+      </c>
+      <c r="Q120" t="b">
+        <v>0</v>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U120" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>default-3b1827</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>1781339598782</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>2</v>
+      </c>
+      <c r="M121" t="b">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>44</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Calcium Chloride (CaCl2)</t>
+        </is>
+      </c>
+      <c r="Q121" t="b">
+        <v>0</v>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U121" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>default-4e9d62</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>1704369577229</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2.10.4</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>2</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="b">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Epsom Salt (MgSO4)</t>
+        </is>
+      </c>
+      <c r="Q122" t="b">
+        <v>0</v>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U122" t="b">
+        <v>1</v>
+      </c>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>default-1f88df</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1781339597373</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>3</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="b">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>941.2</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Gypsum (CaSO4)</t>
+        </is>
+      </c>
+      <c r="Q123" t="b">
+        <v>0</v>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U123" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>1781339599470</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L124" t="n">
+        <v>80</v>
+      </c>
+      <c r="M124" t="b">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q124" t="b">
+        <v>0</v>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U124" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>default-yn1j28sf</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1781339600221</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>5</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="b">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>33</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q125" t="b">
+        <v>0</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>default-5adf6e</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>1778997170065</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>5</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="b">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q126" t="b">
+        <v>0</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Fining</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB119"/>
+  <autoFilter ref="A1:AB126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -1682,7 +1682,7 @@
         <v>5.38</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>30.1</v>
+        <v>28.8</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>5.7</v>
@@ -15636,7 +15636,7 @@
         <v>6.3</v>
       </c>
       <c r="H53" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
         <v>3.5</v>
@@ -15648,7 +15648,7 @@
         <v>30</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>12.9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -15817,11 +15817,11 @@
         <v>10</v>
       </c>
       <c r="H55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -15,10 +15,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AO$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -775,7 +775,7 @@
         <v>5.12</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>29.9</v>
+        <v>28.7</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>4.2</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1.063943546</v>
+        <v>1.064283542</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.013</v>
@@ -1431,10 +1431,10 @@
         <v>6.69</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>27.7</v>
+        <v>31.7</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>12</v>
@@ -1673,19 +1673,19 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.050006898</v>
+        <v>1.047685263</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.009</v>
+        <v>1.01</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5.38</v>
+        <v>4.99</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>28.8</v>
+        <v>30.3</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>12</v>
@@ -1912,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT79"/>
+  <dimension ref="A1:AT80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7530,7 +7530,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q52" t="n">
         <v>1.9</v>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>58.54</v>
+        <v>70.73</v>
       </c>
       <c r="AI52" t="n">
         <v>1.0368</v>
@@ -7609,7 +7609,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q53" t="n">
         <v>5.1</v>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>24.39</v>
+        <v>19.51</v>
       </c>
       <c r="AI53" t="n">
         <v>1.03588</v>
@@ -7688,7 +7688,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="P54" t="n">
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>17.07</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AI54" t="n">
         <v>1.035</v>
@@ -7765,12 +7765,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7780,90 +7780,80 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>default-nym-3n456</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1721546982782</v>
+        <v>1781339589491</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M55" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
       <c r="Q55" t="n">
-        <v>1.77665</v>
-      </c>
-      <c r="U55" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="V55" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X55" t="b">
         <v>0</v>
       </c>
-      <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Barke Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>45.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.035</v>
+        <v>1.034</v>
       </c>
       <c r="AJ55" t="n">
-        <v>76.48</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
@@ -7894,47 +7884,68 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>default-nym-3n456</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1721546982782</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>3.807107</v>
+        <v>1.77665</v>
       </c>
       <c r="U56" t="n">
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="V56" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X56" t="b">
         <v>0</v>
       </c>
       <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
       <c r="AB56" t="n">
         <v>100</v>
       </c>
       <c r="AC56" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Barke Vienna Malt</t>
+          <t>Barke Pilsner</t>
         </is>
       </c>
       <c r="AE56" t="b">
@@ -7947,16 +7958,13 @@
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>32.26</v>
+        <v>45.16</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ56" t="n">
-        <v>74.66</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>10.5</v>
+        <v>76.48</v>
       </c>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr">
@@ -7971,13 +7979,9 @@
       </c>
       <c r="AO56" t="inlineStr"/>
       <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="inlineStr"/>
-      <c r="AS56" t="b">
-        <v>0</v>
-      </c>
+      <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -7999,75 +8003,66 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Q57" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
+        <v>3.807107</v>
+      </c>
+      <c r="U57" t="n">
+        <v>79</v>
+      </c>
+      <c r="V57" t="n">
+        <v>80</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X57" t="b">
         <v>0</v>
       </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y57" t="inlineStr"/>
       <c r="AB57" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="AC57" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Barke Vienna Malt</t>
         </is>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>8.06</v>
+        <v>32.26</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.036</v>
+        <v>1.034</v>
       </c>
       <c r="AJ57" t="n">
-        <v>77.90000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="AK57" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr">
@@ -8083,10 +8078,12 @@
       <c r="AO57" t="inlineStr"/>
       <c r="AP57" t="inlineStr"/>
       <c r="AQ57" t="n">
-        <v>412.8</v>
+        <v>3.4</v>
       </c>
       <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="inlineStr"/>
+      <c r="AS57" t="b">
+        <v>0</v>
+      </c>
       <c r="AT57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -8108,7 +8105,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -8121,14 +8118,12 @@
       <c r="L58" t="n">
         <v>0.25</v>
       </c>
-      <c r="M58" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="P58" t="n">
         <v>1.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>558.375635</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -8145,14 +8140,14 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AC58" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE58" t="b">
@@ -8160,7 +8155,7 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
@@ -8172,13 +8167,13 @@
         <v>8.06</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.037</v>
+        <v>1.036</v>
       </c>
       <c r="AJ58" t="n">
-        <v>80.06999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr">
@@ -8193,7 +8188,9 @@
       </c>
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
-      <c r="AQ58" t="inlineStr"/>
+      <c r="AQ58" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR58" t="inlineStr"/>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr"/>
@@ -8217,29 +8214,34 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>default-60a8af8</t>
+          <t>default-1482365</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M59" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q59" t="n">
-        <v>7.614213</v>
+        <v>2</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
-      </c>
-      <c r="U59" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X59" t="b">
@@ -8249,14 +8251,14 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AC59" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Munich I</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE59" t="b">
@@ -8264,7 +8266,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -8273,22 +8275,18 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>6.45</v>
+        <v>8.06</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.038</v>
+        <v>1.037</v>
       </c>
       <c r="AJ59" t="n">
-        <v>82.3</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AK59" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>Amber Liquid Extract</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -8301,9 +8299,7 @@
       </c>
       <c r="AO59" t="inlineStr"/>
       <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="inlineStr"/>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr"/>
@@ -8311,12 +8307,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8327,7 +8323,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-60a8af8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -8335,44 +8331,73 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>1.9</v>
+        <v>7.614213</v>
+      </c>
+      <c r="S60" t="n">
+        <v>50</v>
+      </c>
+      <c r="U60" t="n">
+        <v>78</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr"/>
+          <t>Base (Munich)</t>
+        </is>
+      </c>
+      <c r="X60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Munich I</t>
         </is>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+        </is>
+      </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>64.09999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.0368</v>
+        <v>1.038</v>
       </c>
       <c r="AJ60" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL60" t="inlineStr"/>
+        <v>82.3</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Amber Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
@@ -8382,7 +8407,9 @@
       </c>
       <c r="AO60" t="inlineStr"/>
       <c r="AP60" t="inlineStr"/>
-      <c r="AQ60" t="inlineStr"/>
+      <c r="AQ60" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr"/>
@@ -8406,7 +8433,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -8414,20 +8441,20 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>0.62</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE61" t="b">
@@ -8440,13 +8467,13 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>19.87</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ61" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr">
@@ -8485,7 +8512,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -8493,39 +8520,20 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="P62" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="Q62" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S62" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U62" t="n">
-        <v>80</v>
-      </c>
-      <c r="V62" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X62" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>4.6</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE62" t="b">
@@ -8538,16 +8546,13 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>9.619999999999999</v>
+        <v>19.87</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ62" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr">
@@ -8586,80 +8591,74 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
       <c r="L63" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>558.375635</v>
+        <v>6.6</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>80</v>
+      </c>
+      <c r="V63" t="n">
+        <v>80</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X63" t="b">
         <v>0</v>
       </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>5</v>
-      </c>
+      <c r="Y63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>6.41</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="AJ63" t="n">
-        <v>77.90000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="AK63" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
@@ -8669,9 +8668,7 @@
       </c>
       <c r="AO63" t="inlineStr"/>
       <c r="AP63" t="inlineStr"/>
-      <c r="AQ63" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ63" t="inlineStr"/>
       <c r="AR63" t="inlineStr"/>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr"/>
@@ -8679,12 +8676,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8692,78 +8689,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
-        <v>1777108192684</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
+          <t>default-b5ffdd1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.9</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X64" t="b">
         <v>0</v>
       </c>
-      <c r="Z64" t="n">
-        <v>7.8</v>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>3</v>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>73.95999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ64" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>10</v>
       </c>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
@@ -8773,10 +8775,10 @@
       </c>
       <c r="AO64" t="inlineStr"/>
       <c r="AP64" t="inlineStr"/>
-      <c r="AQ64" t="inlineStr"/>
-      <c r="AR64" t="b">
-        <v>0</v>
-      </c>
+      <c r="AQ64" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="AR64" t="inlineStr"/>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr"/>
     </row>
@@ -8798,52 +8800,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1781339591852</v>
+        <v>1777108192684</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X65" t="b">
         <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.85</v>
+        <v>7.8</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE65" t="b">
@@ -8856,13 +8858,13 @@
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>14.79</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ65" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr">
@@ -8878,7 +8880,9 @@
       <c r="AO65" t="inlineStr"/>
       <c r="AP65" t="inlineStr"/>
       <c r="AQ65" t="inlineStr"/>
-      <c r="AR65" t="inlineStr"/>
+      <c r="AR65" t="b">
+        <v>0</v>
+      </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr"/>
     </row>
@@ -8900,26 +8904,26 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -8927,42 +8931,25 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="P66" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S66" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U66" t="n">
-        <v>80</v>
-      </c>
-      <c r="V66" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X66" t="b">
         <v>0</v>
       </c>
-      <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE66" t="b">
@@ -8975,16 +8962,13 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>8.880000000000001</v>
+        <v>14.79</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ66" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr">
@@ -9022,75 +9006,91 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1776345994305</v>
+        <v>1781339591050</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S67" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>80</v>
+      </c>
+      <c r="V67" t="n">
+        <v>80</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X67" t="b">
         <v>0</v>
       </c>
+      <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>2</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>2.37</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ67" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
@@ -9113,12 +9113,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9128,71 +9128,75 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1781339591476</v>
+        <v>1776345994305</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.45</v>
+        <v>0.08</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.9</v>
+        <v>61</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X68" t="b">
         <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG68" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>74.23999999999999</v>
+        <v>2.37</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.0368</v>
+        <v>1.034</v>
       </c>
       <c r="AJ68" t="n">
-        <v>80</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr">
@@ -9230,26 +9234,26 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -9257,25 +9261,25 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X69" t="b">
         <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE69" t="b">
@@ -9288,13 +9292,13 @@
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>15.15</v>
+        <v>73.02</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ69" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr">
@@ -9332,26 +9336,26 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -9359,42 +9363,25 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="P70" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="Q70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S70" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U70" t="n">
-        <v>80</v>
-      </c>
-      <c r="V70" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X70" t="b">
         <v>0</v>
       </c>
-      <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE70" t="b">
@@ -9407,16 +9394,13 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>9.09</v>
+        <v>14.29</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ70" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr">
@@ -9454,26 +9438,26 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1781339589491</v>
+        <v>1781339591050</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -9481,48 +9465,64 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S71" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>80</v>
+      </c>
+      <c r="V71" t="n">
+        <v>80</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X71" t="b">
         <v>0</v>
       </c>
+      <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>1.36</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>1.52</v>
+        <v>11.11</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ71" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr">
@@ -9545,12 +9545,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9558,52 +9558,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="n">
-        <v>0</v>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1781339589491</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L72" t="n">
-        <v>3</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="P72" t="n">
-        <v>1.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.8527919</v>
-      </c>
-      <c r="S72" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X72" t="b">
         <v>0</v>
       </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>4.5</v>
+      <c r="Z72" t="n">
+        <v>1.36</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® Extra Pale</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE72" t="b">
@@ -9611,30 +9613,27 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>68.18000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.038</v>
+        <v>1.034</v>
       </c>
       <c r="AJ72" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>10.1</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
@@ -9668,7 +9667,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -9679,21 +9678,21 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="P73" t="n">
         <v>1.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.9593909</v>
+        <v>1.8527919</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X73" t="b">
@@ -9710,7 +9709,7 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Clear Choice Malt ® Extra Pale</t>
         </is>
       </c>
       <c r="AE73" t="b">
@@ -9718,7 +9717,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
@@ -9727,16 +9726,16 @@
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>22.73</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ73" t="n">
-        <v>80</v>
+        <v>81.5</v>
       </c>
       <c r="AK73" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr">
@@ -9772,75 +9771,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>1706434202728</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2.10.5</t>
-        </is>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>3.9593909</v>
+      </c>
+      <c r="S74" t="n">
+        <v>50</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X74" t="b">
         <v>0</v>
       </c>
-      <c r="Z74" t="n">
-        <v>-2.29</v>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+        </is>
+      </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>6.82</v>
+        <v>22.73</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.036</v>
+        <v>1.037</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>9.6</v>
       </c>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
@@ -9851,9 +9858,7 @@
       <c r="AO74" t="inlineStr"/>
       <c r="AP74" t="inlineStr"/>
       <c r="AQ74" t="inlineStr"/>
-      <c r="AR74" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR74" t="inlineStr"/>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr"/>
     </row>
@@ -9875,108 +9880,73 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>default-4c1345c</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1712314604140</v>
+        <v>1706434202728</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
+          <t>2.10.5</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q75" t="n">
         <v>2</v>
       </c>
-      <c r="L75" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P75" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X75" t="b">
         <v>0</v>
       </c>
-      <c r="Y75" t="n">
-        <v>0</v>
-      </c>
       <c r="Z75" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>4</v>
+        <v>-2.29</v>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
-        </is>
-      </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>2.27</v>
+        <v>6.82</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
+        <v>1.036</v>
+      </c>
+      <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
@@ -9987,19 +9957,21 @@
       <c r="AO75" t="inlineStr"/>
       <c r="AP75" t="inlineStr"/>
       <c r="AQ75" t="inlineStr"/>
-      <c r="AR75" t="inlineStr"/>
+      <c r="AR75" t="b">
+        <v>0</v>
+      </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10007,69 +9979,110 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+          <t>default-4c1345c</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>1712314604140</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
       <c r="L76" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q76" t="n">
-        <v>3</v>
-      </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="X76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>4</v>
+      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Pale Malt, Maris Otter</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
+        </is>
+      </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>100</v>
+        <v>2.27</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.03795</v>
+        <v>1.03</v>
       </c>
       <c r="AJ76" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
+        <v>65.2</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Maris Otter</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
@@ -10082,21 +10095,17 @@
       <c r="AQ76" t="inlineStr"/>
       <c r="AR76" t="inlineStr"/>
       <c r="AS76" t="inlineStr"/>
-      <c r="AT76" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="AT76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10104,78 +10113,69 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>1781339591476</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
-        <v>2.5</v>
-      </c>
+        <v>13.18</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
-        <v>1.9</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X77" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>6.7</v>
-      </c>
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
-        </is>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
+          <t>Pale Malt, Maris Otter</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>81.97</v>
+        <v>100</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.0368</v>
+        <v>1.03795</v>
       </c>
       <c r="AJ77" t="n">
-        <v>80</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Maris Otter</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -10188,7 +10188,11 @@
       <c r="AQ77" t="inlineStr"/>
       <c r="AR77" t="inlineStr"/>
       <c r="AS77" t="inlineStr"/>
-      <c r="AT77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10208,26 +10212,26 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -10235,25 +10239,25 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q78" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X78" t="b">
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE78" t="b">
@@ -10266,13 +10270,13 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>11.48</v>
+        <v>81.97</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ78" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="inlineStr">
@@ -10310,71 +10314,81 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>default-132c22b</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1772634460383</v>
+        <v>1781339591852</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1.22</v>
+        <v>0.35</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>5.1</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Base (Vienna)</t>
+        </is>
       </c>
       <c r="X79" t="b">
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Sugar, Table (Sucrose)</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
       <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="AH79" t="n">
-        <v>6.56</v>
+        <v>11.48</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.046</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ79" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr"/>
@@ -10384,8 +10398,100 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>default-132c22b</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>1772634460383</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2.20.2</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="X80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>Sugar, Table (Sucrose)</t>
+        </is>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>Sugar</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT79"/>
+  <autoFilter ref="A1:AT80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11574,7 +11680,7 @@
         <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
         <v>5.59</v>
@@ -11586,7 +11692,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -11683,7 +11789,7 @@
         <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
         <v>5.59</v>
@@ -11695,7 +11801,7 @@
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -14188,7 +14294,7 @@
         <v>6.5</v>
       </c>
       <c r="H37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
         <v>3.5</v>
@@ -14200,7 +14306,7 @@
         <v>30</v>
       </c>
       <c r="Q37" t="n">
-        <v>15.4</v>
+        <v>20.4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -14285,7 +14391,7 @@
         <v>30</v>
       </c>
       <c r="Q38" t="n">
-        <v>8.9</v>
+        <v>6.8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -14308,7 +14414,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -14382,13 +14488,13 @@
         <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -15636,7 +15742,7 @@
         <v>6.3</v>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J53" t="n">
         <v>3.5</v>
@@ -15648,7 +15754,7 @@
         <v>30</v>
       </c>
       <c r="Q53" t="n">
-        <v>12.9</v>
+        <v>15.3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -15748,7 +15854,7 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -15890,11 +15996,11 @@
         <v>10</v>
       </c>
       <c r="H56" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -15965,11 +16071,11 @@
         <v>5.5</v>
       </c>
       <c r="H57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -19426,7 +19532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB126"/>
+  <dimension ref="A1:AB125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -21073,16 +21179,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>U7Q7AloKFG2MwxuQxE9znDsGScpFBa</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 14000000, "_seconds": 1778997168}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1778997168014</v>
+        <v>1781339598782</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -21090,13 +21196,13 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -21157,16 +21263,16 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>RsTDDT4iPhBM6HtLnE1sLut1VSfSzy</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 554000000, "_seconds": 1778997167}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1778997167554</v>
+        <v>1781339597373</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -21174,14 +21280,14 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>943</v>
+        <v>941.2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -21242,16 +21348,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>GMe0y7iJZybWYXIcl3sWc1BgoZQQnT</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 359000000, "_seconds": 1778997168}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1778997168359</v>
+        <v>1781339599470</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -21268,7 +21374,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>344.5</v>
+        <v>342.5</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -25632,30 +25738,30 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1704369575930</v>
+        <v>1781339598782</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -25683,9 +25789,6 @@
       <c r="U73" t="b">
         <v>1</v>
       </c>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
@@ -25807,31 +25910,31 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1723974351111</v>
+        <v>1781339597373</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>-21</v>
+        <v>941.2</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -25892,20 +25995,20 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1723974352697</v>
+        <v>1781339599470</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -25918,7 +26021,7 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>-15</v>
+        <v>342.5</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -25946,9 +26049,6 @@
       <c r="U76" t="b">
         <v>1</v>
       </c>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr"/>
@@ -26107,12 +26207,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -26122,26 +26222,26 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
+          <t>default-bk9j78</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
+          <t>E5Gr0KsnlU7nZUzYNeiN3uBXsR8AlK</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
+          <t>{"_nanoseconds": 580000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1723974355076</v>
+        <v>1723974351580</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -26149,39 +26249,44 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Gelatin</t>
+          <t>Canning Salt (NaCl)</t>
         </is>
       </c>
       <c r="Q79" t="b">
+        <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U79" t="b">
         <v>1</v>
       </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
@@ -26205,26 +26310,26 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>default-bk9j78</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>E5Gr0KsnlU7nZUzYNeiN3uBXsR8AlK</t>
+          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 580000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1723974351580</v>
+        <v>1723974351111</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -26239,11 +26344,11 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>-11</v>
+        <v>-21</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Canning Salt (NaCl)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q80" t="b">
@@ -26267,9 +26372,6 @@
       <c r="U80" t="b">
         <v>1</v>
       </c>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
@@ -26293,26 +26395,26 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
+          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1723974351111</v>
+        <v>1723974352697</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -26320,18 +26422,20 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>3</v>
-      </c>
-      <c r="L81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>80</v>
+      </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>-21</v>
+        <v>-15</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q81" t="b">
@@ -26344,7 +26448,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -26355,6 +26459,9 @@
       <c r="U81" t="b">
         <v>1</v>
       </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr"/>
@@ -26378,26 +26485,26 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1723974352697</v>
+        <v>1723974354144</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -26407,44 +26514,40 @@
       <c r="K82" t="n">
         <v>1</v>
       </c>
-      <c r="L82" t="n">
-        <v>80</v>
-      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>15</v>
       </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U82" t="b">
-        <v>1</v>
-      </c>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
@@ -26468,26 +26571,26 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-6bc446</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
+          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
+          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1723974354144</v>
+        <v>1721546982940</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -26495,39 +26598,36 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>-19</v>
+        <v>-5</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P83" t="n">
-        <v>15</v>
+          <t>Biofine Clear</t>
+        </is>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="U83" t="inlineStr"/>
@@ -26539,12 +26639,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -26554,66 +26654,70 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
+          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1721546982940</v>
+        <v>1704369575930</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>3</v>
-      </c>
-      <c r="L84" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q84" t="b">
+        <v>0</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U84" t="b">
         <v>1</v>
       </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
@@ -26637,35 +26741,36 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>lcvTqdMfO6NPRj6JBJoHMhZuaJN2Fj</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 428000000, "_seconds": 1772634485}</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1704369575930</v>
+        <v>1772634485428</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.20.2</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>2.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="b">
         <v>0</v>
       </c>
@@ -26674,7 +26779,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q85" t="b">
@@ -26698,9 +26803,6 @@
       <c r="U85" t="b">
         <v>1</v>
       </c>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
@@ -26724,26 +26826,26 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>lcvTqdMfO6NPRj6JBJoHMhZuaJN2Fj</t>
+          <t>eIuDGEasVf2TMzwhyNhxT2RGDDKeIc</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 428000000, "_seconds": 1772634485}</t>
+          <t>{"_nanoseconds": 497000000, "_seconds": 1772634487}</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1772634485428</v>
+        <v>1772634487497</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -26751,9 +26853,11 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
-      </c>
-      <c r="L86" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L86" t="n">
+        <v>80</v>
+      </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
@@ -26762,7 +26866,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q86" t="b">
@@ -26775,7 +26879,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -26809,70 +26913,69 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>eIuDGEasVf2TMzwhyNhxT2RGDDKeIc</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 497000000, "_seconds": 1772634487}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1772634487497</v>
+        <v>1723974354144</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L87" t="n">
-        <v>80</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="b">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>15</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U87" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
@@ -26894,55 +26997,31 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>1723974354144</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>new-BdtFpaKlultfp6wX0TWywYGFQGjVk6</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="b">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>-19</v>
-      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t xml:space="preserve">Zync tablet </t>
         </is>
       </c>
       <c r="P88" t="n">
         <v>15</v>
       </c>
-      <c r="Q88" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>Other</t>
@@ -26959,10 +27038,17 @@
         </is>
       </c>
       <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>1/6 zync tablet zync sulphate</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -26980,68 +27066,82 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>new-BdtFpaKlultfp6wX0TWywYGFQGjVk6</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>default-6bc446</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>1721546982940</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K89" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="M89" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-5</v>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zync tablet </t>
-        </is>
-      </c>
-      <c r="P89" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q89" t="inlineStr"/>
+          <t>Biofine Clear</t>
+        </is>
+      </c>
+      <c r="Q89" t="b">
+        <v>1</v>
+      </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>1/6 zync tablet zync sulphate</t>
-        </is>
-      </c>
+      <c r="AB89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -27051,66 +27151,67 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1721546982940</v>
+        <v>1781339598782</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>3</v>
-      </c>
-      <c r="L90" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="M90" t="b">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>-5</v>
+        <v>44</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q90" t="b">
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U90" t="b">
         <v>1</v>
       </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="inlineStr"/>
@@ -27134,26 +27235,26 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1781339598782</v>
+        <v>1781339597373</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -27161,17 +27262,18 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="b">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>44</v>
+        <v>941.2</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q91" t="b">
@@ -27218,26 +27320,26 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1781339597373</v>
+        <v>1781339599470</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -27245,18 +27347,20 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L92" t="n">
+        <v>80</v>
+      </c>
       <c r="M92" t="b">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>941.2</v>
+        <v>342.5</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q92" t="b">
@@ -27269,7 +27373,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -27303,70 +27407,69 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1781339599470</v>
+        <v>1775809151504</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
-      </c>
-      <c r="L93" t="n">
-        <v>80</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="b">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>342.5</v>
+        <v>5</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U93" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="inlineStr"/>
@@ -27390,26 +27493,26 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-yn-wln1000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
+          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1775809151504</v>
+        <v>1775809134067</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -27417,18 +27520,18 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="b">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
+          <t>Yeast Nutrient (WLN1000)</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -27439,7 +27542,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -27453,7 +27556,15 @@
         </is>
       </c>
       <c r="U94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
+      <c r="V94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
+We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
+        </is>
+      </c>
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr"/>
@@ -27461,12 +27572,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -27476,56 +27587,53 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>default-yn-wln1000</t>
+          <t>default-2302b0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
+          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1775809134067</v>
+        <v>1781339599069</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="b">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>80</v>
+        <v>94.5</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Yeast Nutrient (WLN1000)</t>
-        </is>
-      </c>
-      <c r="P95" t="n">
-        <v>10</v>
+          <t>Baking Soda (NaHCO3)</t>
+        </is>
       </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -27535,19 +27643,13 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
-We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
-        </is>
-      </c>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U95" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="inlineStr"/>
       <c r="AB95" t="inlineStr"/>
@@ -27570,26 +27672,26 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>default-2302b0</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1781339599069</v>
+        <v>1781339598782</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -27597,18 +27699,17 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
       <c r="M96" t="b">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>94.5</v>
+        <v>44</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Baking Soda (NaHCO3)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q96" t="b">
@@ -27655,26 +27756,26 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1781339598782</v>
+        <v>1781339597373</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -27682,17 +27783,18 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>3.5</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>44</v>
+        <v>941.2</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q97" t="b">
@@ -27739,26 +27841,26 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1781339597373</v>
+        <v>1781339599470</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -27766,18 +27868,20 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L98" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L98" t="n">
+        <v>80</v>
+      </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>941.2</v>
+        <v>342.5</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q98" t="b">
@@ -27790,7 +27894,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -27824,70 +27928,69 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1781339599470</v>
+        <v>1775809151504</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
-      </c>
-      <c r="L99" t="n">
-        <v>80</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>342.5</v>
+        <v>5</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
       </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U99" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
@@ -27911,26 +28014,26 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-yn-wln1000</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
+          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1775809151504</v>
+        <v>1775809134067</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -27938,18 +28041,18 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="b">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
+          <t>Yeast Nutrient (WLN1000)</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -27960,7 +28063,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -27974,7 +28077,15 @@
         </is>
       </c>
       <c r="U100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
+      <c r="V100" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
+We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
+        </is>
+      </c>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -27982,12 +28093,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -27997,56 +28108,53 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>default-yn-wln1000</t>
+          <t>default-bk9j78</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
+          <t>1PMknHJZdv0oQ7VqqIQ2rbYXMm9N5D</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 260000000, "_seconds": 1712314610}</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1775809134067</v>
+        <v>1712314610260</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="b">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>80</v>
+        <v>-5</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Yeast Nutrient (WLN1000)</t>
-        </is>
-      </c>
-      <c r="P101" t="n">
-        <v>10</v>
+          <t>Canning Salt (NaCl)</t>
+        </is>
       </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -28056,19 +28164,16 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
-We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
-        </is>
-      </c>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U101" t="b">
+        <v>1</v>
+      </c>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr"/>
       <c r="AB101" t="inlineStr"/>
@@ -28091,26 +28196,26 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>default-bk9j78</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1PMknHJZdv0oQ7VqqIQ2rbYXMm9N5D</t>
+          <t>lwPgFpUrns6MH8XqOw1PIDi3cAnGBV</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 260000000, "_seconds": 1712314610}</t>
+          <t>{"_nanoseconds": 450000000, "_seconds": 1712314609}</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1712314610260</v>
+        <v>1712314609450</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -28118,18 +28223,18 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Canning Salt (NaCl)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q102" t="b">
@@ -28153,9 +28258,6 @@
       <c r="U102" t="b">
         <v>1</v>
       </c>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr"/>
@@ -28179,45 +28281,47 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>lwPgFpUrns6MH8XqOw1PIDi3cAnGBV</t>
+          <t>Wtg8GXKfWxQjJGGYxmK7mUYTRcgSh9</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 450000000, "_seconds": 1712314609}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1712314609450</v>
+        <v>1706434207828</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.5</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>6</v>
-      </c>
-      <c r="L103" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L103" t="n">
+        <v>80</v>
+      </c>
       <c r="M103" t="b">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q103" t="b">
@@ -28230,7 +28334,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -28241,6 +28345,9 @@
       <c r="U103" t="b">
         <v>1</v>
       </c>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr"/>
@@ -28262,57 +28369,36 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Wtg8GXKfWxQjJGGYxmK7mUYTRcgSh9</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>1706434207828</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>2.10.5</t>
-        </is>
-      </c>
+          <t>default-6bc446</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>3</v>
-      </c>
-      <c r="L104" t="n">
-        <v>80</v>
-      </c>
-      <c r="M104" t="b">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Biofine Clear</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>15</v>
       </c>
       <c r="Q104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -28322,15 +28408,10 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U104" t="b">
-        <v>1</v>
-      </c>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr"/>
@@ -28352,41 +28433,63 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+          <t>default-yn1j28sf</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>1712314613742</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="M105" t="b">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-11</v>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
+          <t>Yeast Nutrients</t>
         </is>
       </c>
       <c r="P105" t="n">
         <v>15</v>
       </c>
       <c r="Q105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -28418,66 +28521,63 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-90c63c</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
+          <t>n39qcIsSvY0mhj8mb0KhJHE9df0bXd</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
+          <t>{"_nanoseconds": 300000000, "_seconds": 1704369578}</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1712314613742</v>
+        <v>1704369578300</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="b">
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P106" t="n">
-        <v>15</v>
+          <t>Gelatin</t>
+        </is>
       </c>
       <c r="Q106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="U106" t="inlineStr"/>
@@ -28489,12 +28589,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -28502,68 +28602,47 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>n39qcIsSvY0mhj8mb0KhJHE9df0bXd</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 300000000, "_seconds": 1704369578}</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>1704369578300</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>2.10.4</t>
-        </is>
-      </c>
+          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>5</v>
+        <v>0.96</v>
       </c>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" t="b">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
-      </c>
-      <c r="Q107" t="b">
-        <v>1</v>
-      </c>
+          <t>Calcium Chloride</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Mash</t>
         </is>
       </c>
       <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr"/>
@@ -28588,7 +28667,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -28596,14 +28675,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>0.96</v>
+        <v>10</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Calcium Chloride</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr"/>
@@ -28650,7 +28729,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
+          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -28658,14 +28737,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
-        <v>10</v>
+        <v>17.64</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Gypsum (Calcium Sulfate)</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr"/>
@@ -28712,7 +28791,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -28720,17 +28799,21 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="L110" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="L110" t="n">
+        <v>80</v>
+      </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Gypsum (Calcium Sulfate)</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr"/>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q110" t="b">
+        <v>0</v>
+      </c>
       <c r="R110" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -28738,7 +28821,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -28746,7 +28829,9 @@
           <t>Mash</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
+      <c r="U110" t="b">
+        <v>1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
@@ -28774,7 +28859,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -28782,21 +28867,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="L111" t="n">
-        <v>80</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
-      </c>
-      <c r="Q111" t="b">
-        <v>0</v>
-      </c>
+          <t>Salt</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -28804,7 +28885,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -28812,9 +28893,7 @@
           <t>Mash</t>
         </is>
       </c>
-      <c r="U111" t="b">
-        <v>1</v>
-      </c>
+      <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
@@ -28842,7 +28921,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -28850,17 +28929,21 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L112" t="inlineStr"/>
+        <v>3.05</v>
+      </c>
+      <c r="L112" t="n">
+        <v>80</v>
+      </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Salt</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr"/>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q112" t="b">
+        <v>0</v>
+      </c>
       <c r="R112" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -28868,15 +28951,17 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr"/>
+          <t>Sparge</t>
+        </is>
+      </c>
+      <c r="U112" t="b">
+        <v>1</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
@@ -28904,7 +28989,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -28912,21 +28997,20 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L113" t="n">
-        <v>80</v>
-      </c>
+        <v>0.34</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
-      </c>
-      <c r="Q113" t="b">
-        <v>0</v>
-      </c>
+          <t>Calcium Chloride</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -28934,17 +29018,15 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>Sparge</t>
-        </is>
-      </c>
-      <c r="U113" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
@@ -28972,7 +29054,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -28980,14 +29062,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="n">
-        <v>0.34</v>
+        <v>3.62</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Calcium Chloride</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -29037,7 +29119,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
+          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -29045,14 +29127,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="n">
-        <v>3.62</v>
+        <v>6.4</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Gypsum (Calcium Sulfate)</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -29102,7 +29184,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
+          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -29110,14 +29192,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
-        <v>6.4</v>
+        <v>1.06</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Gypsum (Calcium Sulfate)</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -29167,7 +29249,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
+          <t>new-TUfxqCta0ITj3uHT8vfAbVIfLtzqyA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -29175,28 +29257,28 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
-        <v>1.06</v>
+        <v>2</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Protafloc</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>tbsp</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -29232,7 +29314,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>new-TUfxqCta0ITj3uHT8vfAbVIfLtzqyA</t>
+          <t>new-Xe5CxkyeaTwnbVay8pIU6ai8XycVKB</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -29247,7 +29329,7 @@
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Protafloc</t>
+          <t>Yeast Nutrient</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -29256,12 +29338,12 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>tbsp</t>
+          <t>tsp</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -29281,12 +29363,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -29294,50 +29376,70 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>new-Xe5CxkyeaTwnbVay8pIU6ai8XycVKB</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+          <t>default-2302b0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>1781339599069</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="M119" t="b">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>94.5</v>
+      </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Yeast Nutrient</t>
-        </is>
-      </c>
-      <c r="P119" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q119" t="inlineStr"/>
+          <t>Baking Soda (NaHCO3)</t>
+        </is>
+      </c>
+      <c r="Q119" t="b">
+        <v>0</v>
+      </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>tsp</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U119" t="b">
+        <v>1</v>
+      </c>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
       <c r="AA119" t="inlineStr"/>
@@ -29361,26 +29463,26 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>default-2302b0</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1781339599069</v>
+        <v>1781339598782</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -29388,18 +29490,17 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L120" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="M120" t="b">
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>94.5</v>
+        <v>44</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Baking Soda (NaHCO3)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q120" t="b">
@@ -29446,44 +29547,45 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-4e9d62</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1781339598782</v>
+        <v>1704369577229</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K121" t="n">
         <v>2</v>
       </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="b">
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="Q121" t="b">
@@ -29507,6 +29609,9 @@
       <c r="U121" t="b">
         <v>1</v>
       </c>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr"/>
@@ -29530,45 +29635,45 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>default-4e9d62</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1704369577229</v>
+        <v>1781339597373</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="b">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>941.2</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q122" t="b">
@@ -29592,9 +29697,6 @@
       <c r="U122" t="b">
         <v>1</v>
       </c>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
@@ -29618,26 +29720,26 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1781339597373</v>
+        <v>1781339599470</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -29645,18 +29747,20 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>3</v>
-      </c>
-      <c r="L123" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L123" t="n">
+        <v>80</v>
+      </c>
       <c r="M123" t="b">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>941.2</v>
+        <v>342.5</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q123" t="b">
@@ -29669,7 +29773,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -29703,26 +29807,26 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1781339599470</v>
+        <v>1781339600221</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -29730,43 +29834,42 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L124" t="n">
-        <v>80</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="b">
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>342.5</v>
+        <v>33</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>15</v>
       </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U124" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
       <c r="AA124" t="inlineStr"/>
@@ -29790,26 +29893,26 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
+          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
+          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1781339600221</v>
+        <v>1778997170065</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -29824,22 +29927,22 @@
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -29858,94 +29961,8 @@
       <c r="AA125" t="inlineStr"/>
       <c r="AB125" t="inlineStr"/>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Saison</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Misc</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>default-5adf6e</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
-        </is>
-      </c>
-      <c r="I126" t="n">
-        <v>1778997170065</v>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="K126" t="n">
-        <v>5</v>
-      </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="b">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P126" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q126" t="b">
-        <v>0</v>
-      </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr"/>
-      <c r="Y126" t="inlineStr"/>
-      <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr"/>
-      <c r="AB126" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AB126"/>
+  <autoFilter ref="A1:AB125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AO$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19532,7 +19532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB125"/>
+  <dimension ref="A1:AB124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -27587,26 +27587,26 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>default-2302b0</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1781339599069</v>
+        <v>1781339598782</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -27614,18 +27614,17 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L95" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
       <c r="M95" t="b">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>94.5</v>
+        <v>44</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Baking Soda (NaHCO3)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q95" t="b">
@@ -27672,26 +27671,26 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1781339598782</v>
+        <v>1781339597373</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -27699,17 +27698,18 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>3.5</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="b">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>44</v>
+        <v>941.2</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q96" t="b">
@@ -27756,26 +27756,26 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1781339597373</v>
+        <v>1781339599470</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -27783,18 +27783,20 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L97" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L97" t="n">
+        <v>80</v>
+      </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>941.2</v>
+        <v>342.5</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q97" t="b">
@@ -27807,7 +27809,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -27841,70 +27843,69 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1781339599470</v>
+        <v>1775809151504</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
-      </c>
-      <c r="L98" t="n">
-        <v>80</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>342.5</v>
+        <v>5</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
       </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U98" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr"/>
@@ -27928,26 +27929,26 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-yn-wln1000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
+          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1775809151504</v>
+        <v>1775809134067</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -27955,18 +27956,18 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
+          <t>Yeast Nutrient (WLN1000)</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -27977,7 +27978,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -27991,7 +27992,15 @@
         </is>
       </c>
       <c r="U99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
+      <c r="V99" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
+We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
+        </is>
+      </c>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -27999,12 +28008,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -28014,56 +28023,53 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>default-yn-wln1000</t>
+          <t>default-bk9j78</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
+          <t>1PMknHJZdv0oQ7VqqIQ2rbYXMm9N5D</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 260000000, "_seconds": 1712314610}</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1775809134067</v>
+        <v>1712314610260</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="b">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>80</v>
+        <v>-5</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Yeast Nutrient (WLN1000)</t>
-        </is>
-      </c>
-      <c r="P100" t="n">
-        <v>10</v>
+          <t>Canning Salt (NaCl)</t>
+        </is>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -28073,19 +28079,16 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
-We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
-        </is>
-      </c>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U100" t="b">
+        <v>1</v>
+      </c>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -28108,26 +28111,26 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>default-bk9j78</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1PMknHJZdv0oQ7VqqIQ2rbYXMm9N5D</t>
+          <t>lwPgFpUrns6MH8XqOw1PIDi3cAnGBV</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 260000000, "_seconds": 1712314610}</t>
+          <t>{"_nanoseconds": 450000000, "_seconds": 1712314609}</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1712314610260</v>
+        <v>1712314609450</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -28135,18 +28138,18 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="b">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Canning Salt (NaCl)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q101" t="b">
@@ -28170,9 +28173,6 @@
       <c r="U101" t="b">
         <v>1</v>
       </c>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr"/>
@@ -28196,45 +28196,47 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>lwPgFpUrns6MH8XqOw1PIDi3cAnGBV</t>
+          <t>Wtg8GXKfWxQjJGGYxmK7mUYTRcgSh9</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 450000000, "_seconds": 1712314609}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1712314609450</v>
+        <v>1706434207828</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.5</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>6</v>
-      </c>
-      <c r="L102" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L102" t="n">
+        <v>80</v>
+      </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q102" t="b">
@@ -28247,7 +28249,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -28258,6 +28260,9 @@
       <c r="U102" t="b">
         <v>1</v>
       </c>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr"/>
@@ -28279,57 +28284,36 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Wtg8GXKfWxQjJGGYxmK7mUYTRcgSh9</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>1706434207828</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>2.10.5</t>
-        </is>
-      </c>
+          <t>default-6bc446</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>3</v>
-      </c>
-      <c r="L103" t="n">
-        <v>80</v>
-      </c>
-      <c r="M103" t="b">
-        <v>0</v>
-      </c>
-      <c r="N103" t="n">
-        <v>-4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Biofine Clear</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>15</v>
       </c>
       <c r="Q103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -28339,15 +28323,10 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U103" t="b">
-        <v>1</v>
-      </c>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr"/>
@@ -28369,41 +28348,63 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>default-yn1j28sf</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>1712314613742</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="M104" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-11</v>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
+          <t>Yeast Nutrients</t>
         </is>
       </c>
       <c r="P104" t="n">
         <v>15</v>
       </c>
       <c r="Q104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -28435,66 +28436,63 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-90c63c</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
+          <t>n39qcIsSvY0mhj8mb0KhJHE9df0bXd</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
+          <t>{"_nanoseconds": 300000000, "_seconds": 1704369578}</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1712314613742</v>
+        <v>1704369578300</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="b">
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P105" t="n">
-        <v>15</v>
+          <t>Gelatin</t>
+        </is>
       </c>
       <c r="Q105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="U105" t="inlineStr"/>
@@ -28506,12 +28504,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -28519,68 +28517,47 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>n39qcIsSvY0mhj8mb0KhJHE9df0bXd</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 300000000, "_seconds": 1704369578}</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>1704369578300</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>2.10.4</t>
-        </is>
-      </c>
+          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
-        <v>5</v>
+        <v>0.96</v>
       </c>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="b">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
-      </c>
-      <c r="Q106" t="b">
-        <v>1</v>
-      </c>
+          <t>Calcium Chloride</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Mash</t>
         </is>
       </c>
       <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
       <c r="AA106" t="inlineStr"/>
@@ -28605,7 +28582,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -28613,14 +28590,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>0.96</v>
+        <v>10</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Calcium Chloride</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr"/>
@@ -28667,7 +28644,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
+          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -28675,14 +28652,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>10</v>
+        <v>17.64</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Gypsum (Calcium Sulfate)</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr"/>
@@ -28729,7 +28706,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -28737,17 +28714,21 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="L109" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="L109" t="n">
+        <v>80</v>
+      </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Gypsum (Calcium Sulfate)</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr"/>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q109" t="b">
+        <v>0</v>
+      </c>
       <c r="R109" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -28755,7 +28736,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -28763,7 +28744,9 @@
           <t>Mash</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr"/>
+      <c r="U109" t="b">
+        <v>1</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
@@ -28791,7 +28774,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -28799,21 +28782,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="L110" t="n">
-        <v>80</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
-      </c>
-      <c r="Q110" t="b">
-        <v>0</v>
-      </c>
+          <t>Salt</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -28821,7 +28800,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -28829,9 +28808,7 @@
           <t>Mash</t>
         </is>
       </c>
-      <c r="U110" t="b">
-        <v>1</v>
-      </c>
+      <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
@@ -28859,7 +28836,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -28867,17 +28844,21 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L111" t="inlineStr"/>
+        <v>3.05</v>
+      </c>
+      <c r="L111" t="n">
+        <v>80</v>
+      </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Salt</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr"/>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q111" t="b">
+        <v>0</v>
+      </c>
       <c r="R111" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -28885,15 +28866,17 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr"/>
+          <t>Sparge</t>
+        </is>
+      </c>
+      <c r="U111" t="b">
+        <v>1</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
@@ -28921,7 +28904,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -28929,21 +28912,20 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L112" t="n">
-        <v>80</v>
-      </c>
+        <v>0.34</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
-      </c>
-      <c r="Q112" t="b">
-        <v>0</v>
-      </c>
+          <t>Calcium Chloride</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -28951,17 +28933,15 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Sparge</t>
-        </is>
-      </c>
-      <c r="U112" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
@@ -28989,7 +28969,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -28997,14 +28977,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
-        <v>0.34</v>
+        <v>3.62</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Calcium Chloride</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -29054,7 +29034,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
+          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -29062,14 +29042,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="n">
-        <v>3.62</v>
+        <v>6.4</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Gypsum (Calcium Sulfate)</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -29119,7 +29099,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
+          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -29127,14 +29107,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="n">
-        <v>6.4</v>
+        <v>1.06</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Gypsum (Calcium Sulfate)</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -29184,7 +29164,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
+          <t>new-TUfxqCta0ITj3uHT8vfAbVIfLtzqyA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -29192,28 +29172,28 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
-        <v>1.06</v>
+        <v>2</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Protafloc</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>tbsp</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -29249,7 +29229,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>new-TUfxqCta0ITj3uHT8vfAbVIfLtzqyA</t>
+          <t>new-Xe5CxkyeaTwnbVay8pIU6ai8XycVKB</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -29264,7 +29244,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Protafloc</t>
+          <t>Yeast Nutrient</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -29273,12 +29253,12 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>tbsp</t>
+          <t>tsp</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -29298,12 +29278,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -29311,50 +29291,70 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>new-Xe5CxkyeaTwnbVay8pIU6ai8XycVKB</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+          <t>default-2302b0</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>1781339599069</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="K118" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="M118" t="b">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>94.5</v>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Yeast Nutrient</t>
-        </is>
-      </c>
-      <c r="P118" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q118" t="inlineStr"/>
+          <t>Baking Soda (NaHCO3)</t>
+        </is>
+      </c>
+      <c r="Q118" t="b">
+        <v>0</v>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>tsp</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U118" t="b">
+        <v>1</v>
+      </c>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
       <c r="AA118" t="inlineStr"/>
@@ -29378,26 +29378,26 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>default-2302b0</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1781339599069</v>
+        <v>1781339598782</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -29405,18 +29405,17 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L119" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="M119" t="b">
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>94.5</v>
+        <v>44</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Baking Soda (NaHCO3)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q119" t="b">
@@ -29463,44 +29462,45 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-4e9d62</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1781339598782</v>
+        <v>1704369577229</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K120" t="n">
         <v>2</v>
       </c>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="b">
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="Q120" t="b">
@@ -29524,6 +29524,9 @@
       <c r="U120" t="b">
         <v>1</v>
       </c>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
       <c r="AA120" t="inlineStr"/>
@@ -29547,45 +29550,45 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>default-4e9d62</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1704369577229</v>
+        <v>1781339597373</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="b">
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>941.2</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q121" t="b">
@@ -29609,9 +29612,6 @@
       <c r="U121" t="b">
         <v>1</v>
       </c>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr"/>
@@ -29635,26 +29635,26 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1781339597373</v>
+        <v>1781339599470</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -29662,18 +29662,20 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>3</v>
-      </c>
-      <c r="L122" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L122" t="n">
+        <v>80</v>
+      </c>
       <c r="M122" t="b">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>941.2</v>
+        <v>342.5</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
       <c r="Q122" t="b">
@@ -29686,7 +29688,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
@@ -29720,26 +29722,26 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1781339599470</v>
+        <v>1781339600221</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -29747,43 +29749,42 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L123" t="n">
-        <v>80</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="b">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>342.5</v>
+        <v>33</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>15</v>
       </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U123" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
       <c r="AA123" t="inlineStr"/>
@@ -29807,26 +29808,26 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
+          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
+          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1781339600221</v>
+        <v>1778997170065</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -29841,22 +29842,22 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -29875,94 +29876,8 @@
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr"/>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Saison</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Misc</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>default-5adf6e</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
-        </is>
-      </c>
-      <c r="I125" t="n">
-        <v>1778997170065</v>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="K125" t="n">
-        <v>5</v>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="b">
-        <v>0</v>
-      </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P125" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q125" t="b">
-        <v>0</v>
-      </c>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
-      <c r="AB125" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AB125"/>
+  <autoFilter ref="A1:AB124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -14,11 +14,11 @@
     <sheet name="Misc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AO$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1900,8 +1900,75 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>American Pale Ale</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>All Grain</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ernst Gouws</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1.044619325</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Repitch yeast
+Spund after 4 days
+Ferment on the cooler side 
+Not sure of the app's fg of 1.006 is realistic</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P22"/>
+  <autoFilter ref="A1:P23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1912,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT80"/>
+  <dimension ref="A1:AT81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10490,8 +10557,110 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1785061181508</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X81" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>Swaen Pilsner</t>
+        </is>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH81" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT80"/>
+  <autoFilter ref="A1:AT81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10502,7 +10671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO67"/>
+  <dimension ref="A1:AP71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10534,7 +10703,7 @@
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="53" customWidth="1" min="33" max="33"/>
@@ -10546,6 +10715,7 @@
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10752,6 +10922,11 @@
       <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>_editFlag</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
         </is>
       </c>
     </row>
@@ -10839,6 +11014,7 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10944,6 +11120,7 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11029,6 +11206,7 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11114,6 +11292,7 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11187,6 +11366,7 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11260,6 +11440,7 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11355,6 +11536,7 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11450,6 +11632,7 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11545,6 +11728,7 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11654,6 +11838,7 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11763,6 +11948,7 @@
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11872,6 +12058,7 @@
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11981,6 +12168,7 @@
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12090,6 +12278,7 @@
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12195,6 +12384,7 @@
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12303,6 +12493,7 @@
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12398,6 +12589,7 @@
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12483,6 +12675,7 @@
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12592,6 +12785,7 @@
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12701,6 +12895,7 @@
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12810,6 +13005,7 @@
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12919,6 +13115,7 @@
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13004,6 +13201,7 @@
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13099,6 +13297,7 @@
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13207,6 +13406,7 @@
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13316,6 +13516,7 @@
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13425,6 +13626,7 @@
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13534,6 +13736,7 @@
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13629,6 +13832,7 @@
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13724,6 +13928,7 @@
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13832,6 +14037,7 @@
       </c>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13937,6 +14143,7 @@
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -14046,6 +14253,7 @@
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14159,6 +14367,7 @@
         <v>4</v>
       </c>
       <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14268,6 +14477,7 @@
         <v>4</v>
       </c>
       <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -14353,6 +14563,7 @@
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -14462,6 +14673,7 @@
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14557,6 +14769,7 @@
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14652,6 +14865,7 @@
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14749,6 +14963,7 @@
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14844,6 +15059,7 @@
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14938,6 +15154,7 @@
       </c>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15011,6 +15228,7 @@
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15106,6 +15324,7 @@
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15214,6 +15433,7 @@
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15287,6 +15507,7 @@
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -15395,6 +15616,7 @@
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15493,6 +15715,7 @@
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -15566,6 +15789,7 @@
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15641,6 +15865,7 @@
       <c r="AL51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15716,6 +15941,7 @@
       <c r="AL52" t="inlineStr"/>
       <c r="AN52" t="inlineStr"/>
       <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15824,6 +16050,7 @@
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr"/>
       <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15897,6 +16124,7 @@
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
       <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15970,6 +16198,7 @@
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
       <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -16045,6 +16274,7 @@
       <c r="AL56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
       <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16120,6 +16350,7 @@
       <c r="AL57" t="inlineStr"/>
       <c r="AN57" t="inlineStr"/>
       <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16193,6 +16424,7 @@
       <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr"/>
       <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16266,6 +16498,7 @@
       <c r="AM59" t="inlineStr"/>
       <c r="AN59" t="inlineStr"/>
       <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -16349,6 +16582,7 @@
       <c r="AO60" t="b">
         <v>1</v>
       </c>
+      <c r="AP60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16430,6 +16664,7 @@
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -16511,6 +16746,7 @@
       <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16592,6 +16828,7 @@
       <c r="AM63" t="inlineStr"/>
       <c r="AN63" t="inlineStr"/>
       <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16680,6 +16917,7 @@
       <c r="AO64" t="b">
         <v>1</v>
       </c>
+      <c r="AP64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -16797,6 +17035,7 @@
       <c r="AM65" t="inlineStr"/>
       <c r="AN65" t="inlineStr"/>
       <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16905,6 +17144,7 @@
       <c r="AM66" t="inlineStr"/>
       <c r="AN66" t="inlineStr"/>
       <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17022,9 +17262,428 @@
       <c r="AM67" t="inlineStr"/>
       <c r="AN67" t="inlineStr"/>
       <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>10</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="S69" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>25</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="S70" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>40</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="S71" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Y71" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="n">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO67"/>
+  <autoFilter ref="A1:AP71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17035,7 +17694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL22"/>
+  <dimension ref="A1:AL23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -19520,8 +20179,131 @@
         <v>1</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Yeast</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>default-qytQJkV9cQwX6g1aZ4Carqa9z0LXeE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>250</v>
+      </c>
+      <c r="H23" t="n">
+        <v>80</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Medium-Low</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>WHC Lab</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>13</v>
+      </c>
+      <c r="R23" t="n">
+        <v>80</v>
+      </c>
+      <c r="S23" t="n">
+        <v>22</v>
+      </c>
+      <c r="T23" t="n">
+        <v>76</v>
+      </c>
+      <c r="U23" t="n">
+        <v>18</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Clean West Coast IPA</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>LAX</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Repitch</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 443000000, "_seconds": 1784057955}</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>7L5ixnuXBXaqmTBXyQnlfKg5wkjOhb</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 72000000, "_seconds": 1785061190}</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1785061190072</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL22"/>
+  <autoFilter ref="A1:AL23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19532,7 +20314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB124"/>
+  <dimension ref="A1:AB129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -29876,8 +30658,436 @@
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>default-3b1827</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1785061186542</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>2</v>
+      </c>
+      <c r="M125" t="b">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Calcium Chloride (CaCl2)</t>
+        </is>
+      </c>
+      <c r="Q125" t="b">
+        <v>0</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U125" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>default-1f88df</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>1785061185868</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>3</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="b">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>936.7</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Gypsum (CaSO4)</t>
+        </is>
+      </c>
+      <c r="Q126" t="b">
+        <v>0</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U126" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>1785061187167</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>2</v>
+      </c>
+      <c r="L127" t="n">
+        <v>80</v>
+      </c>
+      <c r="M127" t="b">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q127" t="b">
+        <v>0</v>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U127" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr"/>
+      <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>default-yn1j28sf</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>1781339600221</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="b">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>33</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q128" t="b">
+        <v>0</v>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr"/>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>default-5adf6e</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>hBAibaPvX0FHQT9ll1gxER4gHbbxIg</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1785061187}</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>1785061187983</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="b">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q129" t="b">
+        <v>0</v>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Fining</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB124"/>
+  <autoFilter ref="A1:AB129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$129</definedName>
   </definedNames>
@@ -766,19 +766,19 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.046627194</v>
+        <v>1.045320964</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1.008</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5.12</v>
+        <v>4.86</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>28.7</v>
+        <v>30.1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>12</v>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1.04757289</v>
+        <v>1.047747656</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>1.005</v>
@@ -1874,10 +1874,10 @@
         <v>5.64</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>25.2</v>
+        <v>24.5</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>12</v>
@@ -1935,13 +1935,13 @@
         <v>1.044619325</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.009</v>
+        <v>1.007</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.73</v>
+        <v>4.99</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>3.4</v>
@@ -1979,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT81"/>
+  <dimension ref="A1:AT83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3328,7 +3328,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
         <v>1.9</v>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>79.37</v>
+        <v>74.92</v>
       </c>
       <c r="AI12" t="n">
         <v>1.0368</v>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="Q13" t="n">
         <v>5.1</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>19.05</v>
+        <v>14.66</v>
       </c>
       <c r="AI13" t="n">
         <v>1.03588</v>
@@ -3500,102 +3500,96 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
+          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
+          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1778997166131</v>
+        <v>1785061180905</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.5228426</v>
+        <v>6.6</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>80</v>
+      </c>
+      <c r="V14" t="n">
+        <v>80</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X14" t="b">
         <v>0</v>
       </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>15</v>
+        <v>2.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Dextrin Malt</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>Used to provide extra body to beer and to improve head retention</t>
-        </is>
-      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>1.59</v>
+        <v>6.51</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
       <c r="AJ14" t="n">
-        <v>80</v>
+        <v>75.37</v>
       </c>
       <c r="AK14" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -3613,12 +3607,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
+          <t>AlNro2l8joSt8O98vSwLNZqS08yafE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>London Pub Gen 2 Amber Ale</t>
+          <t>Nog 'n lager</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3628,37 +3622,47 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
+          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1721546982716</v>
+        <v>1778997166131</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>0.12</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1.5228426</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -3668,33 +3672,52 @@
       <c r="X15" t="b">
         <v>0</v>
       </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
       <c r="Z15" t="n">
-        <v>-2.59</v>
+        <v>0.9</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Dextrin Malt</t>
         </is>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Used to provide extra body to beer and to improve head retention</t>
+        </is>
+      </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>74.84999999999999</v>
+        <v>3.91</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.036</v>
+        <v>1.037</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>10</v>
       </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -3725,84 +3748,75 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>default-60a8af8</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>default-sabmjufsad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1721546982716</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
       <c r="Q16" t="n">
-        <v>7.614213</v>
-      </c>
-      <c r="S16" t="n">
-        <v>50</v>
-      </c>
-      <c r="U16" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X16" t="b">
         <v>0</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.5</v>
+      <c r="Z16" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Munich I</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
-        </is>
-      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>14.97</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Amber Liquid Extract</t>
-        </is>
-      </c>
+        <v>1.036</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -3812,9 +3826,7 @@
       </c>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
@@ -3838,34 +3850,29 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>default-aaaccad</t>
+          <t>default-60a8af8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>7.614213</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="U17" t="n">
+        <v>78</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X17" t="b">
@@ -3875,14 +3882,14 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Carahell</t>
+          <t>Munich I</t>
         </is>
       </c>
       <c r="AE17" t="b">
@@ -3890,7 +3897,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -3899,18 +3906,22 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>5.99</v>
+        <v>14.97</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.035</v>
+        <v>1.038</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.73999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Amber Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM17" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -3923,7 +3934,9 @@
       </c>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
@@ -3947,7 +3960,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>default-741be46</t>
+          <t>default-aaaccad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -3958,14 +3971,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.15</v>
+      </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3982,14 +3997,14 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Caramunich II</t>
+          <t>Carahell</t>
         </is>
       </c>
       <c r="AE18" t="b">
@@ -3997,7 +4012,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>German crystal malt. Adds maltiness, aroma, color.</t>
+          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -4006,7 +4021,7 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
       <c r="AI18" t="n">
         <v>1.035</v>
@@ -4054,7 +4069,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-741be46</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -4065,23 +4080,21 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.05</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>558.375635</v>
+        <v>63</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X19" t="b">
@@ -4091,14 +4104,14 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Caramunich II</t>
         </is>
       </c>
       <c r="AE19" t="b">
@@ -4106,7 +4119,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>German crystal malt. Adds maltiness, aroma, color.</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -4115,16 +4128,16 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>2.99</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="AJ19" t="n">
-        <v>77.90000000000001</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="AK19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr">
@@ -4139,9 +4152,7 @@
       </c>
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
@@ -4149,12 +4160,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
+          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rice beer</t>
+          <t>London Pub Gen 2 Amber Ale</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4162,78 +4173,85 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1778997165061</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
+          <t>default-b5ffdd1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0.04</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.9</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X20" t="b">
         <v>0</v>
       </c>
-      <c r="Z20" t="n">
-        <v>7.7</v>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>64.52</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ20" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>10</v>
       </c>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -4243,7 +4261,9 @@
       </c>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
+      <c r="AQ20" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
@@ -4264,31 +4284,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>default-7c1aab5</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1778997165061</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="L21" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.7</v>
+      </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Rice, Flaked</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE21" t="b">
@@ -4297,20 +4340,24 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>24.19</v>
+        <v>64.52</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.0322</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ21" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN21" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -4339,54 +4386,31 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1776345923984</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
-      </c>
+          <t>default-7c1aab5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.45</v>
-      </c>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Rice, Flaked</t>
         </is>
       </c>
       <c r="AE22" t="b">
@@ -4395,24 +4419,20 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>8.06</v>
+        <v>24.19</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.03588</v>
+        <v>1.0322</v>
       </c>
       <c r="AJ22" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
+      <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -4443,102 +4463,76 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
+          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1778997166131</v>
+        <v>1776345923984</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+          <t>3.0.0</t>
+        </is>
       </c>
       <c r="L23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.5228426</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X23" t="b">
         <v>0</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
       <c r="Z23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Dextrin Malt</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>Used to provide extra body to beer and to improve head retention</t>
-        </is>
-      </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>3.23</v>
+        <v>8.06</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.037</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -4556,12 +4550,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
+          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kolserig</t>
+          <t>Rice beer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4569,55 +4563,104 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1778997166131</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" t="n">
-        <v>2.83</v>
+        <v>0.1</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>1.5228426</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7</v>
+      </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Dextrin Malt</t>
         </is>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Used to provide extra body to beer and to improve head retention</t>
+        </is>
+      </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>81.56</v>
+        <v>3.23</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.0368</v>
+        <v>1.037</v>
       </c>
       <c r="AJ24" t="n">
         <v>80</v>
       </c>
+      <c r="AK24" t="n">
+        <v>10</v>
+      </c>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -4651,7 +4694,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -4659,20 +4702,20 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.64</v>
+        <v>2.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE25" t="b">
@@ -4685,13 +4728,13 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>18.44</v>
+        <v>81.56</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ25" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr">
@@ -4714,12 +4757,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
+          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>London Pub Gen 1 Stout saved by Bond</t>
+          <t>Kolserig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4727,104 +4770,55 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>default-e6ba5b8</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1721546982714</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>1.5</v>
+        <v>0.64</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2994924</v>
-      </c>
-      <c r="S26" t="n">
-        <v>53</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
-        </is>
-      </c>
-      <c r="X26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>-4.59</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.5</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Finest Maris Otter® Ale Malt</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
-        </is>
-      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>66.89</v>
+        <v>18.44</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.038</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ26" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -4857,53 +4851,51 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 429000000, "_seconds": 1697269073}</t>
+          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>default-1f44c9e</t>
+          <t>default-e6ba5b8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>F1TM4o4Xs8cgfF95wPoLjkPxbCpQ9w</t>
+          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 155000000, "_seconds": 1704369569}</t>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1704369569155</v>
+        <v>1721546982714</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.87</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.7</v>
+        <v>3.2994924</v>
       </c>
       <c r="S27" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base (Maris Otter)</t>
         </is>
       </c>
       <c r="X27" t="b">
@@ -4913,17 +4905,17 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>-4.59</v>
       </c>
       <c r="AB27" t="n">
         <v>100</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Pilsner</t>
+          <t>Finest Maris Otter® Ale Malt</t>
         </is>
       </c>
       <c r="AE27" t="b">
@@ -4931,34 +4923,30 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Pilsner base malt for all pilsners, lagers. Highly modified malt.</t>
+          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>16.72</v>
+        <v>66.89</v>
       </c>
       <c r="AI27" t="n">
         <v>1.038</v>
       </c>
       <c r="AJ27" t="n">
-        <v>82.23</v>
+        <v>81.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Pilsner Liquid Extract</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -4989,35 +4977,55 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 429000000, "_seconds": 1697269073}</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>default-1f44c9e</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>F1TM4o4Xs8cgfF95wPoLjkPxbCpQ9w</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 155000000, "_seconds": 1704369569}</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1704369569155</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2.10.4</t>
+        </is>
+      </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.87</v>
+      </c>
       <c r="P28" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>558.375635</v>
+        <v>1.7</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X28" t="b">
@@ -5026,15 +5034,18 @@
       <c r="Y28" t="n">
         <v>0</v>
       </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
       <c r="AB28" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="AC28" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Pilsner</t>
         </is>
       </c>
       <c r="AE28" t="b">
@@ -5042,7 +5053,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>Pilsner base malt for all pilsners, lagers. Highly modified malt.</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -5051,18 +5062,22 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>7.36</v>
+        <v>16.72</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.036</v>
+        <v>1.038</v>
       </c>
       <c r="AJ28" t="n">
-        <v>77.90000000000001</v>
+        <v>82.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL28" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Pilsner Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM28" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -5075,9 +5090,7 @@
       </c>
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr"/>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr"/>
@@ -5101,7 +5114,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>default-741be46</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -5112,21 +5125,21 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>63</v>
+        <v>558.375635</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X29" t="b">
@@ -5136,40 +5149,40 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Carafa Special II</t>
+        </is>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK29" t="n">
         <v>10</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Caramunich II</t>
-        </is>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>German crystal malt. Adds maltiness, aroma, color.</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>75.73999999999999</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
       </c>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr">
@@ -5184,7 +5197,9 @@
       </c>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
+      <c r="AQ29" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr"/>
@@ -5208,52 +5223,80 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>default-d2c0778</t>
+          <t>default-741be46</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" t="n">
         <v>0.1</v>
       </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="n">
-        <v>1.4</v>
+        <v>63</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.6</v>
+      </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Oats, Flaked</t>
+          <t>Caramunich II</t>
         </is>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>German crystal malt. Adds maltiness, aroma, color.</t>
+        </is>
+      </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH30" t="n">
         <v>3.34</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.0391</v>
+        <v>1.035</v>
       </c>
       <c r="AJ30" t="n">
-        <v>85</v>
+        <v>75.73999999999999</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
       </c>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Briess</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -5287,80 +5330,52 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>default-fc0f80b</t>
+          <t>default-d2c0778</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>415</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Roasted</t>
-        </is>
-      </c>
-      <c r="X31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.1</v>
-      </c>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Carafa II</t>
+          <t>Oats, Flaked</t>
         </is>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>Chocolate malt. Dark beers, Alts, Bockbiers. Adds color and aroma.</t>
-        </is>
-      </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>2.34</v>
+        <v>3.34</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.036</v>
+        <v>1.0391</v>
       </c>
       <c r="AJ31" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Briess</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -5378,12 +5393,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
+          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Marigold Lager</t>
+          <t>London Pub Gen 1 Stout saved by Bond</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5394,52 +5409,80 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-fc0f80b</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.9</v>
+        <v>415</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.1</v>
+      </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa II</t>
         </is>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Chocolate malt. Dark beers, Alts, Bockbiers. Adds color and aroma.</t>
+        </is>
+      </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>100</v>
+        <v>2.34</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ32" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>10</v>
       </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -5457,12 +5500,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
+          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Marigold Lager</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5470,36 +5513,18 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>default-c3ff8bb88f9</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1778997165061</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>1.9</v>
@@ -5509,12 +5534,7 @@
           <t>Base (Pilsner)</t>
         </is>
       </c>
-      <c r="X33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="X33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
           <t>Swaen Pilsner</t>
@@ -5530,7 +5550,7 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>26.25</v>
+        <v>100</v>
       </c>
       <c r="AI33" t="n">
         <v>1.0368</v>
@@ -5574,69 +5594,52 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jr8QUoFHfyKXPhn1IjtiaA3GZwRjfZ</t>
+          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 385000000, "_seconds": 1777108191}</t>
+          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1777108191385</v>
+        <v>1778997165061</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="P34" t="n">
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S34" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>80</v>
-      </c>
-      <c r="V34" t="n">
-        <v>80</v>
+        <v>1.9</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X34" t="b">
         <v>0</v>
       </c>
-      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE34" t="b">
@@ -5649,16 +5652,13 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>15.75</v>
+        <v>26.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.035</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ34" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>11.7</v>
+        <v>80</v>
       </c>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr">
@@ -5696,26 +5696,26 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+          <t>Jr8QUoFHfyKXPhn1IjtiaA3GZwRjfZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+          <t>{"_nanoseconds": 385000000, "_seconds": 1777108191}</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1776345923984</v>
+        <v>1777108191385</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -5725,23 +5725,40 @@
       <c r="L35" t="n">
         <v>0.6</v>
       </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Q35" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>80</v>
+      </c>
+      <c r="V35" t="n">
+        <v>80</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X35" t="b">
         <v>0</v>
       </c>
+      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE35" t="b">
@@ -5757,10 +5774,13 @@
         <v>15.75</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.03588</v>
+        <v>1.035</v>
       </c>
       <c r="AJ35" t="n">
-        <v>78</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr">
@@ -5796,83 +5816,78 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>default-96t8Xs5OLBpW9y5feB0tUbwyNtbfO4</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1776345923984</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
       </c>
       <c r="L36" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.5380711</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X36" t="b">
         <v>0</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>11</v>
+      <c r="Z36" t="n">
+        <v>3.45</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Flaked Torrefied Oats</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
-        </is>
-      </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>12.6</v>
+        <v>15.75</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.032</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ36" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -5903,52 +5918,31 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>default-0aa30343c0c</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>JLLnm9cGPVv3337nwYsF4XU4bmE8yr</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 206000000, "_seconds": 1776345941}</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1776345941206</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
+          <t>default-96t8Xs5OLBpW9y5feB0tUbwyNtbfO4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>2.5380711</v>
       </c>
       <c r="S37" t="n">
-        <v>76</v>
-      </c>
-      <c r="U37" t="n">
-        <v>81</v>
-      </c>
-      <c r="V37" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -5958,19 +5952,18 @@
       <c r="X37" t="b">
         <v>0</v>
       </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="n">
-        <v>4</v>
+      <c r="Y37" t="n">
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Swaen Ale</t>
+          <t>Flaked Torrefied Oats</t>
         </is>
       </c>
       <c r="AE37" t="b">
@@ -5978,30 +5971,30 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>10.5</v>
+        <v>12.6</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.037</v>
+        <v>1.032</v>
       </c>
       <c r="AJ37" t="n">
-        <v>80.13</v>
+        <v>70</v>
       </c>
       <c r="AK37" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -6034,26 +6027,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
+          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>default-29dda1b5335</t>
+          <t>default-0aa30343c0c</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bvta1UbScHCOHOL3y0bkomTlBk4ToI</t>
+          <t>JLLnm9cGPVv3337nwYsF4XU4bmE8yr</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 566000000, "_seconds": 1776346236}</t>
+          <t>{"_nanoseconds": 206000000, "_seconds": 1776345941}</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1776346236566</v>
+        <v>1776345941206</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -6061,44 +6054,71 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>329.949239</v>
+        <v>3.6</v>
+      </c>
+      <c r="S38" t="n">
+        <v>76</v>
+      </c>
+      <c r="U38" t="n">
+        <v>81</v>
+      </c>
+      <c r="V38" t="n">
+        <v>80</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X38" t="b">
         <v>0</v>
       </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>BlackSwaen Coffee</t>
+          <t>Swaen Ale</t>
         </is>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
+        </is>
+      </c>
       <c r="AG38" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>9.19</v>
+        <v>10.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.028</v>
+        <v>1.037</v>
       </c>
       <c r="AJ38" t="n">
-        <v>60.8695652</v>
+        <v>80.13</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>11.5</v>
       </c>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr">
@@ -6113,9 +6133,7 @@
       </c>
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="n">
-        <v>244.1</v>
-      </c>
+      <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr"/>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr"/>
@@ -6138,26 +6156,26 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-29dda1b5335</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>bvta1UbScHCOHOL3y0bkomTlBk4ToI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 566000000, "_seconds": 1776346236}</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1776345994305</v>
+        <v>1776346236566</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -6165,48 +6183,44 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="Q39" t="n">
-        <v>61</v>
+        <v>329.949239</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X39" t="b">
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>BlackSwaen Coffee</t>
         </is>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>7.35</v>
+        <v>9.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.034</v>
+        <v>1.028</v>
       </c>
       <c r="AJ39" t="n">
-        <v>73.9130435</v>
+        <v>60.8695652</v>
       </c>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr">
@@ -6221,7 +6235,9 @@
       </c>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
+      <c r="AQ39" t="n">
+        <v>244.1</v>
+      </c>
       <c r="AR39" t="inlineStr"/>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
@@ -6244,71 +6260,52 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>jWuqIkMLK24jzylCQapUkVKL5iFO6T</t>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 551000000, "_seconds": 1777108193}</t>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1777108193551</v>
+        <v>1776345994305</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>3.0.0</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>1.5</v>
+        <v>0.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X40" t="b">
         <v>0</v>
       </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
       <c r="Z40" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE40" t="b">
@@ -6316,30 +6313,27 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>2.62</v>
+        <v>7.35</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.036</v>
+        <v>1.034</v>
       </c>
       <c r="AJ40" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>10</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -6349,9 +6343,7 @@
       </c>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="inlineStr"/>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr"/>
@@ -6374,30 +6366,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 546000000, "_seconds": 1712314605}</t>
+          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>default-Q0GFlvnA7LLqVkkfYBAXCniMcRZwnf</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>7aV7RCW73FffCIp6YwXe3Ui8TTLeJE</t>
+          <t>jWuqIkMLK24jzylCQapUkVKL5iFO6T</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 122000000, "_seconds": 1778682369}</t>
+          <t>{"_nanoseconds": 551000000, "_seconds": 1777108193}</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1778682369122</v>
+        <v>1777108193551</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -6408,17 +6400,17 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.8</v>
+        <v>558.375635</v>
       </c>
       <c r="S41" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X41" t="b">
@@ -6428,17 +6420,17 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AB41" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Malteurop Pilsen</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE41" t="b">
@@ -6446,30 +6438,30 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>The lightest of our two-row base malts, Malteurop Pilsen malt imparts a sweet and subtle malt flavor and a straw yellow to light golden color. It can be used up to 100% in all beer styles and provides a perfect canvas for other specialty malts.</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.038</v>
+        <v>1.036</v>
       </c>
       <c r="AJ41" t="n">
-        <v>81.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK41" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Malteurop Malting Co.</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -6479,22 +6471,22 @@
       </c>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="b">
-        <v>1</v>
-      </c>
+      <c r="AQ41" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
+          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lager pseudo idea ii</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6504,79 +6496,102 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+          <t>{"_nanoseconds": 546000000, "_seconds": 1712314605}</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
+          <t>default-Q0GFlvnA7LLqVkkfYBAXCniMcRZwnf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+          <t>7aV7RCW73FffCIp6YwXe3Ui8TTLeJE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 122000000, "_seconds": 1778682369}</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1721546982716</v>
+        <v>1778682369122</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="P42" t="n">
         <v>0.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1.8</v>
+      </c>
+      <c r="S42" t="n">
+        <v>146</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X42" t="b">
         <v>0</v>
       </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
       <c r="Z42" t="n">
-        <v>-2.59</v>
+        <v>1</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.4</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Malteurop Pilsen</t>
         </is>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>The lightest of our two-row base malts, Malteurop Pilsen malt imparts a sweet and subtle malt flavor and a straw yellow to light golden color. It can be used up to 100% in all beer styles and provides a perfect canvas for other specialty malts.</t>
+        </is>
+      </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>92.59</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.035</v>
+        <v>1.038</v>
       </c>
       <c r="AJ42" t="n">
-        <v>76</v>
+        <v>81.7</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>11.3</v>
       </c>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Malteurop Malting Co.</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -6587,7 +6602,9 @@
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
+      <c r="AR42" t="b">
+        <v>1</v>
+      </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
     </row>
@@ -6607,89 +6624,81 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>default-cdbfbd6</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>0</v>
+          <t>default-sabmjufsad</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1721546982716</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
       </c>
       <c r="L43" t="n">
-        <v>0.14</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>30</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X43" t="b">
         <v>0</v>
       </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.8</v>
+      <c r="Z43" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Melanoidin</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
-        </is>
-      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>4.32</v>
+        <v>92.59</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
       <c r="AJ43" t="n">
-        <v>80.06999999999999</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Carared</t>
-        </is>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
@@ -6723,50 +6732,88 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>default-08f456e</t>
+          <t>default-cdbfbd6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Oats, Flaked</t>
+          <t>Melanoidin</t>
         </is>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
+        </is>
+      </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>3.09</v>
+        <v>4.32</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.0368</v>
+        <v>1.037</v>
       </c>
       <c r="AJ44" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
+        <v>80.06999999999999</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Carared</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Weyermann</t>
+        </is>
+      </c>
       <c r="AN44" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -6782,12 +6829,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>First Lager v3</t>
+          <t>Lager pseudo idea ii</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6798,7 +6845,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>default-kTJTLZIhyeFDXlOIOLxrPWfGnU8z4A</t>
+          <t>default-08f456e</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -6806,45 +6853,120 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="L45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Oats, Flaked</t>
+        </is>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AH45" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>First Lager v3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>default-kTJTLZIhyeFDXlOIOLxrPWfGnU8z4A</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="L46" t="n">
         <v>2</v>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="P45" t="n">
+      <c r="M46" t="inlineStr"/>
+      <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q46" t="n">
         <v>1.9</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U46" t="n">
         <v>80</v>
       </c>
-      <c r="V45" t="n">
+      <c r="V46" t="n">
         <v>82</v>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Base (Pilsner)</t>
         </is>
       </c>
-      <c r="X45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="AB45" t="n">
+      <c r="X46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="AB46" t="n">
         <v>100</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AC46" t="n">
         <v>5</v>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>Bohemian Pilsner</t>
         </is>
       </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>Made from the finest Bohemian malting quality barley (Barley varieties Bojos and Malz), this Pilsner malt is characterized by the typical sententious core notes of the original barley varieties.
 Sensory: nutty malt aroma, malty-sweet
@@ -6853,160 +6975,47 @@
 Product Sheet: https://www.weyermann.de/wp-content/uploads/2021/02/Weyermann_Bohemian_Pilsner_Malt_Specification.pdf</t>
         </is>
       </c>
-      <c r="AG45" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>Bohemia</t>
         </is>
       </c>
-      <c r="AH45" t="n">
+      <c r="AH46" t="n">
         <v>71.94</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AI46" t="n">
         <v>1.035</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AJ46" t="n">
         <v>75.05</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AK46" t="n">
         <v>10.75</v>
       </c>
-      <c r="AL45" t="inlineStr">
+      <c r="AL46" t="inlineStr">
         <is>
           <t>Weyermann Floor-Malted Bohemian Pilsner Malt</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AM46" t="inlineStr">
         <is>
           <t>Weyermann</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
+      <c r="AN46" t="inlineStr">
         <is>
           <t>Grain</t>
         </is>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>pilsners</t>
         </is>
       </c>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="n">
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="n">
         <v>1.95</v>
       </c>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>First Lager v3</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Fermentable</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>default-4d8b7c4</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>50</v>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>Vienna Malt</t>
-        </is>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>Vienna base malt - used in many continental beer styles. Full bodied, golden color.</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="AH46" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>82.23</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Weyermann</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr"/>
@@ -7030,7 +7039,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-4d8b7c4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -7041,23 +7050,23 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X47" t="b">
@@ -7067,14 +7076,14 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE47" t="b">
@@ -7082,7 +7091,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+          <t>Vienna base malt - used in many continental beer styles. Full bodied, golden color.</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -7091,18 +7100,22 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>10.07</v>
+        <v>17.99</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ47" t="n">
-        <v>80.06999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM47" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -7123,12 +7136,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>London Pub gen 2 Weskus</t>
+          <t>First Lager v3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7136,78 +7149,85 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1721546982716</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
+          <t>default-1482365</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.6</v>
+        <v>0.28</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q48" t="n">
         <v>2</v>
       </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X48" t="b">
         <v>0</v>
       </c>
-      <c r="Z48" t="n">
-        <v>-2.59</v>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>4.9</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+        </is>
+      </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>79.27</v>
+        <v>10.07</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.035</v>
+        <v>1.037</v>
       </c>
       <c r="AJ48" t="n">
-        <v>76</v>
+        <v>80.06999999999999</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
       </c>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
@@ -7240,102 +7260,76 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 248000000, "_seconds": 1714216056}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CPkrJFvR0z03f2qIouoRdQwhmALFMG</t>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 27000000, "_seconds": 1723974350}</t>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1723974350027</v>
+        <v>1721546982716</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>2.10.6</t>
         </is>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.9593909</v>
-      </c>
-      <c r="S49" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X49" t="b">
         <v>0</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
       <c r="Z49" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>4.5</v>
+        <v>-2.59</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
-        </is>
-      </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>15.24</v>
+        <v>79.27</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
       <c r="AJ49" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>9.6</v>
+        <v>76</v>
       </c>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -7366,37 +7360,53 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 248000000, "_seconds": 1714216056}</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>default-cdbfbd6</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CPkrJFvR0z03f2qIouoRdQwhmALFMG</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 27000000, "_seconds": 1723974350}</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1723974350027</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.73</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>1.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>3.9593909</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X50" t="b">
@@ -7405,15 +7415,18 @@
       <c r="Y50" t="n">
         <v>0</v>
       </c>
+      <c r="Z50" t="n">
+        <v>-3</v>
+      </c>
       <c r="AB50" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Melanoidin</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE50" t="b">
@@ -7421,34 +7434,30 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>3.96</v>
+        <v>15.24</v>
       </c>
       <c r="AI50" t="n">
         <v>1.037</v>
       </c>
       <c r="AJ50" t="n">
-        <v>80.06999999999999</v>
+        <v>80</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Carared</t>
-        </is>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
@@ -7482,7 +7491,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>default-aaaccad</t>
+          <t>default-cdbfbd6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -7493,14 +7502,16 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M51" t="inlineStr"/>
+        <v>0.13</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.73</v>
+      </c>
       <c r="P51" t="n">
         <v>1.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -7517,14 +7528,14 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Carahell</t>
+          <t>Melanoidin</t>
         </is>
       </c>
       <c r="AE51" t="b">
@@ -7532,7 +7543,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -7541,18 +7552,22 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>1.52</v>
+        <v>3.96</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.035</v>
+        <v>1.037</v>
       </c>
       <c r="AJ51" t="n">
-        <v>75.73999999999999</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AK51" t="n">
         <v>0</v>
       </c>
-      <c r="AL51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Carared</t>
+        </is>
+      </c>
       <c r="AM51" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -7573,12 +7588,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>London Pub gen 2 Weskus</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7589,52 +7604,80 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-aaaccad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" t="n">
-        <v>2.9</v>
+        <v>0.05</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.9</v>
+        <v>13</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carahell</t>
         </is>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+        </is>
+      </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>70.73</v>
+        <v>1.52</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.0368</v>
+        <v>1.035</v>
       </c>
       <c r="AJ52" t="n">
-        <v>80</v>
+        <v>75.73999999999999</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
       </c>
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
@@ -7668,7 +7711,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -7676,20 +7719,20 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X53" t="inlineStr"/>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE53" t="b">
@@ -7702,13 +7745,13 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>19.51</v>
+        <v>70.73</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ53" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr">
@@ -7747,7 +7790,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -7755,39 +7798,20 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="P54" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S54" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U54" t="n">
-        <v>80</v>
-      </c>
-      <c r="V54" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="AC54" t="n">
-        <v>4.6</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE54" t="b">
@@ -7800,16 +7824,13 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>8.539999999999999</v>
+        <v>19.51</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ54" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr">
@@ -7845,77 +7866,72 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1781339589491</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>default-c454dca637a</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S55" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>80</v>
+      </c>
+      <c r="V55" t="n">
+        <v>80</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X55" t="b">
         <v>0</v>
       </c>
-      <c r="Z55" t="n">
-        <v>1.36</v>
+      <c r="Y55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ55" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr">
@@ -7938,12 +7954,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7953,90 +7969,80 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>default-nym-3n456</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1721546982782</v>
+        <v>1781339589491</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
       <c r="Q56" t="n">
-        <v>1.77665</v>
-      </c>
-      <c r="U56" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="V56" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X56" t="b">
         <v>0</v>
       </c>
-      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Barke Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>45.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.035</v>
+        <v>1.034</v>
       </c>
       <c r="AJ56" t="n">
-        <v>76.48</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
@@ -8067,47 +8073,68 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>default-nym-3n456</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1721546982782</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>3.807107</v>
+        <v>1.77665</v>
       </c>
       <c r="U57" t="n">
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="V57" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X57" t="b">
         <v>0</v>
       </c>
       <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
       <c r="AB57" t="n">
         <v>100</v>
       </c>
       <c r="AC57" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Barke Vienna Malt</t>
+          <t>Barke Pilsner</t>
         </is>
       </c>
       <c r="AE57" t="b">
@@ -8120,16 +8147,13 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>32.26</v>
+        <v>45.16</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ57" t="n">
-        <v>74.66</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>10.5</v>
+        <v>76.48</v>
       </c>
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr">
@@ -8144,13 +8168,9 @@
       </c>
       <c r="AO57" t="inlineStr"/>
       <c r="AP57" t="inlineStr"/>
-      <c r="AQ57" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="b">
-        <v>0</v>
-      </c>
+      <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -8172,75 +8192,66 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Q58" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
+        <v>3.807107</v>
+      </c>
+      <c r="U58" t="n">
+        <v>79</v>
+      </c>
+      <c r="V58" t="n">
+        <v>80</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X58" t="b">
         <v>0</v>
       </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y58" t="inlineStr"/>
       <c r="AB58" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Barke Vienna Malt</t>
         </is>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>8.06</v>
+        <v>32.26</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.036</v>
+        <v>1.034</v>
       </c>
       <c r="AJ58" t="n">
-        <v>77.90000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="AK58" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr">
@@ -8256,10 +8267,12 @@
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
       <c r="AQ58" t="n">
-        <v>412.8</v>
+        <v>3.4</v>
       </c>
       <c r="AR58" t="inlineStr"/>
-      <c r="AS58" t="inlineStr"/>
+      <c r="AS58" t="b">
+        <v>0</v>
+      </c>
       <c r="AT58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -8281,7 +8294,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -8294,14 +8307,12 @@
       <c r="L59" t="n">
         <v>0.25</v>
       </c>
-      <c r="M59" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="P59" t="n">
         <v>1.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>558.375635</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -8318,14 +8329,14 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AC59" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE59" t="b">
@@ -8333,7 +8344,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -8345,13 +8356,13 @@
         <v>8.06</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.037</v>
+        <v>1.036</v>
       </c>
       <c r="AJ59" t="n">
-        <v>80.06999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr">
@@ -8366,7 +8377,9 @@
       </c>
       <c r="AO59" t="inlineStr"/>
       <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
+      <c r="AQ59" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR59" t="inlineStr"/>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr"/>
@@ -8390,29 +8403,34 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>default-60a8af8</t>
+          <t>default-1482365</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M60" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q60" t="n">
-        <v>7.614213</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
-      </c>
-      <c r="U60" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X60" t="b">
@@ -8422,14 +8440,14 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AC60" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Munich I</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE60" t="b">
@@ -8437,7 +8455,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
@@ -8446,22 +8464,18 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>6.45</v>
+        <v>8.06</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.038</v>
+        <v>1.037</v>
       </c>
       <c r="AJ60" t="n">
-        <v>82.3</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AK60" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Amber Liquid Extract</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -8474,9 +8488,7 @@
       </c>
       <c r="AO60" t="inlineStr"/>
       <c r="AP60" t="inlineStr"/>
-      <c r="AQ60" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr"/>
@@ -8484,12 +8496,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8500,7 +8512,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-60a8af8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -8508,44 +8520,73 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>1.9</v>
+        <v>7.614213</v>
+      </c>
+      <c r="S61" t="n">
+        <v>50</v>
+      </c>
+      <c r="U61" t="n">
+        <v>78</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
+          <t>Base (Munich)</t>
+        </is>
+      </c>
+      <c r="X61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Munich I</t>
         </is>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+        </is>
+      </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>64.09999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.0368</v>
+        <v>1.038</v>
       </c>
       <c r="AJ61" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="inlineStr"/>
+        <v>82.3</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Amber Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
@@ -8555,7 +8596,9 @@
       </c>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
-      <c r="AQ61" t="inlineStr"/>
+      <c r="AQ61" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr"/>
@@ -8579,7 +8622,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -8587,20 +8630,20 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>0.62</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE62" t="b">
@@ -8613,13 +8656,13 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>19.87</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ62" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr">
@@ -8658,7 +8701,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -8666,39 +8709,20 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="P63" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="Q63" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S63" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U63" t="n">
-        <v>80</v>
-      </c>
-      <c r="V63" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="AC63" t="n">
-        <v>4.6</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE63" t="b">
@@ -8711,16 +8735,13 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>9.619999999999999</v>
+        <v>19.87</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ63" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr">
@@ -8759,80 +8780,74 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>558.375635</v>
+        <v>6.6</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>80</v>
+      </c>
+      <c r="V64" t="n">
+        <v>80</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X64" t="b">
         <v>0</v>
       </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>5</v>
-      </c>
+      <c r="Y64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>6.41</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="AJ64" t="n">
-        <v>77.90000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="AK64" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
@@ -8842,9 +8857,7 @@
       </c>
       <c r="AO64" t="inlineStr"/>
       <c r="AP64" t="inlineStr"/>
-      <c r="AQ64" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ64" t="inlineStr"/>
       <c r="AR64" t="inlineStr"/>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr"/>
@@ -8852,12 +8865,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8865,78 +8878,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>1777108192684</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
+          <t>default-b5ffdd1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.9</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X65" t="b">
         <v>0</v>
       </c>
-      <c r="Z65" t="n">
-        <v>7.8</v>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>3</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>73.95999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ65" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>10</v>
       </c>
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
@@ -8946,10 +8964,10 @@
       </c>
       <c r="AO65" t="inlineStr"/>
       <c r="AP65" t="inlineStr"/>
-      <c r="AQ65" t="inlineStr"/>
-      <c r="AR65" t="b">
-        <v>0</v>
-      </c>
+      <c r="AQ65" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr"/>
     </row>
@@ -8971,52 +8989,52 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1781339591852</v>
+        <v>1777108192684</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X66" t="b">
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.85</v>
+        <v>7.8</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE66" t="b">
@@ -9029,13 +9047,13 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>14.79</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ66" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr">
@@ -9051,7 +9069,9 @@
       <c r="AO66" t="inlineStr"/>
       <c r="AP66" t="inlineStr"/>
       <c r="AQ66" t="inlineStr"/>
-      <c r="AR66" t="inlineStr"/>
+      <c r="AR66" t="b">
+        <v>0</v>
+      </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr"/>
     </row>
@@ -9073,26 +9093,26 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -9100,42 +9120,25 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="P67" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S67" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U67" t="n">
-        <v>80</v>
-      </c>
-      <c r="V67" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X67" t="b">
         <v>0</v>
       </c>
-      <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE67" t="b">
@@ -9148,16 +9151,13 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>8.880000000000001</v>
+        <v>14.79</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ67" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
@@ -9195,75 +9195,91 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1776345994305</v>
+        <v>1781339591050</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S68" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>80</v>
+      </c>
+      <c r="V68" t="n">
+        <v>80</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X68" t="b">
         <v>0</v>
       </c>
+      <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>2</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>2.37</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ68" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr">
@@ -9286,12 +9302,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9301,71 +9317,75 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1781339591476</v>
+        <v>1776345994305</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.3</v>
+        <v>0.08</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.9</v>
+        <v>61</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X69" t="b">
         <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG69" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>73.02</v>
+        <v>2.37</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.0368</v>
+        <v>1.034</v>
       </c>
       <c r="AJ69" t="n">
-        <v>80</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr">
@@ -9403,26 +9423,26 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -9430,25 +9450,25 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X70" t="b">
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE70" t="b">
@@ -9461,13 +9481,13 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>14.29</v>
+        <v>73.02</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ70" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr">
@@ -9505,26 +9525,26 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -9532,42 +9552,25 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="P71" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="Q71" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S71" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U71" t="n">
-        <v>80</v>
-      </c>
-      <c r="V71" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X71" t="b">
         <v>0</v>
       </c>
-      <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE71" t="b">
@@ -9580,16 +9583,13 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ71" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr">
@@ -9627,26 +9627,26 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1781339589491</v>
+        <v>1781339591050</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -9654,48 +9654,64 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S72" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>80</v>
+      </c>
+      <c r="V72" t="n">
+        <v>80</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X72" t="b">
         <v>0</v>
       </c>
+      <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>1.36</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>1.59</v>
+        <v>11.11</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ72" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr">
@@ -9718,12 +9734,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9731,52 +9747,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="n">
-        <v>0</v>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1781339589491</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L73" t="n">
-        <v>3</v>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="P73" t="n">
-        <v>1.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.8527919</v>
-      </c>
-      <c r="S73" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X73" t="b">
         <v>0</v>
       </c>
-      <c r="Y73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>4.5</v>
+      <c r="Z73" t="n">
+        <v>1.36</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® Extra Pale</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE73" t="b">
@@ -9784,30 +9802,27 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>68.18000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.038</v>
+        <v>1.034</v>
       </c>
       <c r="AJ73" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK73" t="n">
-        <v>10.1</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
@@ -9841,7 +9856,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -9852,21 +9867,21 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="P74" t="n">
         <v>1.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.9593909</v>
+        <v>1.8527919</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X74" t="b">
@@ -9883,7 +9898,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Clear Choice Malt ® Extra Pale</t>
         </is>
       </c>
       <c r="AE74" t="b">
@@ -9891,7 +9906,7 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
@@ -9900,16 +9915,16 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>22.73</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ74" t="n">
-        <v>80</v>
+        <v>81.5</v>
       </c>
       <c r="AK74" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr">
@@ -9945,75 +9960,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>1706434202728</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2.10.5</t>
-        </is>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>3.9593909</v>
+      </c>
+      <c r="S75" t="n">
+        <v>50</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X75" t="b">
         <v>0</v>
       </c>
-      <c r="Z75" t="n">
-        <v>-2.29</v>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+        </is>
+      </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>6.82</v>
+        <v>22.73</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.036</v>
+        <v>1.037</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>9.6</v>
       </c>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
@@ -10024,9 +10047,7 @@
       <c r="AO75" t="inlineStr"/>
       <c r="AP75" t="inlineStr"/>
       <c r="AQ75" t="inlineStr"/>
-      <c r="AR75" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR75" t="inlineStr"/>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr"/>
     </row>
@@ -10048,108 +10069,73 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>default-4c1345c</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1712314604140</v>
+        <v>1706434202728</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
+          <t>2.10.5</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q76" t="n">
         <v>2</v>
       </c>
-      <c r="L76" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X76" t="b">
         <v>0</v>
       </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
       <c r="Z76" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>4</v>
+        <v>-2.29</v>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
-        </is>
-      </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>2.27</v>
+        <v>6.82</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
+        <v>1.036</v>
+      </c>
+      <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
@@ -10160,19 +10146,21 @@
       <c r="AO76" t="inlineStr"/>
       <c r="AP76" t="inlineStr"/>
       <c r="AQ76" t="inlineStr"/>
-      <c r="AR76" t="inlineStr"/>
+      <c r="AR76" t="b">
+        <v>0</v>
+      </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10180,69 +10168,110 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>default-4c1345c</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1712314604140</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>2</v>
+      </c>
       <c r="L77" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q77" t="n">
-        <v>3</v>
-      </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="X77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>4</v>
+      </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Pale Malt, Maris Otter</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
+        </is>
+      </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>100</v>
+        <v>2.27</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.03795</v>
+        <v>1.03</v>
       </c>
       <c r="AJ77" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
+        <v>65.2</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Maris Otter</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -10255,21 +10284,17 @@
       <c r="AQ77" t="inlineStr"/>
       <c r="AR77" t="inlineStr"/>
       <c r="AS77" t="inlineStr"/>
-      <c r="AT77" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="AT77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10277,78 +10302,69 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>1781339591476</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="n">
-        <v>2.5</v>
-      </c>
+        <v>13.18</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
-        <v>1.9</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X78" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>6.7</v>
-      </c>
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
-        </is>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
+          <t>Pale Malt, Maris Otter</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>81.97</v>
+        <v>100</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.0368</v>
+        <v>1.03795</v>
       </c>
       <c r="AJ78" t="n">
-        <v>80</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Maris Otter</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
@@ -10361,7 +10377,11 @@
       <c r="AQ78" t="inlineStr"/>
       <c r="AR78" t="inlineStr"/>
       <c r="AS78" t="inlineStr"/>
-      <c r="AT78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10381,26 +10401,26 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -10408,25 +10428,25 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X79" t="b">
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE79" t="b">
@@ -10439,13 +10459,13 @@
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>11.48</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ79" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="inlineStr">
@@ -10483,71 +10503,81 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>default-132c22b</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1772634460383</v>
+        <v>1781339591852</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M80" t="n">
-        <v>1.22</v>
+        <v>0.34</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>5.1</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Base (Vienna)</t>
+        </is>
       </c>
       <c r="X80" t="b">
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Sugar, Table (Sucrose)</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
       <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="AH80" t="n">
-        <v>6.56</v>
+        <v>11.11</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.046</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ80" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr"/>
@@ -10560,12 +10590,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Smash Mosaic</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10575,81 +10605,71 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-132c22b</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
+          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
+          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1785061181508</v>
+        <v>1772634460383</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.20.2</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3</v>
+        <v>0.21</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.22</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Base (Pilsner)</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="X81" t="b">
         <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Sugar, Table (Sucrose)</t>
         </is>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
       <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
+      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="AJ81" t="n">
         <v>100</v>
       </c>
-      <c r="AI81" t="n">
-        <v>1.0368</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>80</v>
-      </c>
       <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
+      <c r="AM81" t="inlineStr"/>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr"/>
@@ -10659,8 +10679,232 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr"/>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>default-c454dca637a</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>1785061180905</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="S82" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>80</v>
+      </c>
+      <c r="V82" t="n">
+        <v>80</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Base (Munich)</t>
+        </is>
+      </c>
+      <c r="X82" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Swaen Munich Light</t>
+        </is>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH82" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>75.37</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1785061181508</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X83" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>Swaen Pilsner</t>
+        </is>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH83" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr"/>
+      <c r="AP83" t="inlineStr"/>
+      <c r="AQ83" t="inlineStr"/>
+      <c r="AR83" t="inlineStr"/>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT81"/>
+  <autoFilter ref="A1:AT83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10671,7 +10915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP71"/>
+  <dimension ref="A1:AP72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10703,7 +10947,7 @@
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="36" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="53" customWidth="1" min="33" max="33"/>
@@ -11767,7 +12011,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -11865,7 +12109,7 @@
         <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
         <v>5.59</v>
@@ -11877,7 +12121,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -11975,7 +12219,7 @@
         <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
         <v>5.59</v>
@@ -11987,7 +12231,7 @@
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -16937,56 +17181,30 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>default-NrD3kYzu8ONSucGjXgHxRcgSUwk2aK</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="H65" t="n">
-        <v>20</v>
-      </c>
-      <c r="J65" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K65" t="n">
-        <v>11</v>
-      </c>
-      <c r="L65" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="M65" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
       </c>
-      <c r="P65" t="n">
-        <v>20</v>
-      </c>
       <c r="Q65" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="S65" t="n">
-        <v>33</v>
+        <v>14.5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Saaz</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Saaz is the famous aroma landrace variety originating in the Czech area of the same name. It has very mild, pleasant noble hoppy notes perfectly suited for and defines the Czech-style pilsner beers.
-Pedigree Czech landrace variety Aroma Classic noble aroma hop with long and strong tradition associated with classic pilsner beer.</t>
-        </is>
-      </c>
-      <c r="V65" t="n">
-        <v>0.7</v>
-      </c>
+          <t>Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="X65" t="inlineStr"/>
@@ -16998,7 +17216,11 @@
           <t>Pellet</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
           <t>Boil</t>
@@ -17008,21 +17230,21 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 967000000, "_seconds": 1775807186}</t>
+          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>wgmsfM7hAArpDzCYHBWiW6iwLQheal</t>
+          <t>NN4PCqpf5oxhJkuWbopSaKCIPRhVk7</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 703000000, "_seconds": 1781070146}</t>
+          <t>{"_nanoseconds": 749000000, "_seconds": 1781070162}</t>
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>1781070146703</v>
+        <v>1781070162749</v>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
@@ -17030,12 +17252,14 @@
         </is>
       </c>
       <c r="AL65" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AM65" t="inlineStr"/>
       <c r="AN65" t="inlineStr"/>
       <c r="AO65" t="inlineStr"/>
-      <c r="AP65" t="inlineStr"/>
+      <c r="AP65" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17062,7 +17286,7 @@
         <v>6.3</v>
       </c>
       <c r="H66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>3.5</v>
@@ -17074,7 +17298,7 @@
         <v>30</v>
       </c>
       <c r="Q66" t="n">
-        <v>11.4</v>
+        <v>5.7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -17164,59 +17388,47 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>default-NrD3kYzu8ONSucGjXgHxRcgSUwk2aK</t>
+          <t>default-kazbek</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K67" t="n">
-        <v>11</v>
-      </c>
-      <c r="L67" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="M67" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
       </c>
-      <c r="P67" t="n">
-        <v>20</v>
+      <c r="O67" t="n">
+        <v>15</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S67" t="n">
-        <v>33</v>
+        <v>4.3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
+          <t>Kazbek</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>The classic noble spice of saaz, but with a earthy lemon peel tone. Primarily an aroma hop for whirlpool or dry hopping. Noble hop character but high oil content. Similar to a very strong Saaz with notes of citrus and grapefruit.</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
           <t>Saaz</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Saaz is the famous aroma landrace variety originating in the Czech area of the same name. It has very mild, pleasant noble hoppy notes perfectly suited for and defines the Czech-style pilsner beers.
-Pedigree Czech landrace variety Aroma Classic noble aroma hop with long and strong tradition associated with classic pilsner beer.</t>
-        </is>
-      </c>
-      <c r="V67" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Czech Republic</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr"/>
       <c r="Z67" t="n">
         <v>15</v>
       </c>
@@ -17225,31 +17437,39 @@
           <t>Pellet</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
           <t>Boil</t>
         </is>
       </c>
-      <c r="AD67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Pilsner, IPA, Modern Lager, Saison</t>
+        </is>
+      </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 967000000, "_seconds": 1775807186}</t>
+          <t>{"_nanoseconds": 295000000, "_seconds": 1781069919}</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>wgmsfM7hAArpDzCYHBWiW6iwLQheal</t>
+          <t>jum9pfmvmCJNF6xINUHu7wVYN7BFCG</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 703000000, "_seconds": 1781070146}</t>
+          <t>{"_nanoseconds": 295000000, "_seconds": 1781069919}</t>
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>1781070146703</v>
+        <v>1781069919295</v>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
@@ -17257,7 +17477,7 @@
         </is>
       </c>
       <c r="AL67" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AM67" t="inlineStr"/>
       <c r="AN67" t="inlineStr"/>
@@ -17267,12 +17487,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Smash Mosaic</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -17282,57 +17502,49 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>default-0c4aeb7c</t>
+          <t>default-kazbek</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="H68" t="n">
+        <v>20</v>
+      </c>
+      <c r="J68" t="n">
         <v>5</v>
       </c>
-      <c r="J68" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0.1</v>
-      </c>
       <c r="N68" t="b">
         <v>0</v>
       </c>
-      <c r="P68" t="n">
-        <v>0.1</v>
+      <c r="O68" t="n">
+        <v>15</v>
       </c>
       <c r="Q68" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="S68" t="n">
-        <v>40.6</v>
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Mosaic</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="n">
-        <v>1.7</v>
+          <t>Kazbek</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>The classic noble spice of saaz, but with a earthy lemon peel tone. Primarily an aroma hop for whirlpool or dry hopping. Noble hop character but high oil content. Similar to a very strong Saaz with notes of citrus and grapefruit.</t>
+        </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Citra®</t>
+          <t>Saaz</t>
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -17341,7 +17553,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -17351,22 +17563,40 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>India Pale Ale, Pale Ale</t>
+          <t>Pilsner, IPA, Modern Lager, Saison</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr"/>
-      <c r="AG68" t="inlineStr"/>
-      <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr"/>
-      <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="inlineStr"/>
-      <c r="AL68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 295000000, "_seconds": 1781069919}</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>jum9pfmvmCJNF6xINUHu7wVYN7BFCG</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 295000000, "_seconds": 1781069919}</t>
+        </is>
+      </c>
+      <c r="AJ68" t="n">
+        <v>1781069919295</v>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL68" t="n">
+        <v>100</v>
+      </c>
       <c r="AM68" t="inlineStr"/>
       <c r="AN68" t="inlineStr"/>
       <c r="AO68" t="inlineStr"/>
-      <c r="AP68" t="n">
-        <v>15</v>
-      </c>
+      <c r="AP68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17390,10 +17620,10 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>13.5</v>
+        <v>11.1</v>
       </c>
       <c r="H69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J69" t="n">
         <v>5.6</v>
@@ -17411,7 +17641,7 @@
         <v>0.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>9.6</v>
+        <v>15.9</v>
       </c>
       <c r="S69" t="n">
         <v>40.6</v>
@@ -17436,7 +17666,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -17459,12 +17689,32 @@
         </is>
       </c>
       <c r="AE69" t="inlineStr"/>
-      <c r="AG69" t="inlineStr"/>
-      <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
-      <c r="AJ69" t="inlineStr"/>
-      <c r="AK69" t="inlineStr"/>
-      <c r="AL69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AJ69" t="n">
+        <v>1785754354406</v>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL69" t="n">
+        <v>200</v>
+      </c>
       <c r="AM69" t="inlineStr"/>
       <c r="AN69" t="inlineStr"/>
       <c r="AO69" t="inlineStr"/>
@@ -17494,10 +17744,10 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>13.5</v>
+        <v>11.1</v>
       </c>
       <c r="H70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J70" t="n">
         <v>5.6</v>
@@ -17515,7 +17765,7 @@
         <v>0.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="S70" t="n">
         <v>40.6</v>
@@ -17540,7 +17790,7 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -17563,12 +17813,32 @@
         </is>
       </c>
       <c r="AE70" t="inlineStr"/>
-      <c r="AG70" t="inlineStr"/>
-      <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr"/>
-      <c r="AJ70" t="inlineStr"/>
-      <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AJ70" t="n">
+        <v>1785754354406</v>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL70" t="n">
+        <v>200</v>
+      </c>
       <c r="AM70" t="inlineStr"/>
       <c r="AN70" t="inlineStr"/>
       <c r="AO70" t="inlineStr"/>
@@ -17598,10 +17868,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>13.5</v>
+        <v>11.1</v>
       </c>
       <c r="H71" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
         <v>5.6</v>
@@ -17619,7 +17889,7 @@
         <v>0.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>8.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="S71" t="n">
         <v>40.6</v>
@@ -17643,11 +17913,8 @@
           <t>Citra®</t>
         </is>
       </c>
-      <c r="Y71" t="n">
-        <v>75</v>
-      </c>
       <c r="Z71" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -17661,7 +17928,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -17670,20 +17937,167 @@
         </is>
       </c>
       <c r="AE71" t="inlineStr"/>
-      <c r="AG71" t="inlineStr"/>
-      <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr"/>
-      <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr"/>
-      <c r="AL71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AJ71" t="n">
+        <v>1785754354406</v>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL71" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM71" t="inlineStr"/>
       <c r="AN71" t="inlineStr"/>
       <c r="AO71" t="inlineStr"/>
       <c r="AP71" t="n">
         <v>15</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Smash Mosaic</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>40</v>
+      </c>
+      <c r="J72" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="S72" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Y72" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AJ72" t="n">
+        <v>1785754354406</v>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL72" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP71"/>
+  <autoFilter ref="A1:AP72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30170,16 +30584,16 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1781339598782</v>
+        <v>1785061186542</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -30187,13 +30601,13 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M119" t="b">
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>44</v>
+        <v>40.5</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -30271,7 +30685,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="b">
@@ -30342,16 +30756,16 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1781339597373</v>
+        <v>1785061185868</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -30359,14 +30773,14 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="b">
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>941.2</v>
+        <v>936.7</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -30427,16 +30841,16 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1781339599470</v>
+        <v>1785061187167</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -30453,7 +30867,7 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>342.5</v>
+        <v>340.5</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -14,11 +14,11 @@
     <sheet name="Misc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1962,13 +1962,78 @@
         <is>
           <t>Repitch yeast
 Spund after 4 days
-Ferment on the cooler side 
 Not sure of the app's fg of 1.006 is realistic</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>American Pale Ale</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>All Grain</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ernst Gouws</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1.044619325</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Repitch yeast
+Spund after 4 days
+Not sure of the app's fg of 1.006 is realistic</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P23"/>
+  <autoFilter ref="A1:P24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1979,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT83"/>
+  <dimension ref="A1:AT84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10903,8 +10968,110 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>1785061181508</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X84" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>Swaen Pilsner</t>
+        </is>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH84" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="inlineStr"/>
+      <c r="AR84" t="inlineStr"/>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT83"/>
+  <autoFilter ref="A1:AT84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10915,7 +11082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP72"/>
+  <dimension ref="A1:AP76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -18096,8 +18263,506 @@
         <v>15</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>11</v>
+      </c>
+      <c r="J73" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S73" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AJ73" t="n">
+        <v>1785754354406</v>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL73" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>10</v>
+      </c>
+      <c r="J74" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="S74" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AJ74" t="n">
+        <v>1785754354406</v>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL74" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S75" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AJ75" t="n">
+        <v>1785754354406</v>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL75" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>default-0c4aeb7c</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>40</v>
+      </c>
+      <c r="J76" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="S76" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Citra®</t>
+        </is>
+      </c>
+      <c r="Y76" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>India Pale Ale, Pale Ale</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+        </is>
+      </c>
+      <c r="AJ76" t="n">
+        <v>1785754354406</v>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL76" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP72"/>
+  <autoFilter ref="A1:AP76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18108,7 +18773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL23"/>
+  <dimension ref="A1:AL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -20716,8 +21381,131 @@
         <v>0</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Yeast</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>default-qytQJkV9cQwX6g1aZ4Carqa9z0LXeE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>250</v>
+      </c>
+      <c r="H24" t="n">
+        <v>80</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Medium-Low</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>WHC Lab</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>13</v>
+      </c>
+      <c r="R24" t="n">
+        <v>80</v>
+      </c>
+      <c r="S24" t="n">
+        <v>22</v>
+      </c>
+      <c r="T24" t="n">
+        <v>76</v>
+      </c>
+      <c r="U24" t="n">
+        <v>18</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Clean West Coast IPA</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>LAX</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Repitch</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 443000000, "_seconds": 1784057955}</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>7L5ixnuXBXaqmTBXyQnlfKg5wkjOhb</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 72000000, "_seconds": 1785061190}</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1785061190072</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL23"/>
+  <autoFilter ref="A1:AL24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20728,7 +21516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB129"/>
+  <dimension ref="A1:AB134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -31500,8 +32288,436 @@
       <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>default-3b1827</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>1785061186542</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>2</v>
+      </c>
+      <c r="M130" t="b">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Calcium Chloride (CaCl2)</t>
+        </is>
+      </c>
+      <c r="Q130" t="b">
+        <v>0</v>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U130" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr"/>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>default-1f88df</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>1785061185868</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>3</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="b">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>936.7</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Gypsum (CaSO4)</t>
+        </is>
+      </c>
+      <c r="Q131" t="b">
+        <v>0</v>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U131" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>1785061187167</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>2</v>
+      </c>
+      <c r="L132" t="n">
+        <v>80</v>
+      </c>
+      <c r="M132" t="b">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q132" t="b">
+        <v>0</v>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U132" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y132" t="inlineStr"/>
+      <c r="Z132" t="inlineStr"/>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>default-yn1j28sf</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>1781339600221</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="b">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>33</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q133" t="b">
+        <v>0</v>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Smash shoddy</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>default-5adf6e</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>hBAibaPvX0FHQT9ll1gxER4gHbbxIg</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1785061187}</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>1785061187983</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="b">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q134" t="b">
+        <v>0</v>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Fining</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB129"/>
+  <autoFilter ref="A1:AB134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -1941,7 +1941,7 @@
         <v>4.99</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>34.9</v>
+        <v>36.6</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>3.4</v>
@@ -18162,7 +18162,7 @@
         <v>11.1</v>
       </c>
       <c r="H72" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J72" t="n">
         <v>5.6</v>
@@ -18180,7 +18180,7 @@
         <v>0.1</v>
       </c>
       <c r="Q72" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="S72" t="n">
         <v>40.6</v>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -1935,13 +1935,13 @@
         <v>1.044619325</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.007</v>
+        <v>1.006</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.99</v>
+        <v>5.12</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>36.6</v>
+        <v>37.7</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>3.4</v>
@@ -18038,7 +18038,7 @@
         <v>11.1</v>
       </c>
       <c r="H71" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J71" t="n">
         <v>5.6</v>
@@ -18056,7 +18056,7 @@
         <v>0.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="S71" t="n">
         <v>40.6</v>
@@ -18162,7 +18162,7 @@
         <v>11.1</v>
       </c>
       <c r="H72" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J72" t="n">
         <v>5.6</v>
@@ -18180,7 +18180,7 @@
         <v>0.1</v>
       </c>
       <c r="Q72" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S72" t="n">
         <v>40.6</v>
@@ -31989,7 +31989,7 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="b">

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -1941,7 +1941,7 @@
         <v>5.12</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>3.4</v>
@@ -18038,7 +18038,7 @@
         <v>11.1</v>
       </c>
       <c r="H71" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J71" t="n">
         <v>5.6</v>
@@ -18056,7 +18056,7 @@
         <v>0.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="S71" t="n">
         <v>40.6</v>
@@ -18162,7 +18162,7 @@
         <v>11.1</v>
       </c>
       <c r="H72" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J72" t="n">
         <v>5.6</v>
@@ -18180,7 +18180,7 @@
         <v>0.1</v>
       </c>
       <c r="Q72" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S72" t="n">
         <v>40.6</v>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$134</definedName>
@@ -747,7 +747,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>International Pale Lager</t>
+          <t>German Pils</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -766,19 +766,19 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.045320964</v>
+        <v>1.044619325</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.008</v>
+        <v>1.007</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>4.86</v>
+        <v>4.99</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>12</v>
@@ -795,7 +795,7 @@
       <c r="P5" t="inlineStr">
         <is>
           <t>First time using Apres Ski yeast. 
-Spund from day 2 at 12psi
+Spund later in fermentation up to 12 psi
 Pitch 22 grams yeast
 No gelatine</t>
         </is>
@@ -2044,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT84"/>
+  <dimension ref="A1:AT81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3393,7 +3393,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>1.9</v>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>74.92</v>
+        <v>100</v>
       </c>
       <c r="AI12" t="n">
         <v>1.0368</v>
@@ -3448,12 +3448,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AlNro2l8joSt8O98vSwLNZqS08yafE</t>
+          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nog 'n lager</t>
+          <t>London Pub Gen 2 Amber Ale</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3463,52 +3463,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1776345923984</v>
+        <v>1721546982716</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X13" t="b">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.45</v>
+        <v>-2.59</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE13" t="b">
@@ -3517,22 +3517,19 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>14.66</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.03588</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>78</v>
+        <v>1.036</v>
       </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -3550,12 +3547,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AlNro2l8joSt8O98vSwLNZqS08yafE</t>
+          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nog 'n lager</t>
+          <t>London Pub Gen 2 Amber Ale</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3563,52 +3560,28 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1785061180905</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>default-60a8af8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
       <c r="Q14" t="n">
-        <v>6.6</v>
+        <v>7.614213</v>
       </c>
       <c r="S14" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>80</v>
-      </c>
-      <c r="V14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -3618,43 +3591,53 @@
       <c r="X14" t="b">
         <v>0</v>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="n">
-        <v>2.19</v>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>100</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Munich I</t>
         </is>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+        </is>
+      </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>6.51</v>
+        <v>14.97</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.035</v>
+        <v>1.038</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75.37</v>
+        <v>82.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AL14" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Amber Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -3664,7 +3647,9 @@
       </c>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
@@ -3672,12 +3657,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AlNro2l8joSt8O98vSwLNZqS08yafE</t>
+          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nog 'n lager</t>
+          <t>London Pub Gen 2 Amber Ale</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3685,53 +3670,37 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1778997166131</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>default-aaaccad</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.15</v>
+      </c>
       <c r="P15" t="n">
         <v>1.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.5228426</v>
+        <v>13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X15" t="b">
@@ -3740,18 +3709,15 @@
       <c r="Y15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0.9</v>
-      </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AC15" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Dextrin Malt</t>
+          <t>Carahell</t>
         </is>
       </c>
       <c r="AE15" t="b">
@@ -3759,30 +3725,30 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Used to provide extra body to beer and to improve head retention</t>
+          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>3.91</v>
+        <v>5.99</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -3813,75 +3779,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1721546982716</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
+          <t>default-741be46</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>63</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X16" t="b">
         <v>0</v>
       </c>
-      <c r="Z16" t="n">
-        <v>-2.59</v>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.6</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Caramunich II</t>
         </is>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>German crystal malt. Adds maltiness, aroma, color.</t>
+        </is>
+      </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>74.84999999999999</v>
+        <v>2.99</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
       </c>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -3915,29 +3889,34 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>default-60a8af8</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q17" t="n">
-        <v>7.614213</v>
+        <v>558.375635</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
-      </c>
-      <c r="U17" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X17" t="b">
@@ -3947,14 +3926,14 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Munich I</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE17" t="b">
@@ -3962,7 +3941,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -3971,22 +3950,18 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>14.97</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.038</v>
+        <v>1.036</v>
       </c>
       <c r="AJ17" t="n">
-        <v>82.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Amber Liquid Extract</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -4000,7 +3975,7 @@
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="n">
-        <v>6.2</v>
+        <v>412.8</v>
       </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
@@ -4009,12 +3984,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
+          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>London Pub Gen 2 Amber Ale</t>
+          <t>Rice beer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4022,85 +3997,78 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>default-aaaccad</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1778997165061</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X18" t="b">
         <v>0</v>
       </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>6.7</v>
+      <c r="Z18" t="n">
+        <v>7.7</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Carahell</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
-        </is>
-      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>5.99</v>
+        <v>64.52</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.035</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ18" t="n">
-        <v>75.73999999999999</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -4118,12 +4086,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
+          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>London Pub Gen 2 Amber Ale</t>
+          <t>Rice beer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4134,82 +4102,50 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>default-741be46</t>
+          <t>default-7c1aab5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>63</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
-        </is>
-      </c>
-      <c r="X19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.6</v>
-      </c>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Caramunich II</t>
+          <t>Rice, Flaked</t>
         </is>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>German crystal malt. Adds maltiness, aroma, color.</t>
-        </is>
-      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>2.99</v>
+        <v>24.19</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.035</v>
+        <v>1.0322</v>
       </c>
       <c r="AJ19" t="n">
-        <v>75.73999999999999</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Weyermann</t>
-        </is>
-      </c>
+      <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -4225,12 +4161,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
+          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>London Pub Gen 2 Amber Ale</t>
+          <t>Rice beer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4238,85 +4174,78 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1776345923984</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
       </c>
       <c r="L20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X20" t="b">
         <v>0</v>
       </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3</v>
+      <c r="Z20" t="n">
+        <v>3.45</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>8.06</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.036</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ20" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -4326,9 +4255,7 @@
       </c>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
@@ -4351,76 +4278,102 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
+          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
+          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1778997165061</v>
+        <v>1778997166131</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0.1</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>1.5228426</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X21" t="b">
         <v>0</v>
       </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
       <c r="Z21" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Dextrin Malt</t>
         </is>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Used to provide extra body to beer and to improve head retention</t>
+        </is>
+      </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>64.52</v>
+        <v>3.23</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.0368</v>
+        <v>1.037</v>
       </c>
       <c r="AJ21" t="n">
         <v>80</v>
       </c>
+      <c r="AK21" t="n">
+        <v>10</v>
+      </c>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -4438,12 +4391,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
+          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rice beer</t>
+          <t>Kolserig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4454,7 +4407,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>default-7c1aab5</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -4462,20 +4415,20 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>0.75</v>
+        <v>2.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Rice, Flaked</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE22" t="b">
@@ -4484,20 +4437,24 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>24.19</v>
+        <v>81.56</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.0322</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ22" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN22" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -4513,12 +4470,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
+          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rice beer</t>
+          <t>Kolserig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4526,36 +4483,18 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>default-d9e04639a2c</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1776345923984</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>0.25</v>
+        <v>0.64</v>
       </c>
       <c r="Q23" t="n">
         <v>5.1</v>
@@ -4565,12 +4504,7 @@
           <t>Base (Vienna)</t>
         </is>
       </c>
-      <c r="X23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.45</v>
-      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
           <t>Swaen Vienna</t>
@@ -4586,7 +4520,7 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>8.06</v>
+        <v>18.44</v>
       </c>
       <c r="AI23" t="n">
         <v>1.03588</v>
@@ -4615,12 +4549,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
+          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rice beer</t>
+          <t>London Pub Gen 1 Stout saved by Bond</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4630,51 +4564,51 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
+          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
+          <t>default-e6ba5b8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
+          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1778997166131</v>
+        <v>1721546982714</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>1.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.5228426</v>
+        <v>3.2994924</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Maris Otter)</t>
         </is>
       </c>
       <c r="X24" t="b">
@@ -4684,17 +4618,17 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.9</v>
+        <v>-4.59</v>
       </c>
       <c r="AB24" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AC24" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Dextrin Malt</t>
+          <t>Finest Maris Otter® Ale Malt</t>
         </is>
       </c>
       <c r="AE24" t="b">
@@ -4702,7 +4636,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Used to provide extra body to beer and to improve head retention</t>
+          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -4711,16 +4645,16 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>3.23</v>
+        <v>66.89</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ24" t="n">
-        <v>80</v>
+        <v>81.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr">
@@ -4743,12 +4677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
+          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kolserig</t>
+          <t>London Pub Gen 1 Stout saved by Bond</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4756,55 +4690,110 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 429000000, "_seconds": 1697269073}</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>default-1f44c9e</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>F1TM4o4Xs8cgfF95wPoLjkPxbCpQ9w</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 155000000, "_seconds": 1704369569}</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1704369569155</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2.10.4</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" t="n">
-        <v>2.83</v>
+        <v>0.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
+      </c>
+      <c r="S25" t="n">
+        <v>110</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Base (Pilsner)</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.4</v>
+      </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Pilsner</t>
         </is>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Pilsner base malt for all pilsners, lagers. Highly modified malt.</t>
+        </is>
+      </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>81.56</v>
+        <v>16.72</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.0368</v>
+        <v>1.038</v>
       </c>
       <c r="AJ25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL25" t="inlineStr"/>
+        <v>82.23</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Pilsner Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -4822,12 +4811,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
+          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kolserig</t>
+          <t>London Pub Gen 1 Stout saved by Bond</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4838,52 +4827,80 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.1</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr"/>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3</v>
+      </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>18.44</v>
+        <v>7.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.03588</v>
+        <v>1.036</v>
       </c>
       <c r="AJ26" t="n">
-        <v>78</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>10</v>
       </c>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -4893,7 +4910,9 @@
       </c>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
+      <c r="AQ26" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR26" t="inlineStr"/>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
@@ -4914,53 +4933,35 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>default-e6ba5b8</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1721546982714</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-741be46</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2994924</v>
+        <v>63</v>
       </c>
       <c r="S27" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X27" t="b">
@@ -4969,18 +4970,15 @@
       <c r="Y27" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" t="n">
-        <v>-4.59</v>
-      </c>
       <c r="AB27" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Finest Maris Otter® Ale Malt</t>
+          <t>Caramunich II</t>
         </is>
       </c>
       <c r="AE27" t="b">
@@ -4988,30 +4986,30 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
+          <t>German crystal malt. Adds maltiness, aroma, color.</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>66.89</v>
+        <v>3.34</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.038</v>
+        <v>1.035</v>
       </c>
       <c r="AJ27" t="n">
-        <v>81.5</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="AK27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -5042,110 +5040,55 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 429000000, "_seconds": 1697269073}</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>default-1f44c9e</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>F1TM4o4Xs8cgfF95wPoLjkPxbCpQ9w</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 155000000, "_seconds": 1704369569}</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1704369569155</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2.10.4</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
+          <t>default-d2c0778</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S28" t="n">
-        <v>110</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.4</v>
-      </c>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Pilsner</t>
+          <t>Oats, Flaked</t>
         </is>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>Pilsner base malt for all pilsners, lagers. Highly modified malt.</t>
-        </is>
-      </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>16.72</v>
+        <v>3.34</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.038</v>
+        <v>1.0391</v>
       </c>
       <c r="AJ28" t="n">
-        <v>82.23</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Pilsner Liquid Extract</t>
-        </is>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Briess</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -5179,7 +5122,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-fc0f80b</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -5190,14 +5133,14 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="P29" t="n">
         <v>1.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>558.375635</v>
+        <v>415</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -5217,11 +5160,11 @@
         <v>5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Carafa II</t>
         </is>
       </c>
       <c r="AE29" t="b">
@@ -5229,7 +5172,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>Chocolate malt. Dark beers, Alts, Bockbiers. Adds color and aroma.</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -5238,7 +5181,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>7.36</v>
+        <v>2.34</v>
       </c>
       <c r="AI29" t="n">
         <v>1.036</v>
@@ -5262,9 +5205,7 @@
       </c>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr"/>
@@ -5272,12 +5213,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
+          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>London Pub Gen 1 Stout saved by Bond</t>
+          <t>Marigold Lager</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5288,80 +5229,52 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>default-741be46</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="P30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>63</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
-        </is>
-      </c>
-      <c r="X30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>5.6</v>
-      </c>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Caramunich II</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>German crystal malt. Adds maltiness, aroma, color.</t>
-        </is>
-      </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>3.34</v>
+        <v>100</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.035</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ30" t="n">
-        <v>75.73999999999999</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -5379,12 +5292,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
+          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>London Pub Gen 1 Stout saved by Bond</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5392,31 +5305,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>default-d2c0778</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1778997165061</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="L31" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7.7</v>
+      </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Oats, Flaked</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE31" t="b">
@@ -5425,22 +5361,22 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>3.34</v>
+        <v>26.25</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.0391</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ31" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Briess</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -5458,12 +5394,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
+          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>London Pub Gen 1 Stout saved by Bond</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5471,83 +5407,98 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>default-fc0f80b</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>0</v>
+          <t>default-c454dca637a</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Jr8QUoFHfyKXPhn1IjtiaA3GZwRjfZ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 385000000, "_seconds": 1777108191}</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1777108191385</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
       </c>
       <c r="L32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>415</v>
+        <v>6.6</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>80</v>
+      </c>
+      <c r="V32" t="n">
+        <v>80</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X32" t="b">
         <v>0</v>
       </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>5</v>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>3.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Carafa II</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>Chocolate malt. Dark beers, Alts, Bockbiers. Adds color and aroma.</t>
-        </is>
-      </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>2.34</v>
+        <v>15.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="AJ32" t="n">
-        <v>77.90000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="AK32" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -5565,12 +5516,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
+          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Marigold Lager</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5578,31 +5529,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1776345923984</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
+      </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr"/>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.45</v>
+      </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE33" t="b">
@@ -5615,13 +5589,13 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>100</v>
+        <v>15.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.0368</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ33" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr">
@@ -5657,78 +5631,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1778997165061</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
+          <t>default-96t8Xs5OLBpW9y5feB0tUbwyNtbfO4</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0.48</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.9</v>
+        <v>2.5380711</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X34" t="b">
         <v>0</v>
       </c>
-      <c r="Z34" t="n">
-        <v>7.7</v>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>11</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Flaked Torrefied Oats</t>
         </is>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
+        </is>
+      </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>26.25</v>
+        <v>12.6</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.0368</v>
+        <v>1.032</v>
       </c>
       <c r="AJ34" t="n">
-        <v>80</v>
+        <v>70</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>11</v>
       </c>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
@@ -5761,26 +5740,26 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-0aa30343c0c</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Jr8QUoFHfyKXPhn1IjtiaA3GZwRjfZ</t>
+          <t>JLLnm9cGPVv3337nwYsF4XU4bmE8yr</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 385000000, "_seconds": 1777108191}</t>
+          <t>{"_nanoseconds": 206000000, "_seconds": 1776345941}</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1777108191385</v>
+        <v>1776345941206</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -5788,27 +5767,27 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="S35" t="n">
-        <v>18.2</v>
+        <v>76</v>
       </c>
       <c r="U35" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V35" t="n">
         <v>80</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X35" t="b">
@@ -5816,36 +5795,43 @@
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>3.14</v>
+        <v>4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>100</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Ale</t>
         </is>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
+        </is>
+      </c>
       <c r="AG35" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>15.75</v>
+        <v>10.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.035</v>
+        <v>1.037</v>
       </c>
       <c r="AJ35" t="n">
-        <v>75.37</v>
+        <v>80.13</v>
       </c>
       <c r="AK35" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr">
@@ -5883,26 +5869,26 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-29dda1b5335</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+          <t>bvta1UbScHCOHOL3y0bkomTlBk4ToI</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+          <t>{"_nanoseconds": 566000000, "_seconds": 1776346236}</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1776345923984</v>
+        <v>1776346236566</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -5910,25 +5896,25 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.1</v>
+        <v>329.949239</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X36" t="b">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.45</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>BlackSwaen Coffee</t>
         </is>
       </c>
       <c r="AE36" t="b">
@@ -5941,13 +5927,13 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>15.75</v>
+        <v>9.19</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.03588</v>
+        <v>1.028</v>
       </c>
       <c r="AJ36" t="n">
-        <v>78</v>
+        <v>60.8695652</v>
       </c>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr">
@@ -5962,7 +5948,9 @@
       </c>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
+      <c r="AQ36" t="n">
+        <v>244.1</v>
+      </c>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr"/>
@@ -5983,52 +5971,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>default-96t8Xs5OLBpW9y5feB0tUbwyNtbfO4</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>0</v>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1776345994305</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
       </c>
       <c r="L37" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>1.5</v>
+        <v>0.28</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.5380711</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X37" t="b">
         <v>0</v>
       </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>11</v>
+      <c r="Z37" t="n">
+        <v>2</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Flaked Torrefied Oats</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE37" t="b">
@@ -6036,30 +6026,27 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>12.6</v>
+        <v>7.35</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.032</v>
+        <v>1.034</v>
       </c>
       <c r="AJ37" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>11</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -6092,72 +6079,71 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
+          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>default-0aa30343c0c</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>JLLnm9cGPVv3337nwYsF4XU4bmE8yr</t>
+          <t>jWuqIkMLK24jzylCQapUkVKL5iFO6T</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 206000000, "_seconds": 1776345941}</t>
+          <t>{"_nanoseconds": 551000000, "_seconds": 1777108193}</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1776345941206</v>
+        <v>1777108193551</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>3.0.0</t>
         </is>
       </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>558.375635</v>
       </c>
       <c r="S38" t="n">
-        <v>76</v>
-      </c>
-      <c r="U38" t="n">
-        <v>81</v>
-      </c>
-      <c r="V38" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X38" t="b">
         <v>0</v>
       </c>
-      <c r="Y38" t="inlineStr"/>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>0.88</v>
       </c>
       <c r="AB38" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Swaen Ale</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE38" t="b">
@@ -6165,30 +6151,30 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>10.5</v>
+        <v>2.62</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.037</v>
+        <v>1.036</v>
       </c>
       <c r="AJ38" t="n">
-        <v>80.13</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK38" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
@@ -6198,7 +6184,9 @@
       </c>
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
+      <c r="AQ38" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR38" t="inlineStr"/>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr"/>
@@ -6221,76 +6209,102 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
+          <t>{"_nanoseconds": 546000000, "_seconds": 1712314605}</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>default-29dda1b5335</t>
+          <t>default-Q0GFlvnA7LLqVkkfYBAXCniMcRZwnf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>bvta1UbScHCOHOL3y0bkomTlBk4ToI</t>
+          <t>7aV7RCW73FffCIp6YwXe3Ui8TTLeJE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 566000000, "_seconds": 1776346236}</t>
+          <t>{"_nanoseconds": 122000000, "_seconds": 1778682369}</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1776346236566</v>
+        <v>1778682369122</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3.0.0</t>
-        </is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>0.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>329.949239</v>
+        <v>1.8</v>
+      </c>
+      <c r="S39" t="n">
+        <v>146</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
+      <c r="AB39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.4</v>
+      </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>BlackSwaen Coffee</t>
+          <t>Malteurop Pilsen</t>
         </is>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>The lightest of our two-row base malts, Malteurop Pilsen malt imparts a sweet and subtle malt flavor and a straw yellow to light golden color. It can be used up to 100% in all beer styles and provides a perfect canvas for other specialty malts.</t>
+        </is>
+      </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>9.19</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.028</v>
+        <v>1.038</v>
       </c>
       <c r="AJ39" t="n">
-        <v>60.8695652</v>
+        <v>81.7</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>11.3</v>
       </c>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Malteurop Malting Co.</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
@@ -6300,22 +6314,22 @@
       </c>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="n">
-        <v>244.1</v>
-      </c>
-      <c r="AR39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="b">
+        <v>1</v>
+      </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
+          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Lager pseudo idea ii</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6325,80 +6339,79 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1776345994305</v>
+        <v>1721546982716</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.28</v>
+        <v>3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X40" t="b">
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>-2.59</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>7.35</v>
+        <v>92.59</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ40" t="n">
-        <v>73.9130435</v>
+        <v>76</v>
       </c>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -6416,12 +6429,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
+          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Lager pseudo idea ii</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6429,53 +6442,37 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>jWuqIkMLK24jzylCQapUkVKL5iFO6T</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 551000000, "_seconds": 1777108193}</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>1777108193551</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
-      </c>
+          <t>default-cdbfbd6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
+        <v>0.14</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.73</v>
+      </c>
       <c r="P41" t="n">
         <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>558.375635</v>
+        <v>30</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X41" t="b">
@@ -6484,18 +6481,15 @@
       <c r="Y41" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AB41" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AC41" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Melanoidin</t>
         </is>
       </c>
       <c r="AE41" t="b">
@@ -6503,7 +6497,7 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
@@ -6512,18 +6506,22 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>2.62</v>
+        <v>4.32</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.036</v>
+        <v>1.037</v>
       </c>
       <c r="AJ41" t="n">
-        <v>77.90000000000001</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AK41" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL41" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Carared</t>
+        </is>
+      </c>
       <c r="AM41" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -6536,9 +6534,7 @@
       </c>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ41" t="inlineStr"/>
       <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr"/>
@@ -6546,12 +6542,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
+          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Lager pseudo idea ii</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6559,106 +6555,53 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 546000000, "_seconds": 1712314605}</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>default-Q0GFlvnA7LLqVkkfYBAXCniMcRZwnf</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>7aV7RCW73FffCIp6YwXe3Ui8TTLeJE</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 122000000, "_seconds": 1778682369}</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>1778682369122</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
+          <t>default-08f456e</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>0.1</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>0.8</v>
-      </c>
       <c r="Q42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S42" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>4.4</v>
-      </c>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Malteurop Pilsen</t>
+          <t>Oats, Flaked</t>
         </is>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>The lightest of our two-row base malts, Malteurop Pilsen malt imparts a sweet and subtle malt flavor and a straw yellow to light golden color. It can be used up to 100% in all beer styles and provides a perfect canvas for other specialty malts.</t>
-        </is>
-      </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.038</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ42" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>11.3</v>
+        <v>80</v>
       </c>
       <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Malteurop Malting Co.</t>
-        </is>
-      </c>
+      <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -6667,21 +6610,19 @@
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="b">
-        <v>1</v>
-      </c>
+      <c r="AR42" t="inlineStr"/>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lager pseudo idea ii</t>
+          <t>First Lager v3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6689,81 +6630,89 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>1721546982716</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-kTJTLZIhyeFDXlOIOLxrPWfGnU8z4A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>3</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.8</v>
+        <v>2</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1.9</v>
+      </c>
+      <c r="U43" t="n">
+        <v>80</v>
+      </c>
+      <c r="V43" t="n">
+        <v>82</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X43" t="b">
         <v>0</v>
       </c>
-      <c r="Z43" t="n">
-        <v>-2.59</v>
+      <c r="Y43" t="inlineStr"/>
+      <c r="AB43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>5</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Bohemian Pilsner</t>
         </is>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Made from the finest Bohemian malting quality barley (Barley varieties Bojos and Malz), this Pilsner malt is characterized by the typical sententious core notes of the original barley varieties.
+Sensory: nutty malt aroma, malty-sweet
+Enzyme activity: high
+(Non-floor malted variety) 
+Product Sheet: https://www.weyermann.de/wp-content/uploads/2021/02/Weyermann_Bohemian_Pilsner_Malt_Specification.pdf</t>
+        </is>
+      </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Bohemia</t>
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>92.59</v>
+        <v>71.94</v>
       </c>
       <c r="AI43" t="n">
         <v>1.035</v>
       </c>
       <c r="AJ43" t="n">
-        <v>76</v>
-      </c>
-      <c r="AL43" t="inlineStr"/>
+        <v>75.05</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Weyermann Floor-Malted Bohemian Pilsner Malt</t>
+        </is>
+      </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
@@ -6771,9 +6720,15 @@
           <t>Grain</t>
         </is>
       </c>
-      <c r="AO43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>pilsners</t>
+        </is>
+      </c>
       <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr"/>
+      <c r="AQ43" t="n">
+        <v>1.95</v>
+      </c>
       <c r="AR43" t="inlineStr"/>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr"/>
@@ -6781,12 +6736,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lager pseudo idea ii</t>
+          <t>First Lager v3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6797,7 +6752,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>default-cdbfbd6</t>
+          <t>default-4d8b7c4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -6808,23 +6763,23 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="M44" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="P44" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X44" t="b">
@@ -6834,14 +6789,14 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Melanoidin</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE44" t="b">
@@ -6849,7 +6804,7 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
+          <t>Vienna base malt - used in many continental beer styles. Full bodied, golden color.</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
@@ -6858,20 +6813,20 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>4.32</v>
+        <v>17.99</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ44" t="n">
-        <v>80.06999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>Carared</t>
+          <t>Pale Liquid Extract</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -6894,12 +6849,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lager pseudo idea ii</t>
+          <t>First Lager v3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6910,50 +6865,84 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>default-08f456e</t>
+          <t>default-1482365</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
       <c r="L45" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.9</v>
+      </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Oats, Flaked</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+        </is>
+      </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>3.09</v>
+        <v>10.07</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.0368</v>
+        <v>1.037</v>
       </c>
       <c r="AJ45" t="n">
-        <v>80</v>
+        <v>80.06999999999999</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
       </c>
       <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Weyermann</t>
+        </is>
+      </c>
       <c r="AN45" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -6969,12 +6958,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>First Lager v3</t>
+          <t>London Pub gen 2 Weskus</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6982,89 +6971,78 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>default-kTJTLZIhyeFDXlOIOLxrPWfGnU8z4A</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>default-sabmjufsad</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1721546982716</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="L46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q46" t="n">
         <v>2</v>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U46" t="n">
-        <v>80</v>
-      </c>
-      <c r="V46" t="n">
-        <v>82</v>
-      </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X46" t="b">
         <v>0</v>
       </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="AB46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>5</v>
+      <c r="Z46" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Bohemian Pilsner</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>Made from the finest Bohemian malting quality barley (Barley varieties Bojos and Malz), this Pilsner malt is characterized by the typical sententious core notes of the original barley varieties.
-Sensory: nutty malt aroma, malty-sweet
-Enzyme activity: high
-(Non-floor malted variety) 
-Product Sheet: https://www.weyermann.de/wp-content/uploads/2021/02/Weyermann_Bohemian_Pilsner_Malt_Specification.pdf</t>
-        </is>
-      </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>Bohemia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>71.94</v>
+        <v>79.27</v>
       </c>
       <c r="AI46" t="n">
         <v>1.035</v>
       </c>
       <c r="AJ46" t="n">
-        <v>75.05</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Weyermann Floor-Malted Bohemian Pilsner Malt</t>
-        </is>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
@@ -7072,15 +7050,9 @@
           <t>Grain</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>pilsners</t>
-        </is>
-      </c>
+      <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="n">
-        <v>1.95</v>
-      </c>
+      <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr"/>
@@ -7088,12 +7060,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>First Lager v3</t>
+          <t>London Pub gen 2 Weskus</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7101,30 +7073,46 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 248000000, "_seconds": 1714216056}</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>default-4d8b7c4</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CPkrJFvR0z03f2qIouoRdQwhmALFMG</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 27000000, "_seconds": 1723974350}</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1723974350027</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0.5</v>
       </c>
-      <c r="M47" t="n">
-        <v>0.79</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>3.9593909</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -7140,11 +7128,14 @@
       <c r="Y47" t="n">
         <v>0</v>
       </c>
+      <c r="Z47" t="n">
+        <v>-3</v>
+      </c>
       <c r="AB47" t="n">
         <v>100</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
@@ -7156,34 +7147,30 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Vienna base malt - used in many continental beer styles. Full bodied, golden color.</t>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>17.99</v>
+        <v>15.24</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.038</v>
+        <v>1.037</v>
       </c>
       <c r="AJ47" t="n">
-        <v>82.23</v>
+        <v>80</v>
       </c>
       <c r="AK47" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
@@ -7201,12 +7188,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>First Lager v3</t>
+          <t>London Pub gen 2 Weskus</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7217,7 +7204,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-cdbfbd6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -7228,16 +7215,16 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="P48" t="n">
         <v>1.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7254,14 +7241,14 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Melanoidin</t>
         </is>
       </c>
       <c r="AE48" t="b">
@@ -7269,7 +7256,7 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
@@ -7278,7 +7265,7 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>10.07</v>
+        <v>3.96</v>
       </c>
       <c r="AI48" t="n">
         <v>1.037</v>
@@ -7289,7 +7276,11 @@
       <c r="AK48" t="n">
         <v>0</v>
       </c>
-      <c r="AL48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Carared</t>
+        </is>
+      </c>
       <c r="AM48" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -7323,78 +7314,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>1721546982716</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
+          <t>default-aaaccad</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2.6</v>
+        <v>0.05</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X49" t="b">
         <v>0</v>
       </c>
-      <c r="Z49" t="n">
-        <v>-2.59</v>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>6.7</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Carahell</t>
         </is>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+        </is>
+      </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>79.27</v>
+        <v>1.52</v>
       </c>
       <c r="AI49" t="n">
         <v>1.035</v>
       </c>
       <c r="AJ49" t="n">
-        <v>76</v>
+        <v>75.73999999999999</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
       </c>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -7412,12 +7408,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>London Pub gen 2 Weskus</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7425,104 +7421,55 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 248000000, "_seconds": 1714216056}</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>CPkrJFvR0z03f2qIouoRdQwhmALFMG</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 27000000, "_seconds": 1723974350}</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>1723974350027</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="P50" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.9593909</v>
-      </c>
-      <c r="S50" t="n">
-        <v>50</v>
+        <v>1.9</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>4.5</v>
-      </c>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
-        </is>
-      </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>15.24</v>
+        <v>70.73</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.037</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ50" t="n">
         <v>80</v>
       </c>
-      <c r="AK50" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
@@ -7540,12 +7487,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>London Pub gen 2 Weskus</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7556,86 +7503,52 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>default-cdbfbd6</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>30</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
-        </is>
-      </c>
-      <c r="X51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.8</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Melanoidin</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
-        </is>
-      </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>3.96</v>
+        <v>19.51</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.037</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ51" t="n">
-        <v>80.06999999999999</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>Carared</t>
-        </is>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
@@ -7653,12 +7566,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>London Pub gen 2 Weskus</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7669,80 +7582,74 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>default-aaaccad</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>80</v>
+      </c>
+      <c r="V52" t="n">
+        <v>80</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X52" t="b">
         <v>0</v>
       </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>30</v>
-      </c>
+      <c r="Y52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Carahell</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
-        </is>
-      </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>1.52</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AI52" t="n">
         <v>1.035</v>
       </c>
       <c r="AJ52" t="n">
-        <v>75.73999999999999</v>
+        <v>75.37</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
@@ -7773,50 +7680,77 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1781339589491</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="L53" t="n">
-        <v>2.9</v>
+        <v>0.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.9</v>
+        <v>61</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.36</v>
+      </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG53" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>70.73</v>
+        <v>1.22</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.0368</v>
+        <v>1.034</v>
       </c>
       <c r="AJ53" t="n">
-        <v>80</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr">
@@ -7839,12 +7773,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7852,31 +7786,68 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>default-nym-3n456</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1721546982782</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="L54" t="n">
-        <v>0.8</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>5.1</v>
+        <v>1.77665</v>
+      </c>
+      <c r="U54" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="V54" t="n">
+        <v>84</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr"/>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>5</v>
+      </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Barke Pilsner</t>
         </is>
       </c>
       <c r="AE54" t="b">
@@ -7885,22 +7856,22 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>19.51</v>
+        <v>45.16</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.03588</v>
+        <v>1.035</v>
       </c>
       <c r="AJ54" t="n">
-        <v>78</v>
+        <v>76.48</v>
       </c>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
@@ -7918,12 +7889,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7934,7 +7905,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -7942,39 +7913,36 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
       <c r="Q55" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S55" t="n">
-        <v>18.2</v>
+        <v>3.807107</v>
       </c>
       <c r="U55" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V55" t="n">
         <v>80</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X55" t="b">
         <v>0</v>
       </c>
       <c r="Y55" t="inlineStr"/>
+      <c r="AB55" t="n">
+        <v>100</v>
+      </c>
       <c r="AC55" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Barke Vienna Malt</t>
         </is>
       </c>
       <c r="AE55" t="b">
@@ -7983,25 +7951,25 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>8.539999999999999</v>
+        <v>32.26</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.035</v>
+        <v>1.034</v>
       </c>
       <c r="AJ55" t="n">
-        <v>75.37</v>
+        <v>74.66</v>
       </c>
       <c r="AK55" t="n">
-        <v>11.7</v>
+        <v>10.5</v>
       </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
@@ -8011,20 +7979,24 @@
       </c>
       <c r="AO55" t="inlineStr"/>
       <c r="AP55" t="inlineStr"/>
-      <c r="AQ55" t="inlineStr"/>
+      <c r="AQ55" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AR55" t="inlineStr"/>
-      <c r="AS55" t="inlineStr"/>
+      <c r="AS55" t="b">
+        <v>0</v>
+      </c>
       <c r="AT55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8032,54 +8004,52 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>1781339589491</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
+          <t>default-b5ffdd1</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q56" t="n">
-        <v>61</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X56" t="b">
         <v>0</v>
       </c>
-      <c r="Z56" t="n">
-        <v>1.36</v>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE56" t="b">
@@ -8087,27 +8057,30 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>1.22</v>
+        <v>8.06</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.034</v>
+        <v>1.036</v>
       </c>
       <c r="AJ56" t="n">
-        <v>73.9130435</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>10</v>
       </c>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
@@ -8117,7 +8090,9 @@
       </c>
       <c r="AO56" t="inlineStr"/>
       <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr"/>
+      <c r="AQ56" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR56" t="inlineStr"/>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr"/>
@@ -8138,87 +8113,80 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>default-nym-3n456</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>1721546982782</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
+          <t>default-1482365</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q57" t="n">
-        <v>1.77665</v>
-      </c>
-      <c r="U57" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="V57" t="n">
-        <v>84</v>
+        <v>2</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X57" t="b">
         <v>0</v>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="n">
+      <c r="Y57" t="n">
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AC57" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Barke Pilsner</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+        </is>
+      </c>
       <c r="AG57" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>45.16</v>
+        <v>8.06</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.035</v>
+        <v>1.037</v>
       </c>
       <c r="AJ57" t="n">
-        <v>76.48</v>
+        <v>80.06999999999999</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0</v>
       </c>
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr">
@@ -8257,7 +8225,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
+          <t>default-60a8af8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -8265,60 +8233,70 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>3.807107</v>
+        <v>7.614213</v>
+      </c>
+      <c r="S58" t="n">
+        <v>50</v>
       </c>
       <c r="U58" t="n">
-        <v>79</v>
-      </c>
-      <c r="V58" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X58" t="b">
         <v>0</v>
       </c>
-      <c r="Y58" t="inlineStr"/>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
       <c r="AB58" t="n">
         <v>100</v>
       </c>
       <c r="AC58" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Barke Vienna Malt</t>
+          <t>Munich I</t>
         </is>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+        </is>
+      </c>
       <c r="AG58" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>32.26</v>
+        <v>6.45</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.034</v>
+        <v>1.038</v>
       </c>
       <c r="AJ58" t="n">
-        <v>74.66</v>
+        <v>82.3</v>
       </c>
       <c r="AK58" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AL58" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Amber Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM58" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -8332,23 +8310,21 @@
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
       <c r="AQ58" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR58" t="inlineStr"/>
-      <c r="AS58" t="b">
-        <v>0</v>
-      </c>
+      <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8359,80 +8335,52 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="P59" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Roasted</t>
-        </is>
-      </c>
-      <c r="X59" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>3</v>
-      </c>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>8.06</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.036</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ59" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
@@ -8442,9 +8390,7 @@
       </c>
       <c r="AO59" t="inlineStr"/>
       <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="inlineStr"/>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr"/>
@@ -8452,12 +8398,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8468,82 +8414,52 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
       <c r="L60" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P60" t="n">
-        <v>1.5</v>
+        <v>0.62</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Roasted</t>
-        </is>
-      </c>
-      <c r="X60" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>40</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>4.9</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
-        </is>
-      </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>8.06</v>
+        <v>19.87</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.037</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ60" t="n">
-        <v>80.06999999999999</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
@@ -8561,12 +8477,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8577,7 +8493,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>default-60a8af8</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -8585,17 +8501,23 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
       <c r="Q61" t="n">
-        <v>7.614213</v>
+        <v>6.6</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="U61" t="n">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="V61" t="n">
+        <v>80</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -8605,53 +8527,40 @@
       <c r="X61" t="b">
         <v>0</v>
       </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>100</v>
-      </c>
+      <c r="Y61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Munich I</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
-        </is>
-      </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>6.45</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.038</v>
+        <v>1.035</v>
       </c>
       <c r="AJ61" t="n">
-        <v>82.3</v>
+        <v>75.37</v>
       </c>
       <c r="AK61" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>Amber Liquid Extract</t>
-        </is>
-      </c>
+        <v>11.7</v>
+      </c>
+      <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
@@ -8661,9 +8570,7 @@
       </c>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
-      <c r="AQ61" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr"/>
@@ -8687,52 +8594,80 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>0.2</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.9</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X62" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>3</v>
+      </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>64.09999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ62" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>10</v>
       </c>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
@@ -8742,7 +8677,9 @@
       </c>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
-      <c r="AQ62" t="inlineStr"/>
+      <c r="AQ62" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR62" t="inlineStr"/>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr"/>
@@ -8750,12 +8687,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8763,31 +8700,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>1777108192684</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
+      </c>
       <c r="L63" t="n">
-        <v>0.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE63" t="b">
@@ -8800,13 +8760,13 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>19.87</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ63" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr">
@@ -8822,19 +8782,21 @@
       <c r="AO63" t="inlineStr"/>
       <c r="AP63" t="inlineStr"/>
       <c r="AQ63" t="inlineStr"/>
-      <c r="AR63" t="inlineStr"/>
+      <c r="AR63" t="b">
+        <v>0</v>
+      </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8842,50 +8804,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1781339591852</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="L64" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S64" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U64" t="n">
-        <v>80</v>
-      </c>
-      <c r="V64" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X64" t="b">
         <v>0</v>
       </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="AC64" t="n">
-        <v>4.6</v>
+      <c r="Z64" t="n">
+        <v>2.85</v>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE64" t="b">
@@ -8898,16 +8864,13 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>9.619999999999999</v>
+        <v>14.79</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ64" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr">
@@ -8930,12 +8893,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8943,83 +8906,98 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="n">
-        <v>0</v>
+          <t>default-c454dca637a</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1781339591050</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L65" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>558.375635</v>
+        <v>6.6</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>80</v>
+      </c>
+      <c r="V65" t="n">
+        <v>80</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X65" t="b">
         <v>0</v>
       </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>5</v>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="n">
+        <v>2.54</v>
       </c>
       <c r="AC65" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>6.41</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="AJ65" t="n">
-        <v>77.90000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="AK65" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
@@ -9029,9 +9007,7 @@
       </c>
       <c r="AO65" t="inlineStr"/>
       <c r="AP65" t="inlineStr"/>
-      <c r="AQ65" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr"/>
@@ -9054,26 +9030,26 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1777108192684</v>
+        <v>1776345994305</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -9081,44 +9057,48 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.5</v>
+        <v>0.08</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.9</v>
+        <v>61</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X66" t="b">
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG66" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>73.95999999999999</v>
+        <v>2.37</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.0368</v>
+        <v>1.034</v>
       </c>
       <c r="AJ66" t="n">
-        <v>80</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr">
@@ -9134,21 +9114,19 @@
       <c r="AO66" t="inlineStr"/>
       <c r="AP66" t="inlineStr"/>
       <c r="AQ66" t="inlineStr"/>
-      <c r="AR66" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR66" t="inlineStr"/>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9158,26 +9136,26 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -9185,25 +9163,25 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X67" t="b">
         <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE67" t="b">
@@ -9216,13 +9194,13 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>14.79</v>
+        <v>73.02</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ67" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
@@ -9245,12 +9223,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9260,26 +9238,26 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -9287,42 +9265,25 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="P68" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S68" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U68" t="n">
-        <v>80</v>
-      </c>
-      <c r="V68" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X68" t="b">
         <v>0</v>
       </c>
-      <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE68" t="b">
@@ -9335,16 +9296,13 @@
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>8.880000000000001</v>
+        <v>14.29</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ68" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr">
@@ -9367,12 +9325,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9382,75 +9340,91 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1776345994305</v>
+        <v>1781339591050</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S69" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>80</v>
+      </c>
+      <c r="V69" t="n">
+        <v>80</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X69" t="b">
         <v>0</v>
       </c>
+      <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>2</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>2.37</v>
+        <v>11.11</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ69" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr">
@@ -9488,26 +9462,26 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1781339591476</v>
+        <v>1781339589491</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -9515,44 +9489,48 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.3</v>
+        <v>0.05</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.9</v>
+        <v>61</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X70" t="b">
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>6.7</v>
+        <v>1.36</v>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG70" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>73.02</v>
+        <v>1.59</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.0368</v>
+        <v>1.034</v>
       </c>
       <c r="AJ70" t="n">
-        <v>80</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr">
@@ -9575,12 +9553,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9588,78 +9566,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>1781339591852</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
+          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0.45</v>
+        <v>3</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.1</v>
+        <v>1.8527919</v>
+      </c>
+      <c r="S71" t="n">
+        <v>62</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X71" t="b">
         <v>0</v>
       </c>
-      <c r="Z71" t="n">
-        <v>2.85</v>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Clear Choice Malt ® Extra Pale</t>
         </is>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
+        </is>
+      </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>14.29</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.03588</v>
+        <v>1.038</v>
       </c>
       <c r="AJ71" t="n">
-        <v>78</v>
+        <v>81.5</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>10.1</v>
       </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
@@ -9677,12 +9660,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9690,98 +9673,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>1781339591050</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="P72" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>6.6</v>
+        <v>3.9593909</v>
       </c>
       <c r="S72" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U72" t="n">
+        <v>50</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Vienna Malt</t>
+        </is>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH72" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="AJ72" t="n">
         <v>80</v>
       </c>
-      <c r="V72" t="n">
-        <v>80</v>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X72" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>Swaen Munich Light</t>
-        </is>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="AH72" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>75.37</v>
-      </c>
       <c r="AK72" t="n">
-        <v>11.7</v>
+        <v>9.6</v>
       </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
@@ -9799,12 +9767,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9814,80 +9782,73 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1781339589491</v>
+        <v>1706434202728</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.5</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="Q73" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X73" t="b">
         <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.36</v>
+        <v>-2.29</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>1.59</v>
+        <v>6.82</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.034</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>73.9130435</v>
+        <v>1.036</v>
       </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
@@ -9898,7 +9859,9 @@
       <c r="AO73" t="inlineStr"/>
       <c r="AP73" t="inlineStr"/>
       <c r="AQ73" t="inlineStr"/>
-      <c r="AR73" t="inlineStr"/>
+      <c r="AR73" t="b">
+        <v>0</v>
+      </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr"/>
     </row>
@@ -9918,35 +9881,55 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>default-4c1345c</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1712314604140</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
-      </c>
-      <c r="M74" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.83</v>
+      </c>
       <c r="P74" t="n">
         <v>1.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.8527919</v>
+        <v>1.8</v>
       </c>
       <c r="S74" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Acidulated</t>
         </is>
       </c>
       <c r="X74" t="b">
@@ -9955,15 +9938,18 @@
       <c r="Y74" t="n">
         <v>0</v>
       </c>
+      <c r="Z74" t="n">
+        <v>-0.18</v>
+      </c>
       <c r="AB74" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="AC74" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® Extra Pale</t>
+          <t>Acidulated</t>
         </is>
       </c>
       <c r="AE74" t="b">
@@ -9971,30 +9957,34 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
+          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>68.18000000000001</v>
+        <v>2.27</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.038</v>
+        <v>1.03</v>
       </c>
       <c r="AJ74" t="n">
-        <v>81.5</v>
+        <v>65.2</v>
       </c>
       <c r="AK74" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AL74" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
@@ -10012,12 +10002,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10028,80 +10018,66 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>13.18</v>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="P75" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
-        <v>3.9593909</v>
-      </c>
-      <c r="S75" t="n">
-        <v>50</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X75" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="n">
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Pale Malt, Maris Otter</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH75" t="n">
         <v>100</v>
       </c>
-      <c r="AC75" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>Vienna Malt</t>
-        </is>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="AH75" t="n">
-        <v>22.73</v>
-      </c>
       <c r="AI75" t="n">
-        <v>1.037</v>
+        <v>1.03795</v>
       </c>
       <c r="AJ75" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>9.6</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>Maris Otter</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
@@ -10114,17 +10090,21 @@
       <c r="AQ75" t="inlineStr"/>
       <c r="AR75" t="inlineStr"/>
       <c r="AS75" t="inlineStr"/>
-      <c r="AT75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10134,52 +10114,52 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1706434202728</v>
+        <v>1781339591476</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2.10.5</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X76" t="b">
         <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>-2.29</v>
+        <v>6.7</v>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE76" t="b">
@@ -10188,19 +10168,22 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>6.82</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.036</v>
+        <v>1.0368</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>80</v>
       </c>
       <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
@@ -10211,21 +10194,19 @@
       <c r="AO76" t="inlineStr"/>
       <c r="AP76" t="inlineStr"/>
       <c r="AQ76" t="inlineStr"/>
-      <c r="AR76" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR76" t="inlineStr"/>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10235,108 +10216,76 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>default-4c1345c</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1712314604140</v>
+        <v>1781339591852</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>2</v>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L77" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P77" t="n">
-        <v>1.5</v>
+        <v>0.34</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X77" t="b">
         <v>0</v>
       </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
       <c r="Z77" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
-        </is>
-      </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>2.27</v>
+        <v>11.11</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.03</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ77" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -10354,12 +10303,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10367,74 +10316,73 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>default-132c22b</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1772634460383</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2.20.2</t>
+        </is>
+      </c>
       <c r="L78" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+        <v>0.21</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.22</v>
+      </c>
       <c r="Q78" t="n">
-        <v>3</v>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Base (Maris Otter)</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X78" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Pale Malt, Maris Otter</t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr"/>
+          <t>Sugar, Table (Sucrose)</t>
+        </is>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
       <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
+      <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="AJ78" t="n">
         <v>100</v>
       </c>
-      <c r="AI78" t="n">
-        <v>1.03795</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Maris Otter</t>
-        </is>
-      </c>
+      <c r="AM78" t="inlineStr"/>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr"/>
@@ -10442,11 +10390,7 @@
       <c r="AQ78" t="inlineStr"/>
       <c r="AR78" t="inlineStr"/>
       <c r="AS78" t="inlineStr"/>
-      <c r="AT78" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="AT78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10466,26 +10410,26 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
+          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1781339591476</v>
+        <v>1785061180905</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -10493,25 +10437,42 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.4</v>
+        <v>0.11</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
+      </c>
+      <c r="S79" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>80</v>
+      </c>
+      <c r="V79" t="n">
+        <v>80</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X79" t="b">
         <v>0</v>
       </c>
+      <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>6.7</v>
+        <v>2.19</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE79" t="b">
@@ -10524,13 +10485,16 @@
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>78.43000000000001</v>
+        <v>3.59</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.0368</v>
+        <v>1.035</v>
       </c>
       <c r="AJ79" t="n">
-        <v>80</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="inlineStr">
@@ -10553,12 +10517,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash Mosaic</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10568,26 +10532,26 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1781339591852</v>
+        <v>1785061181508</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -10595,25 +10559,25 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.34</v>
+        <v>3</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X80" t="b">
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE80" t="b">
@@ -10626,13 +10590,13 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ80" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL80" t="inlineStr"/>
       <c r="AM80" t="inlineStr">
@@ -10655,12 +10619,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash shoddy</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10670,71 +10634,81 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>default-132c22b</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1772634460383</v>
+        <v>1785061181508</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>1.9</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Base (Pilsner)</t>
+        </is>
       </c>
       <c r="X81" t="b">
         <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Sugar, Table (Sucrose)</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
       <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="AH81" t="n">
-        <v>6.86</v>
+        <v>100</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.046</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ81" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr"/>
@@ -10744,334 +10718,8 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr"/>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Saison</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Fermentable</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>default-c454dca637a</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>1785061180905</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S82" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U82" t="n">
-        <v>80</v>
-      </c>
-      <c r="V82" t="n">
-        <v>80</v>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X82" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>Swaen Munich Light</t>
-        </is>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="AH82" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr"/>
-      <c r="AP82" t="inlineStr"/>
-      <c r="AQ82" t="inlineStr"/>
-      <c r="AR82" t="inlineStr"/>
-      <c r="AS82" t="inlineStr"/>
-      <c r="AT82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Smash Mosaic</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Fermentable</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>1785061181508</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>Swaen Pilsner</t>
-        </is>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="AH83" t="n">
-        <v>100</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>1.0368</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr"/>
-      <c r="AP83" t="inlineStr"/>
-      <c r="AQ83" t="inlineStr"/>
-      <c r="AR83" t="inlineStr"/>
-      <c r="AS83" t="inlineStr"/>
-      <c r="AT83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Smash shoddy</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Fermentable</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>1785061181508</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="L84" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X84" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>Swaen Pilsner</t>
-        </is>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="inlineStr"/>
-      <c r="AG84" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="AH84" t="n">
-        <v>100</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>1.0368</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr"/>
-      <c r="AP84" t="inlineStr"/>
-      <c r="AQ84" t="inlineStr"/>
-      <c r="AR84" t="inlineStr"/>
-      <c r="AS84" t="inlineStr"/>
-      <c r="AT84" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AT84"/>
+  <autoFilter ref="A1:AT81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12166,7 +11814,7 @@
         <v>5.6</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
         <v>5.59</v>
@@ -12178,7 +11826,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.8</v>
+        <v>20.3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -12227,24 +11875,24 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
+          <t>natsgiFiBiltVb8LI7CaypwjHBmxN2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+          <t>{"_nanoseconds": 673000000, "_seconds": 1775807165}</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1719746363473</v>
+        <v>1775807165673</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="AL11" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
@@ -12288,7 +11936,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -12311,7 +11959,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -12386,7 +12034,7 @@
         <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
         <v>5.59</v>
@@ -12398,7 +12046,7 @@
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.7</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -12420,8 +12068,11 @@
           <t>Saaz, Hallertauer Mittelfrueh</t>
         </is>
       </c>
+      <c r="Y13" t="n">
+        <v>99</v>
+      </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -12435,7 +12086,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -12447,26 +12098,25 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
+          <t>natsgiFiBiltVb8LI7CaypwjHBmxN2</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+          <t>{"_nanoseconds": 673000000, "_seconds": 1775807165}</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1719746363473</v>
+        <v>1775807165673</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="AL13" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
+        <v>50</v>
+      </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
@@ -23163,16 +22813,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>vjR3TZSLVuLk8qB9CNQnCBEGksFtLx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 652000000, "_seconds": 1786789729}</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1781339598782</v>
+        <v>1786789729652</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -23180,13 +22830,13 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>44</v>
+        <v>38.5</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -23247,16 +22897,16 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>ZoNtSHVvqHcJXO4uTvjhGVWtnZpcPQ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 135000000, "_seconds": 1786789729}</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1781339597373</v>
+        <v>1786789729135</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -23264,14 +22914,14 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>941.2</v>
+        <v>933.2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -23332,16 +22982,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>cUtlWL0SE56LvTXQN0VkwAWelrEQMz</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 122000000, "_seconds": 1786789730}</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1781339599470</v>
+        <v>1786789730122</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -23358,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>342.5</v>
+        <v>338.5</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$139</definedName>
@@ -775,10 +775,10 @@
         <v>5.12</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>25.6</v>
+        <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>12</v>
@@ -797,7 +797,8 @@
           <t>First time using Apres Ski yeast. 
 Spund later in fermentation up to 12 psi
 Pitch 22 grams yeast
-No gelatine</t>
+No gelatine
+First time using ISY Enhance.</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT86"/>
+  <dimension ref="A1:AT87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3445,31 +3446,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 218000000, "_seconds": 1784057842}</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>default-c4dd41c950d</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AXp7oOluCAHfEYcypMwZBoIFWG2sY2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 217000000, "_seconds": 1784057842}</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1784057842217</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Base (Pilsner)</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Lager</t>
         </is>
       </c>
       <c r="AE12" t="b">
@@ -3482,7 +3506,7 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>87.09999999999999</v>
+        <v>64.52</v>
       </c>
       <c r="AI12" t="n">
         <v>1.0368</v>
@@ -3524,54 +3548,31 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>vNwfSmBlJ1e4z5jdNJOlLtSxOILZid</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 15000000, "_seconds": 1785061182}</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1785061182015</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.4</v>
-      </c>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE13" t="b">
@@ -3584,13 +3585,13 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>8.06</v>
+        <v>22.58</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr">
@@ -3628,26 +3629,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
+          <t>vNwfSmBlJ1e4z5jdNJOlLtSxOILZid</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
+          <t>{"_nanoseconds": 15000000, "_seconds": 1785061182}</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1785061180905</v>
+        <v>1785061182015</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -3655,42 +3656,25 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>80</v>
-      </c>
-      <c r="V14" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X14" t="b">
         <v>0</v>
       </c>
-      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE14" t="b">
@@ -3703,16 +3687,13 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>4.84</v>
+        <v>8.06</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr">
@@ -3735,12 +3716,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
+          <t>AlNro2l8joSt8O98vSwLNZqS08yafE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>London Pub Gen 2 Amber Ale</t>
+          <t>Kalahari lager</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3750,52 +3731,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1721546982716</v>
+        <v>1785061180905</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>0.15</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>6.6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>80</v>
+      </c>
+      <c r="V15" t="n">
+        <v>80</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X15" t="b">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>-2.59</v>
+        <v>2.19</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE15" t="b">
@@ -3804,19 +3802,25 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>74.84999999999999</v>
+        <v>4.84</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>75.37</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -3847,84 +3851,75 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>default-60a8af8</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>default-sabmjufsad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1721546982716</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
       <c r="Q16" t="n">
-        <v>7.614213</v>
-      </c>
-      <c r="S16" t="n">
-        <v>50</v>
-      </c>
-      <c r="U16" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X16" t="b">
         <v>0</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.5</v>
+      <c r="Z16" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Munich I</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
-        </is>
-      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>14.97</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Amber Liquid Extract</t>
-        </is>
-      </c>
+        <v>1.036</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -3934,9 +3929,7 @@
       </c>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
@@ -3960,34 +3953,29 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>default-aaaccad</t>
+          <t>default-60a8af8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>7.614213</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="U17" t="n">
+        <v>78</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X17" t="b">
@@ -3997,14 +3985,14 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Carahell</t>
+          <t>Munich I</t>
         </is>
       </c>
       <c r="AE17" t="b">
@@ -4012,7 +4000,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -4021,18 +4009,22 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>5.99</v>
+        <v>14.97</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.035</v>
+        <v>1.038</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.73999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Amber Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM17" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -4045,7 +4037,9 @@
       </c>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
@@ -4069,7 +4063,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>default-741be46</t>
+          <t>default-aaaccad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -4080,14 +4074,16 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.15</v>
+      </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4104,14 +4100,14 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Caramunich II</t>
+          <t>Carahell</t>
         </is>
       </c>
       <c r="AE18" t="b">
@@ -4119,7 +4115,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>German crystal malt. Adds maltiness, aroma, color.</t>
+          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -4128,7 +4124,7 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
       <c r="AI18" t="n">
         <v>1.035</v>
@@ -4176,7 +4172,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-741be46</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -4187,23 +4183,21 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.05</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>558.375635</v>
+        <v>63</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X19" t="b">
@@ -4213,14 +4207,14 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Caramunich II</t>
         </is>
       </c>
       <c r="AE19" t="b">
@@ -4228,7 +4222,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>German crystal malt. Adds maltiness, aroma, color.</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -4237,16 +4231,16 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>2.99</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="AJ19" t="n">
-        <v>77.90000000000001</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="AK19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr">
@@ -4261,9 +4255,7 @@
       </c>
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
@@ -4271,12 +4263,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
+          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rice beer</t>
+          <t>London Pub Gen 2 Amber Ale</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4284,78 +4276,85 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1778997165061</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
+          <t>default-b5ffdd1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0.04</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.9</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X20" t="b">
         <v>0</v>
       </c>
-      <c r="Z20" t="n">
-        <v>7.7</v>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>64.52</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ20" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>10</v>
       </c>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -4365,7 +4364,9 @@
       </c>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
+      <c r="AQ20" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
@@ -4386,31 +4387,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>default-7c1aab5</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1778997165061</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="L21" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.7</v>
+      </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Rice, Flaked</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE21" t="b">
@@ -4419,20 +4443,24 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>24.19</v>
+        <v>64.52</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.0322</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ21" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN21" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -4461,54 +4489,31 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1776345923984</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
-      </c>
+          <t>default-7c1aab5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.45</v>
-      </c>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Rice, Flaked</t>
         </is>
       </c>
       <c r="AE22" t="b">
@@ -4517,24 +4522,20 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>8.06</v>
+        <v>24.19</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.03588</v>
+        <v>1.0322</v>
       </c>
       <c r="AJ22" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
+      <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -4565,102 +4566,76 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
+          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1778997166131</v>
+        <v>1776345923984</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+          <t>3.0.0</t>
+        </is>
       </c>
       <c r="L23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.5228426</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X23" t="b">
         <v>0</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
       <c r="Z23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Dextrin Malt</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>Used to provide extra body to beer and to improve head retention</t>
-        </is>
-      </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>3.23</v>
+        <v>8.06</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.037</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -4678,12 +4653,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
+          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kolserig</t>
+          <t>Rice beer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4691,55 +4666,104 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1723974349}</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>default-U47qukVpb3qP1tD63NJOeAyGA4OyAv</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>K5gwRLYk54aSlKSRKHA3WGx4VwYnsI</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 131000000, "_seconds": 1778997166}</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1778997166131</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" t="n">
-        <v>2.83</v>
+        <v>0.1</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>1.5228426</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7</v>
+      </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Dextrin Malt</t>
         </is>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Used to provide extra body to beer and to improve head retention</t>
+        </is>
+      </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>81.56</v>
+        <v>3.23</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.0368</v>
+        <v>1.037</v>
       </c>
       <c r="AJ24" t="n">
         <v>80</v>
       </c>
+      <c r="AK24" t="n">
+        <v>10</v>
+      </c>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -4773,7 +4797,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -4781,20 +4805,20 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.64</v>
+        <v>2.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE25" t="b">
@@ -4807,13 +4831,13 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>18.44</v>
+        <v>81.56</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ25" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr">
@@ -4836,12 +4860,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
+          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>London Pub Gen 1 Stout saved by Bond</t>
+          <t>Kolserig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4849,104 +4873,55 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>default-e6ba5b8</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1721546982714</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>1.5</v>
+        <v>0.64</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2994924</v>
-      </c>
-      <c r="S26" t="n">
-        <v>53</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
-        </is>
-      </c>
-      <c r="X26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>-4.59</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.5</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Finest Maris Otter® Ale Malt</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
-        </is>
-      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>66.89</v>
+        <v>18.44</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.038</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ26" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -4979,53 +4954,51 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 429000000, "_seconds": 1697269073}</t>
+          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>default-1f44c9e</t>
+          <t>default-e6ba5b8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>F1TM4o4Xs8cgfF95wPoLjkPxbCpQ9w</t>
+          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 155000000, "_seconds": 1704369569}</t>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1704369569155</v>
+        <v>1721546982714</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.87</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.7</v>
+        <v>3.2994924</v>
       </c>
       <c r="S27" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base (Maris Otter)</t>
         </is>
       </c>
       <c r="X27" t="b">
@@ -5035,17 +5008,17 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>-4.59</v>
       </c>
       <c r="AB27" t="n">
         <v>100</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Pilsner</t>
+          <t>Finest Maris Otter® Ale Malt</t>
         </is>
       </c>
       <c r="AE27" t="b">
@@ -5053,34 +5026,30 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Pilsner base malt for all pilsners, lagers. Highly modified malt.</t>
+          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>16.72</v>
+        <v>66.89</v>
       </c>
       <c r="AI27" t="n">
         <v>1.038</v>
       </c>
       <c r="AJ27" t="n">
-        <v>82.23</v>
+        <v>81.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Pilsner Liquid Extract</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -5111,35 +5080,55 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 429000000, "_seconds": 1697269073}</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>default-1f44c9e</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>F1TM4o4Xs8cgfF95wPoLjkPxbCpQ9w</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 155000000, "_seconds": 1704369569}</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1704369569155</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2.10.4</t>
+        </is>
+      </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.87</v>
+      </c>
       <c r="P28" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>558.375635</v>
+        <v>1.7</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X28" t="b">
@@ -5148,15 +5137,18 @@
       <c r="Y28" t="n">
         <v>0</v>
       </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
       <c r="AB28" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="AC28" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Pilsner</t>
         </is>
       </c>
       <c r="AE28" t="b">
@@ -5164,7 +5156,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>Pilsner base malt for all pilsners, lagers. Highly modified malt.</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -5173,18 +5165,22 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>7.36</v>
+        <v>16.72</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.036</v>
+        <v>1.038</v>
       </c>
       <c r="AJ28" t="n">
-        <v>77.90000000000001</v>
+        <v>82.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL28" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Pilsner Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM28" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -5197,9 +5193,7 @@
       </c>
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr"/>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr"/>
@@ -5223,7 +5217,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>default-741be46</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -5234,21 +5228,21 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>63</v>
+        <v>558.375635</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X29" t="b">
@@ -5258,40 +5252,40 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Carafa Special II</t>
+        </is>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK29" t="n">
         <v>10</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Caramunich II</t>
-        </is>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>German crystal malt. Adds maltiness, aroma, color.</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>75.73999999999999</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
       </c>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr">
@@ -5306,7 +5300,9 @@
       </c>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
+      <c r="AQ29" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr"/>
@@ -5330,52 +5326,80 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>default-d2c0778</t>
+          <t>default-741be46</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" t="n">
         <v>0.1</v>
       </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="n">
-        <v>1.4</v>
+        <v>63</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.6</v>
+      </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Oats, Flaked</t>
+          <t>Caramunich II</t>
         </is>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>German crystal malt. Adds maltiness, aroma, color.</t>
+        </is>
+      </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH30" t="n">
         <v>3.34</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.0391</v>
+        <v>1.035</v>
       </c>
       <c r="AJ30" t="n">
-        <v>85</v>
+        <v>75.73999999999999</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
       </c>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Briess</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -5409,80 +5433,52 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>default-fc0f80b</t>
+          <t>default-d2c0778</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>415</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Roasted</t>
-        </is>
-      </c>
-      <c r="X31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.1</v>
-      </c>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Carafa II</t>
+          <t>Oats, Flaked</t>
         </is>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>Chocolate malt. Dark beers, Alts, Bockbiers. Adds color and aroma.</t>
-        </is>
-      </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>2.34</v>
+        <v>3.34</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.036</v>
+        <v>1.0391</v>
       </c>
       <c r="AJ31" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Briess</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -5500,12 +5496,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
+          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Marigold Lager</t>
+          <t>London Pub Gen 1 Stout saved by Bond</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5516,52 +5512,80 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-fc0f80b</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.9</v>
+        <v>415</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.1</v>
+      </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa II</t>
         </is>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Chocolate malt. Dark beers, Alts, Bockbiers. Adds color and aroma.</t>
+        </is>
+      </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>100</v>
+        <v>2.34</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ32" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>10</v>
       </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -5579,12 +5603,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
+          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Marigold Lager</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5592,36 +5616,18 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>default-c3ff8bb88f9</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1778997165061</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>1.9</v>
@@ -5631,12 +5637,7 @@
           <t>Base (Pilsner)</t>
         </is>
       </c>
-      <c r="X33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="X33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
           <t>Swaen Pilsner</t>
@@ -5652,7 +5653,7 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>26.25</v>
+        <v>100</v>
       </c>
       <c r="AI33" t="n">
         <v>1.0368</v>
@@ -5696,69 +5697,52 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jr8QUoFHfyKXPhn1IjtiaA3GZwRjfZ</t>
+          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 385000000, "_seconds": 1777108191}</t>
+          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1777108191385</v>
+        <v>1778997165061</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="P34" t="n">
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S34" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>80</v>
-      </c>
-      <c r="V34" t="n">
-        <v>80</v>
+        <v>1.9</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X34" t="b">
         <v>0</v>
       </c>
-      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE34" t="b">
@@ -5771,16 +5755,13 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>15.75</v>
+        <v>26.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.035</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ34" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>11.7</v>
+        <v>80</v>
       </c>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr">
@@ -5818,26 +5799,26 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+          <t>Jr8QUoFHfyKXPhn1IjtiaA3GZwRjfZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+          <t>{"_nanoseconds": 385000000, "_seconds": 1777108191}</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1776345923984</v>
+        <v>1777108191385</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -5847,23 +5828,40 @@
       <c r="L35" t="n">
         <v>0.6</v>
       </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Q35" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>80</v>
+      </c>
+      <c r="V35" t="n">
+        <v>80</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X35" t="b">
         <v>0</v>
       </c>
+      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE35" t="b">
@@ -5879,10 +5877,13 @@
         <v>15.75</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.03588</v>
+        <v>1.035</v>
       </c>
       <c r="AJ35" t="n">
-        <v>78</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr">
@@ -5918,83 +5919,78 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>default-96t8Xs5OLBpW9y5feB0tUbwyNtbfO4</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1776345923984</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
       </c>
       <c r="L36" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.5380711</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X36" t="b">
         <v>0</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>11</v>
+      <c r="Z36" t="n">
+        <v>3.45</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Flaked Torrefied Oats</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
-        </is>
-      </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>12.6</v>
+        <v>15.75</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.032</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ36" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -6025,52 +6021,31 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>default-0aa30343c0c</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>JLLnm9cGPVv3337nwYsF4XU4bmE8yr</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 206000000, "_seconds": 1776345941}</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1776345941206</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
+          <t>default-96t8Xs5OLBpW9y5feB0tUbwyNtbfO4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>2.5380711</v>
       </c>
       <c r="S37" t="n">
-        <v>76</v>
-      </c>
-      <c r="U37" t="n">
-        <v>81</v>
-      </c>
-      <c r="V37" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6080,19 +6055,18 @@
       <c r="X37" t="b">
         <v>0</v>
       </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="n">
-        <v>4</v>
+      <c r="Y37" t="n">
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Swaen Ale</t>
+          <t>Flaked Torrefied Oats</t>
         </is>
       </c>
       <c r="AE37" t="b">
@@ -6100,30 +6074,30 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>10.5</v>
+        <v>12.6</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.037</v>
+        <v>1.032</v>
       </c>
       <c r="AJ37" t="n">
-        <v>80.13</v>
+        <v>70</v>
       </c>
       <c r="AK37" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -6156,26 +6130,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
+          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>default-29dda1b5335</t>
+          <t>default-0aa30343c0c</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bvta1UbScHCOHOL3y0bkomTlBk4ToI</t>
+          <t>JLLnm9cGPVv3337nwYsF4XU4bmE8yr</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 566000000, "_seconds": 1776346236}</t>
+          <t>{"_nanoseconds": 206000000, "_seconds": 1776345941}</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1776346236566</v>
+        <v>1776345941206</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -6183,44 +6157,71 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>329.949239</v>
+        <v>3.6</v>
+      </c>
+      <c r="S38" t="n">
+        <v>76</v>
+      </c>
+      <c r="U38" t="n">
+        <v>81</v>
+      </c>
+      <c r="V38" t="n">
+        <v>80</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X38" t="b">
         <v>0</v>
       </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>BlackSwaen Coffee</t>
+          <t>Swaen Ale</t>
         </is>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
+        </is>
+      </c>
       <c r="AG38" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>9.19</v>
+        <v>10.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.028</v>
+        <v>1.037</v>
       </c>
       <c r="AJ38" t="n">
-        <v>60.8695652</v>
+        <v>80.13</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>11.5</v>
       </c>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr">
@@ -6235,9 +6236,7 @@
       </c>
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="n">
-        <v>244.1</v>
-      </c>
+      <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr"/>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr"/>
@@ -6260,26 +6259,26 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-29dda1b5335</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>bvta1UbScHCOHOL3y0bkomTlBk4ToI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 566000000, "_seconds": 1776346236}</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1776345994305</v>
+        <v>1776346236566</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -6287,48 +6286,44 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="Q39" t="n">
-        <v>61</v>
+        <v>329.949239</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X39" t="b">
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>BlackSwaen Coffee</t>
         </is>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>7.35</v>
+        <v>9.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.034</v>
+        <v>1.028</v>
       </c>
       <c r="AJ39" t="n">
-        <v>73.9130435</v>
+        <v>60.8695652</v>
       </c>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr">
@@ -6343,7 +6338,9 @@
       </c>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
+      <c r="AQ39" t="n">
+        <v>244.1</v>
+      </c>
       <c r="AR39" t="inlineStr"/>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
@@ -6366,71 +6363,52 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>jWuqIkMLK24jzylCQapUkVKL5iFO6T</t>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 551000000, "_seconds": 1777108193}</t>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1777108193551</v>
+        <v>1776345994305</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>3.0.0</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>1.5</v>
+        <v>0.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X40" t="b">
         <v>0</v>
       </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
       <c r="Z40" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE40" t="b">
@@ -6438,30 +6416,27 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>2.62</v>
+        <v>7.35</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.036</v>
+        <v>1.034</v>
       </c>
       <c r="AJ40" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>10</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -6471,9 +6446,7 @@
       </c>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="inlineStr"/>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr"/>
@@ -6496,30 +6469,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 546000000, "_seconds": 1712314605}</t>
+          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>default-Q0GFlvnA7LLqVkkfYBAXCniMcRZwnf</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>7aV7RCW73FffCIp6YwXe3Ui8TTLeJE</t>
+          <t>jWuqIkMLK24jzylCQapUkVKL5iFO6T</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 122000000, "_seconds": 1778682369}</t>
+          <t>{"_nanoseconds": 551000000, "_seconds": 1777108193}</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1778682369122</v>
+        <v>1777108193551</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -6530,17 +6503,17 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.8</v>
+        <v>558.375635</v>
       </c>
       <c r="S41" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X41" t="b">
@@ -6550,17 +6523,17 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AB41" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Malteurop Pilsen</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE41" t="b">
@@ -6568,30 +6541,30 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>The lightest of our two-row base malts, Malteurop Pilsen malt imparts a sweet and subtle malt flavor and a straw yellow to light golden color. It can be used up to 100% in all beer styles and provides a perfect canvas for other specialty malts.</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.038</v>
+        <v>1.036</v>
       </c>
       <c r="AJ41" t="n">
-        <v>81.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK41" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Malteurop Malting Co.</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -6601,22 +6574,22 @@
       </c>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="b">
-        <v>1</v>
-      </c>
+      <c r="AQ41" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
+          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lager pseudo idea ii</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6626,79 +6599,102 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+          <t>{"_nanoseconds": 546000000, "_seconds": 1712314605}</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
+          <t>default-Q0GFlvnA7LLqVkkfYBAXCniMcRZwnf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+          <t>7aV7RCW73FffCIp6YwXe3Ui8TTLeJE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 122000000, "_seconds": 1778682369}</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1721546982716</v>
+        <v>1778682369122</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="P42" t="n">
         <v>0.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1.8</v>
+      </c>
+      <c r="S42" t="n">
+        <v>146</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X42" t="b">
         <v>0</v>
       </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
       <c r="Z42" t="n">
-        <v>-2.59</v>
+        <v>1</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.4</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Malteurop Pilsen</t>
         </is>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>The lightest of our two-row base malts, Malteurop Pilsen malt imparts a sweet and subtle malt flavor and a straw yellow to light golden color. It can be used up to 100% in all beer styles and provides a perfect canvas for other specialty malts.</t>
+        </is>
+      </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>92.59</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.035</v>
+        <v>1.038</v>
       </c>
       <c r="AJ42" t="n">
-        <v>76</v>
+        <v>81.7</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>11.3</v>
       </c>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Malteurop Malting Co.</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -6709,7 +6705,9 @@
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
+      <c r="AR42" t="b">
+        <v>1</v>
+      </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
     </row>
@@ -6729,89 +6727,81 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>default-cdbfbd6</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>0</v>
+          <t>default-sabmjufsad</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1721546982716</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
       </c>
       <c r="L43" t="n">
-        <v>0.14</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>30</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X43" t="b">
         <v>0</v>
       </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.8</v>
+      <c r="Z43" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Melanoidin</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
-        </is>
-      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>4.32</v>
+        <v>92.59</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
       <c r="AJ43" t="n">
-        <v>80.06999999999999</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Carared</t>
-        </is>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
@@ -6845,50 +6835,88 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>default-08f456e</t>
+          <t>default-cdbfbd6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Oats, Flaked</t>
+          <t>Melanoidin</t>
         </is>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
+        </is>
+      </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>3.09</v>
+        <v>4.32</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.0368</v>
+        <v>1.037</v>
       </c>
       <c r="AJ44" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
+        <v>80.06999999999999</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Carared</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Weyermann</t>
+        </is>
+      </c>
       <c r="AN44" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -6904,12 +6932,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>First Lager v3</t>
+          <t>Lager pseudo idea ii</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6920,7 +6948,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>default-kTJTLZIhyeFDXlOIOLxrPWfGnU8z4A</t>
+          <t>default-08f456e</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -6928,45 +6956,120 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="L45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Oats, Flaked</t>
+        </is>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AH45" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>First Lager v3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>default-kTJTLZIhyeFDXlOIOLxrPWfGnU8z4A</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="L46" t="n">
         <v>2</v>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="P45" t="n">
+      <c r="M46" t="inlineStr"/>
+      <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q46" t="n">
         <v>1.9</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U46" t="n">
         <v>80</v>
       </c>
-      <c r="V45" t="n">
+      <c r="V46" t="n">
         <v>82</v>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Base (Pilsner)</t>
         </is>
       </c>
-      <c r="X45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="AB45" t="n">
+      <c r="X46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="AB46" t="n">
         <v>100</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AC46" t="n">
         <v>5</v>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>Bohemian Pilsner</t>
         </is>
       </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>Made from the finest Bohemian malting quality barley (Barley varieties Bojos and Malz), this Pilsner malt is characterized by the typical sententious core notes of the original barley varieties.
 Sensory: nutty malt aroma, malty-sweet
@@ -6975,160 +7078,47 @@
 Product Sheet: https://www.weyermann.de/wp-content/uploads/2021/02/Weyermann_Bohemian_Pilsner_Malt_Specification.pdf</t>
         </is>
       </c>
-      <c r="AG45" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>Bohemia</t>
         </is>
       </c>
-      <c r="AH45" t="n">
+      <c r="AH46" t="n">
         <v>71.94</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AI46" t="n">
         <v>1.035</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AJ46" t="n">
         <v>75.05</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AK46" t="n">
         <v>10.75</v>
       </c>
-      <c r="AL45" t="inlineStr">
+      <c r="AL46" t="inlineStr">
         <is>
           <t>Weyermann Floor-Malted Bohemian Pilsner Malt</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AM46" t="inlineStr">
         <is>
           <t>Weyermann</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
+      <c r="AN46" t="inlineStr">
         <is>
           <t>Grain</t>
         </is>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>pilsners</t>
         </is>
       </c>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="n">
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="n">
         <v>1.95</v>
       </c>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>First Lager v3</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Fermentable</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>default-4d8b7c4</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>50</v>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>Vienna Malt</t>
-        </is>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>Vienna base malt - used in many continental beer styles. Full bodied, golden color.</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="AH46" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>82.23</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Weyermann</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr"/>
@@ -7152,7 +7142,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-4d8b7c4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -7163,23 +7153,23 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X47" t="b">
@@ -7189,14 +7179,14 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE47" t="b">
@@ -7204,7 +7194,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+          <t>Vienna base malt - used in many continental beer styles. Full bodied, golden color.</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -7213,18 +7203,22 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>10.07</v>
+        <v>17.99</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ47" t="n">
-        <v>80.06999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM47" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -7245,12 +7239,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>London Pub gen 2 Weskus</t>
+          <t>First Lager v3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7258,78 +7252,85 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1721546982716</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
+          <t>default-1482365</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.6</v>
+        <v>0.28</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q48" t="n">
         <v>2</v>
       </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X48" t="b">
         <v>0</v>
       </c>
-      <c r="Z48" t="n">
-        <v>-2.59</v>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>4.9</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+        </is>
+      </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>79.27</v>
+        <v>10.07</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.035</v>
+        <v>1.037</v>
       </c>
       <c r="AJ48" t="n">
-        <v>76</v>
+        <v>80.06999999999999</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
       </c>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
@@ -7362,102 +7363,76 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 248000000, "_seconds": 1714216056}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CPkrJFvR0z03f2qIouoRdQwhmALFMG</t>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 27000000, "_seconds": 1723974350}</t>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1723974350027</v>
+        <v>1721546982716</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>2.10.6</t>
         </is>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.9593909</v>
-      </c>
-      <c r="S49" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X49" t="b">
         <v>0</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
       <c r="Z49" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>4.5</v>
+        <v>-2.59</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
-        </is>
-      </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>15.24</v>
+        <v>79.27</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
       <c r="AJ49" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>9.6</v>
+        <v>76</v>
       </c>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -7488,37 +7463,53 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 248000000, "_seconds": 1714216056}</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>default-cdbfbd6</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CPkrJFvR0z03f2qIouoRdQwhmALFMG</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 27000000, "_seconds": 1723974350}</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1723974350027</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.73</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>1.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>3.9593909</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X50" t="b">
@@ -7527,15 +7518,18 @@
       <c r="Y50" t="n">
         <v>0</v>
       </c>
+      <c r="Z50" t="n">
+        <v>-3</v>
+      </c>
       <c r="AB50" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Melanoidin</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE50" t="b">
@@ -7543,34 +7537,30 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>3.96</v>
+        <v>15.24</v>
       </c>
       <c r="AI50" t="n">
         <v>1.037</v>
       </c>
       <c r="AJ50" t="n">
-        <v>80.06999999999999</v>
+        <v>80</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Carared</t>
-        </is>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
@@ -7604,7 +7594,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>default-aaaccad</t>
+          <t>default-cdbfbd6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -7615,14 +7605,16 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M51" t="inlineStr"/>
+        <v>0.13</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.73</v>
+      </c>
       <c r="P51" t="n">
         <v>1.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -7639,14 +7631,14 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Carahell</t>
+          <t>Melanoidin</t>
         </is>
       </c>
       <c r="AE51" t="b">
@@ -7654,7 +7646,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -7663,18 +7655,22 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>1.52</v>
+        <v>3.96</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.035</v>
+        <v>1.037</v>
       </c>
       <c r="AJ51" t="n">
-        <v>75.73999999999999</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AK51" t="n">
         <v>0</v>
       </c>
-      <c r="AL51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Carared</t>
+        </is>
+      </c>
       <c r="AM51" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -7695,12 +7691,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>London Pub gen 2 Weskus</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7711,52 +7707,80 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-aaaccad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" t="n">
-        <v>2.9</v>
+        <v>0.05</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.9</v>
+        <v>13</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carahell</t>
         </is>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+        </is>
+      </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>70.73</v>
+        <v>1.52</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.0368</v>
+        <v>1.035</v>
       </c>
       <c r="AJ52" t="n">
-        <v>80</v>
+        <v>75.73999999999999</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
       </c>
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
@@ -7790,7 +7814,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -7798,20 +7822,20 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X53" t="inlineStr"/>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE53" t="b">
@@ -7824,13 +7848,13 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>19.51</v>
+        <v>70.73</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ53" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr">
@@ -7869,7 +7893,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -7877,39 +7901,20 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="P54" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S54" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U54" t="n">
-        <v>80</v>
-      </c>
-      <c r="V54" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="AC54" t="n">
-        <v>4.6</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE54" t="b">
@@ -7922,16 +7927,13 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>8.539999999999999</v>
+        <v>19.51</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ54" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr">
@@ -7967,77 +7969,72 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1781339589491</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>default-c454dca637a</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S55" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>80</v>
+      </c>
+      <c r="V55" t="n">
+        <v>80</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X55" t="b">
         <v>0</v>
       </c>
-      <c r="Z55" t="n">
-        <v>1.36</v>
+      <c r="Y55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ55" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr">
@@ -8060,12 +8057,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8075,90 +8072,80 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>default-nym-3n456</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1721546982782</v>
+        <v>1781339589491</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
       <c r="Q56" t="n">
-        <v>1.77665</v>
-      </c>
-      <c r="U56" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="V56" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X56" t="b">
         <v>0</v>
       </c>
-      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Barke Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>45.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.035</v>
+        <v>1.034</v>
       </c>
       <c r="AJ56" t="n">
-        <v>76.48</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
@@ -8189,47 +8176,68 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>default-nym-3n456</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1721546982782</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>3.807107</v>
+        <v>1.77665</v>
       </c>
       <c r="U57" t="n">
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="V57" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X57" t="b">
         <v>0</v>
       </c>
       <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
       <c r="AB57" t="n">
         <v>100</v>
       </c>
       <c r="AC57" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Barke Vienna Malt</t>
+          <t>Barke Pilsner</t>
         </is>
       </c>
       <c r="AE57" t="b">
@@ -8242,16 +8250,13 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>32.26</v>
+        <v>45.16</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ57" t="n">
-        <v>74.66</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>10.5</v>
+        <v>76.48</v>
       </c>
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr">
@@ -8266,13 +8271,9 @@
       </c>
       <c r="AO57" t="inlineStr"/>
       <c r="AP57" t="inlineStr"/>
-      <c r="AQ57" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="b">
-        <v>0</v>
-      </c>
+      <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -8294,75 +8295,66 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Q58" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
+        <v>3.807107</v>
+      </c>
+      <c r="U58" t="n">
+        <v>79</v>
+      </c>
+      <c r="V58" t="n">
+        <v>80</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X58" t="b">
         <v>0</v>
       </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y58" t="inlineStr"/>
       <c r="AB58" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Barke Vienna Malt</t>
         </is>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>8.06</v>
+        <v>32.26</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.036</v>
+        <v>1.034</v>
       </c>
       <c r="AJ58" t="n">
-        <v>77.90000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="AK58" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr">
@@ -8378,10 +8370,12 @@
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
       <c r="AQ58" t="n">
-        <v>412.8</v>
+        <v>3.4</v>
       </c>
       <c r="AR58" t="inlineStr"/>
-      <c r="AS58" t="inlineStr"/>
+      <c r="AS58" t="b">
+        <v>0</v>
+      </c>
       <c r="AT58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -8403,7 +8397,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -8416,14 +8410,12 @@
       <c r="L59" t="n">
         <v>0.25</v>
       </c>
-      <c r="M59" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="P59" t="n">
         <v>1.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>558.375635</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -8440,14 +8432,14 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AC59" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE59" t="b">
@@ -8455,7 +8447,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -8467,13 +8459,13 @@
         <v>8.06</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.037</v>
+        <v>1.036</v>
       </c>
       <c r="AJ59" t="n">
-        <v>80.06999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr">
@@ -8488,7 +8480,9 @@
       </c>
       <c r="AO59" t="inlineStr"/>
       <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
+      <c r="AQ59" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR59" t="inlineStr"/>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr"/>
@@ -8512,29 +8506,34 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>default-60a8af8</t>
+          <t>default-1482365</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M60" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q60" t="n">
-        <v>7.614213</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
-      </c>
-      <c r="U60" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X60" t="b">
@@ -8544,14 +8543,14 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AC60" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Munich I</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE60" t="b">
@@ -8559,7 +8558,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
@@ -8568,22 +8567,18 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>6.45</v>
+        <v>8.06</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.038</v>
+        <v>1.037</v>
       </c>
       <c r="AJ60" t="n">
-        <v>82.3</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AK60" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Amber Liquid Extract</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -8596,9 +8591,7 @@
       </c>
       <c r="AO60" t="inlineStr"/>
       <c r="AP60" t="inlineStr"/>
-      <c r="AQ60" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr"/>
@@ -8606,12 +8599,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8622,7 +8615,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-60a8af8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -8630,44 +8623,73 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>1.9</v>
+        <v>7.614213</v>
+      </c>
+      <c r="S61" t="n">
+        <v>50</v>
+      </c>
+      <c r="U61" t="n">
+        <v>78</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
+          <t>Base (Munich)</t>
+        </is>
+      </c>
+      <c r="X61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Munich I</t>
         </is>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+        </is>
+      </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>64.09999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.0368</v>
+        <v>1.038</v>
       </c>
       <c r="AJ61" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="inlineStr"/>
+        <v>82.3</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Amber Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
@@ -8677,7 +8699,9 @@
       </c>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
-      <c r="AQ61" t="inlineStr"/>
+      <c r="AQ61" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr"/>
@@ -8701,7 +8725,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -8709,20 +8733,20 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>0.62</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE62" t="b">
@@ -8735,13 +8759,13 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>19.87</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ62" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr">
@@ -8780,7 +8804,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -8788,39 +8812,20 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="P63" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="Q63" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S63" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U63" t="n">
-        <v>80</v>
-      </c>
-      <c r="V63" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="AC63" t="n">
-        <v>4.6</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE63" t="b">
@@ -8833,16 +8838,13 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>9.619999999999999</v>
+        <v>19.87</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ63" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr">
@@ -8881,80 +8883,74 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>558.375635</v>
+        <v>6.6</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>80</v>
+      </c>
+      <c r="V64" t="n">
+        <v>80</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X64" t="b">
         <v>0</v>
       </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>5</v>
-      </c>
+      <c r="Y64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>6.41</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="AJ64" t="n">
-        <v>77.90000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="AK64" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
@@ -8964,9 +8960,7 @@
       </c>
       <c r="AO64" t="inlineStr"/>
       <c r="AP64" t="inlineStr"/>
-      <c r="AQ64" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ64" t="inlineStr"/>
       <c r="AR64" t="inlineStr"/>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr"/>
@@ -8974,12 +8968,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8987,78 +8981,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>1777108192684</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
+          <t>default-b5ffdd1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.9</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X65" t="b">
         <v>0</v>
       </c>
-      <c r="Z65" t="n">
-        <v>7.8</v>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>3</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>73.95999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ65" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>10</v>
       </c>
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
@@ -9068,10 +9067,10 @@
       </c>
       <c r="AO65" t="inlineStr"/>
       <c r="AP65" t="inlineStr"/>
-      <c r="AQ65" t="inlineStr"/>
-      <c r="AR65" t="b">
-        <v>0</v>
-      </c>
+      <c r="AQ65" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr"/>
     </row>
@@ -9093,52 +9092,52 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1781339591852</v>
+        <v>1777108192684</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X66" t="b">
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.85</v>
+        <v>7.8</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE66" t="b">
@@ -9151,13 +9150,13 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>14.79</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ66" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr">
@@ -9173,7 +9172,9 @@
       <c r="AO66" t="inlineStr"/>
       <c r="AP66" t="inlineStr"/>
       <c r="AQ66" t="inlineStr"/>
-      <c r="AR66" t="inlineStr"/>
+      <c r="AR66" t="b">
+        <v>0</v>
+      </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr"/>
     </row>
@@ -9195,26 +9196,26 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -9222,42 +9223,25 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="P67" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S67" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U67" t="n">
-        <v>80</v>
-      </c>
-      <c r="V67" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X67" t="b">
         <v>0</v>
       </c>
-      <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE67" t="b">
@@ -9270,16 +9254,13 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>8.880000000000001</v>
+        <v>14.79</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ67" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
@@ -9317,75 +9298,91 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1776345994305</v>
+        <v>1781339591050</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S68" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>80</v>
+      </c>
+      <c r="V68" t="n">
+        <v>80</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X68" t="b">
         <v>0</v>
       </c>
+      <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>2</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>2.37</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ68" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr">
@@ -9408,12 +9405,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9423,71 +9420,75 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1781339591476</v>
+        <v>1776345994305</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.8</v>
+        <v>0.08</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.9</v>
+        <v>61</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X69" t="b">
         <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG69" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>87.23</v>
+        <v>2.37</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.0368</v>
+        <v>1.034</v>
       </c>
       <c r="AJ69" t="n">
-        <v>80</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr">
@@ -9525,26 +9526,26 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1781339591050</v>
+        <v>1781339591476</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -9552,42 +9553,25 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="P70" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="Q70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S70" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U70" t="n">
-        <v>80</v>
-      </c>
-      <c r="V70" t="n">
-        <v>80</v>
+        <v>1.9</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X70" t="b">
         <v>0</v>
       </c>
-      <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE70" t="b">
@@ -9600,16 +9584,13 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>10.9</v>
+        <v>87.23</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.035</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ70" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>11.7</v>
+        <v>80</v>
       </c>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr">
@@ -9647,26 +9628,26 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1781339589491</v>
+        <v>1781339591050</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -9674,48 +9655,64 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S71" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>80</v>
+      </c>
+      <c r="V71" t="n">
+        <v>80</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X71" t="b">
         <v>0</v>
       </c>
+      <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>1.36</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>1.87</v>
+        <v>10.9</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ71" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr">
@@ -9738,12 +9735,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9751,52 +9748,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="n">
-        <v>0</v>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1781339589491</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L72" t="n">
-        <v>3</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="P72" t="n">
-        <v>1.5</v>
+        <v>0.06</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.8527919</v>
-      </c>
-      <c r="S72" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X72" t="b">
         <v>0</v>
       </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>4.5</v>
+      <c r="Z72" t="n">
+        <v>1.36</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® Extra Pale</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE72" t="b">
@@ -9804,30 +9803,27 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>68.18000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.038</v>
+        <v>1.034</v>
       </c>
       <c r="AJ72" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>10.1</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
@@ -9861,7 +9857,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -9872,21 +9868,21 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="P73" t="n">
         <v>1.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.9593909</v>
+        <v>1.8527919</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X73" t="b">
@@ -9903,7 +9899,7 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Clear Choice Malt ® Extra Pale</t>
         </is>
       </c>
       <c r="AE73" t="b">
@@ -9911,7 +9907,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
@@ -9920,16 +9916,16 @@
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>22.73</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ73" t="n">
-        <v>80</v>
+        <v>81.5</v>
       </c>
       <c r="AK73" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr">
@@ -9965,75 +9961,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>1706434202728</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2.10.5</t>
-        </is>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>3.9593909</v>
+      </c>
+      <c r="S74" t="n">
+        <v>50</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X74" t="b">
         <v>0</v>
       </c>
-      <c r="Z74" t="n">
-        <v>-2.29</v>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+        </is>
+      </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>6.82</v>
+        <v>22.73</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.036</v>
+        <v>1.037</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>9.6</v>
       </c>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
@@ -10044,9 +10048,7 @@
       <c r="AO74" t="inlineStr"/>
       <c r="AP74" t="inlineStr"/>
       <c r="AQ74" t="inlineStr"/>
-      <c r="AR74" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR74" t="inlineStr"/>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr"/>
     </row>
@@ -10068,108 +10070,73 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>default-4c1345c</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1712314604140</v>
+        <v>1706434202728</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
+          <t>2.10.5</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q75" t="n">
         <v>2</v>
       </c>
-      <c r="L75" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P75" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X75" t="b">
         <v>0</v>
       </c>
-      <c r="Y75" t="n">
-        <v>0</v>
-      </c>
       <c r="Z75" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>4</v>
+        <v>-2.29</v>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
-        </is>
-      </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>2.27</v>
+        <v>6.82</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
+        <v>1.036</v>
+      </c>
+      <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
@@ -10180,19 +10147,21 @@
       <c r="AO75" t="inlineStr"/>
       <c r="AP75" t="inlineStr"/>
       <c r="AQ75" t="inlineStr"/>
-      <c r="AR75" t="inlineStr"/>
+      <c r="AR75" t="b">
+        <v>0</v>
+      </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10200,69 +10169,110 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+          <t>default-4c1345c</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>1712314604140</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
       <c r="L76" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q76" t="n">
-        <v>3</v>
-      </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="X76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>4</v>
+      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Pale Malt, Maris Otter</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
+        </is>
+      </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>100</v>
+        <v>2.27</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.03795</v>
+        <v>1.03</v>
       </c>
       <c r="AJ76" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
+        <v>65.2</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Maris Otter</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
@@ -10275,21 +10285,17 @@
       <c r="AQ76" t="inlineStr"/>
       <c r="AR76" t="inlineStr"/>
       <c r="AS76" t="inlineStr"/>
-      <c r="AT76" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="AT76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10297,78 +10303,69 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>1781339591476</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
-        <v>2.4</v>
-      </c>
+        <v>13.18</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
-        <v>1.9</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X77" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>6.7</v>
-      </c>
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
-        </is>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
+          <t>Pale Malt, Maris Otter</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>78.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.0368</v>
+        <v>1.03795</v>
       </c>
       <c r="AJ77" t="n">
-        <v>80</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Maris Otter</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -10381,7 +10378,11 @@
       <c r="AQ77" t="inlineStr"/>
       <c r="AR77" t="inlineStr"/>
       <c r="AS77" t="inlineStr"/>
-      <c r="AT77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10401,26 +10402,26 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -10428,25 +10429,25 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X78" t="b">
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE78" t="b">
@@ -10459,13 +10460,13 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>11.11</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ78" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="inlineStr">
@@ -10503,71 +10504,81 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>default-132c22b</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1772634460383</v>
+        <v>1781339591852</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1.22</v>
+        <v>0.34</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>5.1</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Base (Vienna)</t>
+        </is>
       </c>
       <c r="X79" t="b">
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Sugar, Table (Sucrose)</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
       <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="AH79" t="n">
-        <v>6.86</v>
+        <v>11.11</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.046</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ79" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr"/>
@@ -10595,101 +10606,71 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-132c22b</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
+          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
+          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1785061180905</v>
+        <v>1772634460383</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.20.2</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="P80" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S80" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U80" t="n">
-        <v>80</v>
-      </c>
-      <c r="V80" t="n">
-        <v>80</v>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
       <c r="X80" t="b">
         <v>0</v>
       </c>
-      <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Sugar, Table (Sucrose)</t>
         </is>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
       <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
+      <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="n">
-        <v>3.59</v>
+        <v>6.86</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.035</v>
+        <v>1.046</v>
       </c>
       <c r="AJ80" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK80" t="n">
-        <v>11.7</v>
+        <v>100</v>
       </c>
       <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
+      <c r="AM80" t="inlineStr"/>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr"/>
@@ -10702,12 +10683,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Smash Mosaic</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10717,26 +10698,26 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
+          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
+          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1785061181508</v>
+        <v>1785061180905</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -10744,25 +10725,42 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3</v>
+        <v>0.11</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
+      </c>
+      <c r="S81" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>80</v>
+      </c>
+      <c r="V81" t="n">
+        <v>80</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X81" t="b">
         <v>0</v>
       </c>
+      <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>4.4</v>
+        <v>2.19</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE81" t="b">
@@ -10775,13 +10773,16 @@
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>100</v>
+        <v>3.59</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.0368</v>
+        <v>1.035</v>
       </c>
       <c r="AJ81" t="n">
-        <v>80</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL81" t="inlineStr"/>
       <c r="AM81" t="inlineStr">
@@ -10804,12 +10805,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Smash shoddy</t>
+          <t>Smash Mosaic</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10906,12 +10907,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Smash shoddy</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10921,26 +10922,26 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 218000000, "_seconds": 1784057842}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>default-c4dd41c950d</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>AXp7oOluCAHfEYcypMwZBoIFWG2sY2</t>
+          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 217000000, "_seconds": 1784057842}</t>
+          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1784057842217</v>
+        <v>1785061181508</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -10948,10 +10949,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -10962,11 +10963,11 @@
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Swaen Lager</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE83" t="b">
@@ -10979,7 +10980,7 @@
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="AI83" t="n">
         <v>1.0368</v>
@@ -11023,26 +11024,26 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 218000000, "_seconds": 1784057842}</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-c4dd41c950d</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>GOG6rzO2xrYYSto1fMsaU5lUVzV9v7</t>
+          <t>AXp7oOluCAHfEYcypMwZBoIFWG2sY2</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 7000000, "_seconds": 1786789728}</t>
+          <t>{"_nanoseconds": 217000000, "_seconds": 1784057842}</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1786789728007</v>
+        <v>1784057842217</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -11050,10 +11051,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -11064,11 +11065,11 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>11.4</v>
+        <v>2</v>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Lager</t>
         </is>
       </c>
       <c r="AE84" t="b">
@@ -11081,7 +11082,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>15.63</v>
+        <v>62.5</v>
       </c>
       <c r="AI84" t="n">
         <v>1.0368</v>
@@ -11125,26 +11126,26 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>vNwfSmBlJ1e4z5jdNJOlLtSxOILZid</t>
+          <t>GOG6rzO2xrYYSto1fMsaU5lUVzV9v7</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 15000000, "_seconds": 1785061182}</t>
+          <t>{"_nanoseconds": 7000000, "_seconds": 1786789728}</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1785061182015</v>
+        <v>1786789728007</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -11155,22 +11156,22 @@
         <v>0.5</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X85" t="b">
         <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE85" t="b">
@@ -11186,10 +11187,10 @@
         <v>15.63</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ85" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="inlineStr">
@@ -11225,83 +11226,78 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="n">
-        <v>0</v>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>vNwfSmBlJ1e4z5jdNJOlLtSxOILZid</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 15000000, "_seconds": 1785061182}</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1785061182015</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L86" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="P86" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.5380711</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Base (Wheat)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X86" t="b">
         <v>0</v>
       </c>
-      <c r="Y86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC86" t="n">
-        <v>10</v>
+      <c r="Z86" t="n">
+        <v>2.4</v>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Torrefied Wheat</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
-        </is>
-      </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>6.25</v>
+        <v>15.63</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.038</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ86" t="n">
-        <v>82</v>
-      </c>
-      <c r="AK86" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
@@ -11316,8 +11312,115 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Kalahari blond</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2.5380711</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Base (Wheat)</t>
+        </is>
+      </c>
+      <c r="X87" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>Torrefied Wheat</t>
+        </is>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH87" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>82</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="inlineStr"/>
+      <c r="AR87" t="inlineStr"/>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT86"/>
+  <autoFilter ref="A1:AT87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12412,7 +12515,7 @@
         <v>5.6</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
         <v>5.59</v>
@@ -12424,7 +12527,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -12522,7 +12625,7 @@
         <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
         <v>5.59</v>
@@ -12534,7 +12637,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -23844,7 +23947,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
@@ -24013,7 +24116,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L21" t="n">
         <v>80</v>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22283,7 +22283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB139"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -24196,7 +24196,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -24282,7 +24282,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -24311,12 +24311,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
+          <t>AlNro2l8joSt8O98vSwLNZqS08yafE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>London Pub Gen 2 Amber Ale</t>
+          <t>Kalahari lager</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -24326,52 +24326,54 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 320000000, "_seconds": 1787845020}</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>FxymQbqWfYaVaT8ypqgApwGcTjOAXm</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>usCupaaCHuKs2M74t9dINjMUyLWSXg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 320000000, "_seconds": 1787845020}</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1704369575930</v>
+        <v>1787845020320</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="b">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
+          <t>ISY Enhabce</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -24381,15 +24383,10 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U24" t="b">
-        <v>1</v>
-      </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -24413,45 +24410,44 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
+          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1723974351111</v>
+        <v>1704369575930</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q25" t="b">
@@ -24475,6 +24471,9 @@
       <c r="U25" t="b">
         <v>1</v>
       </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -24498,26 +24497,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1723974352697</v>
+        <v>1723974351111</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -24525,20 +24524,18 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>80</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="b">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q26" t="b">
@@ -24551,7 +24548,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -24562,9 +24559,6 @@
       <c r="U26" t="b">
         <v>1</v>
       </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -24586,49 +24580,75 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1723974352697</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>80</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-15</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U27" t="b">
         <v>1</v>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>0</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
@@ -24650,52 +24670,32 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1723974355076</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-5adf6e</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-15</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
       <c r="Q28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -24704,12 +24704,12 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -24721,12 +24721,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
+          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rice beer</t>
+          <t>London Pub Gen 2 Amber Ale</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -24736,67 +24736,67 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-90c63c</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>U7Q7AloKFG2MwxuQxE9znDsGScpFBa</t>
+          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 14000000, "_seconds": 1778997168}</t>
+          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1778997168014</v>
+        <v>1723974355076</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="b">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>47</v>
+        <v>-15</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
-      </c>
+          <t>Gelatin</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U29" t="b">
-        <v>1</v>
-      </c>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -24820,26 +24820,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>RsTDDT4iPhBM6HtLnE1sLut1VSfSzy</t>
+          <t>U7Q7AloKFG2MwxuQxE9znDsGScpFBa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 554000000, "_seconds": 1778997167}</t>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1778997168}</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1778997167554</v>
+        <v>1778997168014</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -24847,18 +24847,17 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>943</v>
+        <v>47</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q30" t="b">
@@ -24905,26 +24904,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GMe0y7iJZybWYXIcl3sWc1BgoZQQnT</t>
+          <t>RsTDDT4iPhBM6HtLnE1sLut1VSfSzy</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 359000000, "_seconds": 1778997168}</t>
+          <t>{"_nanoseconds": 554000000, "_seconds": 1778997167}</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1778997168359</v>
+        <v>1778997167554</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -24932,20 +24931,18 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>80</v>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="b">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>344.5</v>
+        <v>943</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q31" t="b">
@@ -24958,7 +24955,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -24992,26 +24989,26 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
+          <t>GMe0y7iJZybWYXIcl3sWc1BgoZQQnT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
+          <t>{"_nanoseconds": 359000000, "_seconds": 1778997168}</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1778997170065</v>
+        <v>1778997168359</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -25019,42 +25016,43 @@
         </is>
       </c>
       <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>80</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U32" t="b">
         <v>1</v>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="b">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -25078,26 +25076,26 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>qQbARGKEUKW4e3IlCSOKSDImAsivc7</t>
+          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 151000000, "_seconds": 1778126952}</t>
+          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1778126952151</v>
+        <v>1778997170065</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -25112,11 +25110,11 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -25127,7 +25125,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -25149,12 +25147,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
+          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kolserig</t>
+          <t>Rice beer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -25164,26 +25162,26 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>U7Q7AloKFG2MwxuQxE9znDsGScpFBa</t>
+          <t>qQbARGKEUKW4e3IlCSOKSDImAsivc7</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 14000000, "_seconds": 1778997168}</t>
+          <t>{"_nanoseconds": 151000000, "_seconds": 1778126952}</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1778997168014</v>
+        <v>1778126952151</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -25191,25 +25189,29 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="b">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -25219,12 +25221,10 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U34" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
@@ -25248,26 +25248,26 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>RsTDDT4iPhBM6HtLnE1sLut1VSfSzy</t>
+          <t>U7Q7AloKFG2MwxuQxE9znDsGScpFBa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 554000000, "_seconds": 1778997167}</t>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1778997168}</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1778997167554</v>
+        <v>1778997168014</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -25275,18 +25275,17 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="M35" t="b">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>943</v>
+        <v>47</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q35" t="b">
@@ -25333,26 +25332,26 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GMe0y7iJZybWYXIcl3sWc1BgoZQQnT</t>
+          <t>RsTDDT4iPhBM6HtLnE1sLut1VSfSzy</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 359000000, "_seconds": 1778997168}</t>
+          <t>{"_nanoseconds": 554000000, "_seconds": 1778997167}</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1778997168359</v>
+        <v>1778997167554</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -25360,20 +25359,18 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="L36" t="n">
-        <v>80</v>
-      </c>
+        <v>2.667</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="b">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>344.5</v>
+        <v>943</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q36" t="b">
@@ -25386,7 +25383,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -25420,69 +25417,70 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
+          <t>GMe0y7iJZybWYXIcl3sWc1BgoZQQnT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
+          <t>{"_nanoseconds": 359000000, "_seconds": 1778997168}</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1723974354144</v>
+        <v>1778997168359</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
+        <v>3.333</v>
+      </c>
+      <c r="L37" t="n">
+        <v>80</v>
+      </c>
       <c r="M37" t="b">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-19</v>
+        <v>344.5</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P37" t="n">
-        <v>15</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U37" t="b">
+        <v>1</v>
+      </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
@@ -25506,56 +25504,56 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1778997170065</v>
+        <v>1723974354144</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1.333</v>
+        <v>2.667</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="b">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
+          <t>Yeast Nutrients</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -25577,12 +25575,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
+          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>London Pub Gen 1 Stout saved by Bond</t>
+          <t>Kolserig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -25592,53 +25590,56 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>default-2302b0</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>oacPO0mcJVjJi7nTZqloc40GAkgEE7</t>
+          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 902000000, "_seconds": 1719746364}</t>
+          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1719746364902</v>
+        <v>1778997170065</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="b">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Baking Soda (NaHCO3)</t>
-        </is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
       </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -25648,15 +25649,10 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U39" t="b">
-        <v>1</v>
-      </c>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -25680,44 +25676,45 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-2302b0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>oacPO0mcJVjJi7nTZqloc40GAkgEE7</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 902000000, "_seconds": 1719746364}</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1704369575930</v>
+        <v>1719746364902</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="b">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Baking Soda (NaHCO3)</t>
         </is>
       </c>
       <c r="Q40" t="b">
@@ -25767,45 +25764,44 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
+          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1723974351111</v>
+        <v>1704369575930</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
       <c r="M41" t="b">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q41" t="b">
@@ -25829,6 +25825,9 @@
       <c r="U41" t="b">
         <v>1</v>
       </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
@@ -25852,26 +25851,26 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1723974352697</v>
+        <v>1723974351111</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -25879,20 +25878,18 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L42" t="n">
-        <v>80</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="b">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q42" t="b">
@@ -25905,7 +25902,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -25916,9 +25913,6 @@
       <c r="U42" t="b">
         <v>1</v>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
@@ -25942,26 +25936,26 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
+          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1721546982940</v>
+        <v>1723974352697</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -25969,42 +25963,46 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>80</v>
+      </c>
       <c r="M43" t="b">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>15</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U43" t="b">
         <v>1</v>
       </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
@@ -26028,26 +26026,26 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-6bc446</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
+          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
+          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1723974354144</v>
+        <v>1721546982940</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -26062,27 +26060,27 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-19</v>
+        <v>-5</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Biofine Clear</t>
         </is>
       </c>
       <c r="P44" t="n">
         <v>15</v>
       </c>
       <c r="Q44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -26099,12 +26097,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
+          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marigold Lager</t>
+          <t>London Pub Gen 1 Stout saved by Bond</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -26114,52 +26112,56 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1704369575930</v>
+        <v>1723974354144</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>2.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="b">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>15</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -26169,15 +26171,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U45" t="b">
-        <v>1</v>
-      </c>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
@@ -26201,36 +26198,35 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>lcvTqdMfO6NPRj6JBJoHMhZuaJN2Fj</t>
+          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 428000000, "_seconds": 1772634485}</t>
+          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1772634485428</v>
+        <v>1704369575930</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
@@ -26239,7 +26235,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q46" t="b">
@@ -26263,6 +26259,9 @@
       <c r="U46" t="b">
         <v>1</v>
       </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
@@ -26286,26 +26285,26 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>eIuDGEasVf2TMzwhyNhxT2RGDDKeIc</t>
+          <t>lcvTqdMfO6NPRj6JBJoHMhZuaJN2Fj</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 497000000, "_seconds": 1772634487}</t>
+          <t>{"_nanoseconds": 428000000, "_seconds": 1772634485}</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1772634487497</v>
+        <v>1772634485428</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -26315,9 +26314,7 @@
       <c r="K47" t="n">
         <v>2</v>
       </c>
-      <c r="L47" t="n">
-        <v>80</v>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="b">
         <v>0</v>
       </c>
@@ -26326,7 +26323,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q47" t="b">
@@ -26339,7 +26336,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -26373,66 +26370,70 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
+          <t>eIuDGEasVf2TMzwhyNhxT2RGDDKeIc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
+          <t>{"_nanoseconds": 497000000, "_seconds": 1772634487}</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1723974355076</v>
+        <v>1772634487497</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.20.2</t>
         </is>
       </c>
       <c r="K48" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>80</v>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U48" t="b">
         <v>1</v>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="b">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-15</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Gelatin</t>
-        </is>
-      </c>
-      <c r="Q48" t="b">
-        <v>1</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
@@ -26441,12 +26442,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
+          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Marigold Lager</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -26456,68 +26457,66 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>default-2302b0</t>
+          <t>default-90c63c</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>12gjpvorcO1e8MRDnqUsAJ2H0trK3l</t>
+          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 274000000, "_seconds": 1778126960}</t>
+          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1778126960274</v>
+        <v>1723974355076</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="b">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>97.5</v>
+        <v>-15</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Baking Soda (NaHCO3)</t>
+          <t>Gelatin</t>
         </is>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U49" t="b">
-        <v>1</v>
-      </c>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
@@ -26541,26 +26540,26 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-2302b0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>U7Q7AloKFG2MwxuQxE9znDsGScpFBa</t>
+          <t>12gjpvorcO1e8MRDnqUsAJ2H0trK3l</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 14000000, "_seconds": 1778997168}</t>
+          <t>{"_nanoseconds": 274000000, "_seconds": 1778126960}</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1778997168014</v>
+        <v>1778126960274</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -26570,15 +26569,16 @@
       <c r="K50" t="n">
         <v>3</v>
       </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="b">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>47</v>
+        <v>97.5</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Baking Soda (NaHCO3)</t>
         </is>
       </c>
       <c r="Q50" t="b">
@@ -26625,26 +26625,26 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>RsTDDT4iPhBM6HtLnE1sLut1VSfSzy</t>
+          <t>U7Q7AloKFG2MwxuQxE9znDsGScpFBa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 554000000, "_seconds": 1778997167}</t>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1778997168}</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1778997167554</v>
+        <v>1778997168014</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -26652,18 +26652,17 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="M51" t="b">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>943</v>
+        <v>47</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q51" t="b">
@@ -26710,26 +26709,26 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>GMe0y7iJZybWYXIcl3sWc1BgoZQQnT</t>
+          <t>RsTDDT4iPhBM6HtLnE1sLut1VSfSzy</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 359000000, "_seconds": 1778997168}</t>
+          <t>{"_nanoseconds": 554000000, "_seconds": 1778997167}</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1778997168359</v>
+        <v>1778997167554</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -26737,20 +26736,18 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" t="n">
-        <v>80</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="b">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>344.5</v>
+        <v>943</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q52" t="b">
@@ -26763,7 +26760,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -26797,69 +26794,70 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
+          <t>GMe0y7iJZybWYXIcl3sWc1BgoZQQnT</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
+          <t>{"_nanoseconds": 359000000, "_seconds": 1778997168}</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1723974354144</v>
+        <v>1778997168359</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K53" t="n">
+        <v>2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>80</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U53" t="b">
         <v>1</v>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="b">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-19</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P53" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q53" t="b">
-        <v>0</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
@@ -26883,26 +26881,26 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1721546982940</v>
+        <v>1723974354144</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -26910,34 +26908,34 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="b">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
+          <t>Yeast Nutrients</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -26954,12 +26952,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
+          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lager pseudo idea ii</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -26969,70 +26967,69 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-6bc446</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1704369575930</v>
+        <v>1721546982940</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="b">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
+          <t>Biofine Clear</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U55" t="b">
-        <v>1</v>
-      </c>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
@@ -27056,45 +27053,44 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
+          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1723974351111</v>
+        <v>1704369575930</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="M56" t="b">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q56" t="b">
@@ -27118,6 +27114,9 @@
       <c r="U56" t="b">
         <v>1</v>
       </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr"/>
@@ -27141,26 +27140,26 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1723974352697</v>
+        <v>1723974351111</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -27168,20 +27167,18 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>80</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="b">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q57" t="b">
@@ -27194,7 +27191,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -27205,9 +27202,6 @@
       <c r="U57" t="b">
         <v>1</v>
       </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
@@ -27229,49 +27223,75 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1723974352697</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>80</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-15</v>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P58" t="n">
-        <v>15</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U58" t="b">
+        <v>1</v>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
@@ -27293,47 +27313,25 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1723974354144</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-5adf6e</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="b">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-19</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -27344,7 +27342,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -27381,26 +27379,26 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1723974355076</v>
+        <v>1723974354144</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -27415,29 +27413,32 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>15</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
@@ -27449,12 +27450,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>First Lager v3</t>
+          <t>Lager pseudo idea ii</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -27464,70 +27465,66 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-90c63c</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1704369575930</v>
+        <v>1723974355076</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="b">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Gelatin</t>
         </is>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U61" t="b">
-        <v>1</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr"/>
@@ -27551,45 +27548,44 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
+          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1723974351111</v>
+        <v>1704369575930</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="M62" t="b">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q62" t="b">
@@ -27613,6 +27609,9 @@
       <c r="U62" t="b">
         <v>1</v>
       </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
@@ -27636,26 +27635,26 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1723974352697</v>
+        <v>1723974351111</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -27665,18 +27664,16 @@
       <c r="K63" t="n">
         <v>2</v>
       </c>
-      <c r="L63" t="n">
-        <v>80</v>
-      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="b">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q63" t="b">
@@ -27689,7 +27686,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -27700,9 +27697,6 @@
       <c r="U63" t="b">
         <v>1</v>
       </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
@@ -27726,26 +27720,26 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
+          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1721546982940</v>
+        <v>1723974352697</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -27753,42 +27747,46 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L64" t="n">
+        <v>80</v>
+      </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
-        </is>
-      </c>
-      <c r="P64" t="n">
-        <v>15</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q64" t="b">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U64" t="b">
         <v>1</v>
       </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
@@ -27812,26 +27810,26 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-6bc446</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
+          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
+          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1712314613742</v>
+        <v>1721546982940</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -27839,34 +27837,34 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="b">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Biofine Clear</t>
         </is>
       </c>
       <c r="P65" t="n">
         <v>15</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -27898,26 +27896,26 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
+          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
+          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1723974355076</v>
+        <v>1712314613742</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -27925,36 +27923,39 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="b">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>15</v>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
@@ -27966,12 +27967,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>London Pub gen 2 Weskus</t>
+          <t>First Lager v3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -27981,70 +27982,66 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-90c63c</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1704369575930</v>
+        <v>1723974355076</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>2.6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="b">
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Gelatin</t>
         </is>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U67" t="b">
-        <v>1</v>
-      </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
@@ -28068,45 +28065,44 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
+          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1723974351111</v>
+        <v>1704369575930</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
       <c r="M68" t="b">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q68" t="b">
@@ -28130,6 +28126,9 @@
       <c r="U68" t="b">
         <v>1</v>
       </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
@@ -28153,26 +28152,26 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1723974352697</v>
+        <v>1723974351111</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -28180,20 +28179,18 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L69" t="n">
-        <v>80</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="b">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q69" t="b">
@@ -28206,7 +28203,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -28217,9 +28214,6 @@
       <c r="U69" t="b">
         <v>1</v>
       </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
@@ -28243,26 +28237,26 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
+          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
+          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1723974355076</v>
+        <v>1723974352697</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -28270,9 +28264,11 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L70" t="n">
+        <v>80</v>
+      </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
@@ -28281,31 +28277,33 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
-      </c>
-      <c r="P70" t="n">
-        <v>10</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q70" t="b">
+        <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U70" t="b">
         <v>1</v>
       </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr"/>
@@ -28327,32 +28325,54 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>default-90c63c</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1723974355076</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-15</v>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
+          <t>Gelatin</t>
         </is>
       </c>
       <c r="P71" t="n">
         <v>10</v>
       </c>
       <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -28361,7 +28381,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -28391,47 +28411,25 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>1723974354144</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-5adf6e</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="b">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>-19</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -28442,7 +28440,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -28464,12 +28462,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>London Pub gen 2 Weskus</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -28479,52 +28477,56 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1781339598782</v>
+        <v>1723974354144</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>3.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="b">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>44</v>
+        <v>-19</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
       </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -28534,12 +28536,10 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U73" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
@@ -28563,45 +28563,44 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>default-4e9d62</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1704369577229</v>
+        <v>1781339598782</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L74" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q74" t="b">
@@ -28625,9 +28624,6 @@
       <c r="U74" t="b">
         <v>1</v>
       </c>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr"/>
@@ -28651,30 +28647,30 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-4e9d62</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1781339597373</v>
+        <v>1704369577229</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -28685,11 +28681,11 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>941.2</v>
+        <v>0</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="Q75" t="b">
@@ -28713,6 +28709,9 @@
       <c r="U75" t="b">
         <v>1</v>
       </c>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr"/>
@@ -28736,26 +28735,26 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1781339599470</v>
+        <v>1781339597373</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -28763,20 +28762,18 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L76" t="n">
-        <v>80</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>342.5</v>
+        <v>941.2</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q76" t="b">
@@ -28789,7 +28786,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -28821,49 +28818,72 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1781339599470</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
       <c r="K77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L77" t="n">
+        <v>80</v>
+      </c>
+      <c r="M77" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q77" t="b">
+        <v>0</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U77" t="b">
         <v>1</v>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P77" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q77" t="b">
-        <v>0</v>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
@@ -28885,47 +28905,25 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>1723974354144</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-5adf6e</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="b">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>-19</v>
-      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -28936,7 +28934,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -28958,12 +28956,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -28973,26 +28971,26 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>default-bk9j78</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>E5Gr0KsnlU7nZUzYNeiN3uBXsR8AlK</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 580000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1723974351580</v>
+        <v>1723974354144</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -29000,26 +28998,29 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>-11</v>
+        <v>-19</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Canning Salt (NaCl)</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -29029,15 +29030,10 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U79" t="b">
-        <v>1</v>
-      </c>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
@@ -29061,26 +29057,26 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-bk9j78</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
+          <t>E5Gr0KsnlU7nZUzYNeiN3uBXsR8AlK</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
+          <t>{"_nanoseconds": 580000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1723974351111</v>
+        <v>1723974351580</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -29095,11 +29091,11 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>-21</v>
+        <v>-11</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Canning Salt (NaCl)</t>
         </is>
       </c>
       <c r="Q80" t="b">
@@ -29123,6 +29119,9 @@
       <c r="U80" t="b">
         <v>1</v>
       </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
@@ -29146,26 +29145,26 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
+          <t>TpP3hziN1KkNCiM1py3FfQsf42sLzE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
+          <t>{"_nanoseconds": 111000000, "_seconds": 1723974351}</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1723974352697</v>
+        <v>1723974351111</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -29173,20 +29172,18 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>80</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q81" t="b">
@@ -29199,7 +29196,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -29210,9 +29207,6 @@
       <c r="U81" t="b">
         <v>1</v>
       </c>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr"/>
@@ -29236,26 +29230,26 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
+          <t>hFhod722VtAMbXy0UdAqFDURQixc0S</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
+          <t>{"_nanoseconds": 697000000, "_seconds": 1723974352}</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1723974354144</v>
+        <v>1723974352697</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -29265,40 +29259,44 @@
       <c r="K82" t="n">
         <v>1</v>
       </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="L82" t="n">
+        <v>80</v>
+      </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>-19</v>
+        <v>-15</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P82" t="n">
-        <v>15</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U82" t="b">
+        <v>1</v>
+      </c>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
@@ -29322,26 +29320,26 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1721546982940</v>
+        <v>1723974354144</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -29349,36 +29347,39 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>15</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="U83" t="inlineStr"/>
@@ -29390,12 +29391,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -29405,70 +29406,66 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-6bc446</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1704369575930</v>
+        <v>1721546982940</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>2.5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="b">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Biofine Clear</t>
         </is>
       </c>
       <c r="Q84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U84" t="b">
-        <v>1</v>
-      </c>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
@@ -29492,36 +29489,35 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>lcvTqdMfO6NPRj6JBJoHMhZuaJN2Fj</t>
+          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 428000000, "_seconds": 1772634485}</t>
+          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1772634485428</v>
+        <v>1704369575930</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
-      </c>
-      <c r="L85" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
@@ -29530,7 +29526,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q85" t="b">
@@ -29554,6 +29550,9 @@
       <c r="U85" t="b">
         <v>1</v>
       </c>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
@@ -29577,26 +29576,26 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>eIuDGEasVf2TMzwhyNhxT2RGDDKeIc</t>
+          <t>lcvTqdMfO6NPRj6JBJoHMhZuaJN2Fj</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 497000000, "_seconds": 1772634487}</t>
+          <t>{"_nanoseconds": 428000000, "_seconds": 1772634485}</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1772634487497</v>
+        <v>1772634485428</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -29604,11 +29603,9 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L86" t="n">
-        <v>80</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="b">
         <v>0</v>
       </c>
@@ -29617,7 +29614,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q86" t="b">
@@ -29630,7 +29627,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -29664,69 +29661,70 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
+          <t>eIuDGEasVf2TMzwhyNhxT2RGDDKeIc</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
+          <t>{"_nanoseconds": 497000000, "_seconds": 1772634487}</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1723974354144</v>
+        <v>1772634487497</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.20.2</t>
         </is>
       </c>
       <c r="K87" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L87" t="n">
+        <v>80</v>
+      </c>
+      <c r="M87" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q87" t="b">
+        <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U87" t="b">
         <v>1</v>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="b">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>-19</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P87" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q87" t="b">
-        <v>0</v>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
@@ -29748,31 +29746,55 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>new-BdtFpaKlultfp6wX0TWywYGFQGjVk6</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+          <t>default-yn1j28sf</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1723974354144</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K88" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="M88" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-19</v>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zync tablet </t>
+          <t>Yeast Nutrients</t>
         </is>
       </c>
       <c r="P88" t="n">
         <v>15</v>
       </c>
-      <c r="Q88" t="inlineStr"/>
+      <c r="Q88" t="b">
+        <v>0</v>
+      </c>
       <c r="R88" t="inlineStr">
         <is>
           <t>Other</t>
@@ -29789,17 +29811,10 @@
         </is>
       </c>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>1/6 zync tablet zync sulphate</t>
-        </is>
-      </c>
+      <c r="AB88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -29817,82 +29832,68 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>1721546982940</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>new-BdtFpaKlultfp6wX0TWywYGFQGjVk6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="b">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-5</v>
-      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
-        </is>
-      </c>
-      <c r="Q89" t="b">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve">Zync tablet </t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>1/6 zync tablet zync sulphate</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -29902,67 +29903,66 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-6bc446</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1781339598782</v>
+        <v>1721546982940</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="b">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>44</v>
+        <v>-5</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Biofine Clear</t>
         </is>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U90" t="b">
-        <v>1</v>
-      </c>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="inlineStr"/>
@@ -29986,26 +29986,26 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1781339597373</v>
+        <v>1781339598782</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -30013,18 +30013,17 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
-      </c>
-      <c r="L91" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>941.2</v>
+        <v>44</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q91" t="b">
@@ -30071,26 +30070,26 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1781339599470</v>
+        <v>1781339597373</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -30098,20 +30097,18 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" t="n">
-        <v>80</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="b">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>342.5</v>
+        <v>941.2</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q92" t="b">
@@ -30124,7 +30121,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -30158,69 +30155,70 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1775809151504</v>
+        <v>1781339599470</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>5</v>
-      </c>
-      <c r="L93" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L93" t="n">
+        <v>80</v>
+      </c>
       <c r="M93" t="b">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>342.5</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P93" t="n">
-        <v>10</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U93" t="b">
+        <v>1</v>
+      </c>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="inlineStr"/>
@@ -30244,26 +30242,26 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>default-yn-wln1000</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
+          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1775809134067</v>
+        <v>1775809151504</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -30271,18 +30269,18 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="b">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Yeast Nutrient (WLN1000)</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -30293,7 +30291,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -30307,15 +30305,7 @@
         </is>
       </c>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
-We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
-        </is>
-      </c>
+      <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr"/>
@@ -30323,12 +30313,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -30338,52 +30328,56 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-yn-wln1000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
+          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1781339598782</v>
+        <v>1775809134067</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>3.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="b">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
+          <t>Yeast Nutrient (WLN1000)</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
       </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -30393,13 +30387,19 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U95" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y95" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
+We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
+        </is>
+      </c>
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="inlineStr"/>
       <c r="AB95" t="inlineStr"/>
@@ -30422,26 +30422,26 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
+          <t>H7UJqQmCQoIgN0FnBDrWOqLcKcg5ej</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1781339598}</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1781339597373</v>
+        <v>1781339598782</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -30449,18 +30449,17 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
       <c r="M96" t="b">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>941.2</v>
+        <v>44</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q96" t="b">
@@ -30507,26 +30506,26 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
+          <t>NY07RRt0S89HR4jFBqrMhymNbPVBus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
+          <t>{"_nanoseconds": 373000000, "_seconds": 1781339597}</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1781339599470</v>
+        <v>1781339597373</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -30534,20 +30533,18 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" t="n">
-        <v>80</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>342.5</v>
+        <v>941.2</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q97" t="b">
@@ -30560,7 +30557,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -30594,69 +30591,70 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
+          <t>260vJiZ8NKF6Ccvlq0W1kKFJapTxCQ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 470000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1775809151504</v>
+        <v>1781339599470</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>5</v>
-      </c>
-      <c r="L98" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L98" t="n">
+        <v>80</v>
+      </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>342.5</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P98" t="n">
-        <v>10</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U98" t="b">
+        <v>1</v>
+      </c>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr"/>
@@ -30680,26 +30678,26 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>default-yn-wln1000</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
+          <t>z82GocB6JPQV699Mhx10blYxb69kZE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1775809134067</v>
+        <v>1775809151504</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -30707,18 +30705,18 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Yeast Nutrient (WLN1000)</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -30729,7 +30727,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -30743,15 +30741,7 @@
         </is>
       </c>
       <c r="U99" t="inlineStr"/>
-      <c r="V99" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
-We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
-        </is>
-      </c>
+      <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -30759,12 +30749,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -30774,53 +30764,56 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>default-bk9j78</t>
+          <t>default-yn-wln1000</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1PMknHJZdv0oQ7VqqIQ2rbYXMm9N5D</t>
+          <t>naf4Kaq8Bj5vVUHIgICtzv9zYVFplp</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 260000000, "_seconds": 1712314610}</t>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1712314610260</v>
+        <v>1775809134067</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="b">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>-5</v>
+        <v>80</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Canning Salt (NaCl)</t>
-        </is>
+          <t>Yeast Nutrient (WLN1000)</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -30830,16 +30823,19 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U100" t="b">
-        <v>1</v>
-      </c>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
+We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
+        </is>
+      </c>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -30862,26 +30858,26 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 191000000, "_seconds": 1706434206}</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-bk9j78</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>lwPgFpUrns6MH8XqOw1PIDi3cAnGBV</t>
+          <t>1PMknHJZdv0oQ7VqqIQ2rbYXMm9N5D</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 450000000, "_seconds": 1712314609}</t>
+          <t>{"_nanoseconds": 260000000, "_seconds": 1712314610}</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1712314609450</v>
+        <v>1712314610260</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -30889,18 +30885,18 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="b">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Canning Salt (NaCl)</t>
         </is>
       </c>
       <c r="Q101" t="b">
@@ -30924,6 +30920,9 @@
       <c r="U101" t="b">
         <v>1</v>
       </c>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr"/>
@@ -30947,47 +30946,45 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Wtg8GXKfWxQjJGGYxmK7mUYTRcgSh9</t>
+          <t>lwPgFpUrns6MH8XqOw1PIDi3cAnGBV</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 450000000, "_seconds": 1712314609}</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1706434207828</v>
+        <v>1712314609450</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2.10.5</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>3</v>
-      </c>
-      <c r="L102" t="n">
-        <v>80</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q102" t="b">
@@ -31000,7 +30997,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -31011,9 +31008,6 @@
       <c r="U102" t="b">
         <v>1</v>
       </c>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr"/>
@@ -31035,49 +31029,75 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>default-6bc446</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Wtg8GXKfWxQjJGGYxmK7mUYTRcgSh9</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>1706434207828</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2.10.5</t>
+        </is>
+      </c>
       <c r="K103" t="n">
-        <v>5</v>
-      </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L103" t="n">
+        <v>80</v>
+      </c>
+      <c r="M103" t="b">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>-4</v>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Biofine Clear</t>
-        </is>
-      </c>
-      <c r="P103" t="n">
-        <v>15</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q103" t="b">
+        <v>0</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U103" t="b">
         <v>1</v>
       </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>Fining</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr"/>
@@ -31099,63 +31119,41 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>1712314613742</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-6bc446</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="b">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-11</v>
-      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
+          <t>Biofine Clear</t>
         </is>
       </c>
       <c r="P104" t="n">
         <v>15</v>
       </c>
       <c r="Q104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -31187,63 +31185,66 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>n39qcIsSvY0mhj8mb0KhJHE9df0bXd</t>
+          <t>n9o5cFAQDFJBRKVV6LFjrQgK6Vnlsr</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 300000000, "_seconds": 1704369578}</t>
+          <t>{"_nanoseconds": 742000000, "_seconds": 1712314613}</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1704369578300</v>
+        <v>1712314613742</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="b">
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>15</v>
       </c>
       <c r="Q105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="U105" t="inlineStr"/>
@@ -31255,12 +31256,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -31268,47 +31269,68 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+          <t>default-90c63c</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>n39qcIsSvY0mhj8mb0KhJHE9df0bXd</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 300000000, "_seconds": 1704369578}</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>1704369578300</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2.10.4</t>
+        </is>
+      </c>
       <c r="K106" t="n">
-        <v>0.96</v>
+        <v>5</v>
       </c>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Calcium Chloride</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr"/>
+          <t>Gelatin</t>
+        </is>
+      </c>
+      <c r="Q106" t="b">
+        <v>1</v>
+      </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Mash</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
       <c r="AA106" t="inlineStr"/>
@@ -31333,7 +31355,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
+          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -31341,14 +31363,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>10</v>
+        <v>0.96</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Calcium Chloride</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr"/>
@@ -31395,7 +31417,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
+          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -31403,14 +31425,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>17.64</v>
+        <v>10</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Gypsum (Calcium Sulfate)</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr"/>
@@ -31457,7 +31479,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -31465,21 +31487,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="L109" t="n">
-        <v>80</v>
-      </c>
+        <v>17.64</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
-      </c>
-      <c r="Q109" t="b">
-        <v>0</v>
-      </c>
+          <t>Gypsum (Calcium Sulfate)</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -31487,7 +31505,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -31495,9 +31513,7 @@
           <t>Mash</t>
         </is>
       </c>
-      <c r="U109" t="b">
-        <v>1</v>
-      </c>
+      <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
@@ -31525,7 +31541,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -31533,17 +31549,21 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L110" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="L110" t="n">
+        <v>80</v>
+      </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Salt</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr"/>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q110" t="b">
+        <v>0</v>
+      </c>
       <c r="R110" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -31551,7 +31571,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -31559,7 +31579,9 @@
           <t>Mash</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
+      <c r="U110" t="b">
+        <v>1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
@@ -31587,7 +31609,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -31595,21 +31617,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L111" t="n">
-        <v>80</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
-        </is>
-      </c>
-      <c r="Q111" t="b">
-        <v>0</v>
-      </c>
+          <t>Salt</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -31617,17 +31635,15 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Sparge</t>
-        </is>
-      </c>
-      <c r="U111" t="b">
-        <v>1</v>
-      </c>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
@@ -31655,7 +31671,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -31663,20 +31679,21 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="L112" t="inlineStr"/>
+        <v>3.05</v>
+      </c>
+      <c r="L112" t="n">
+        <v>80</v>
+      </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Calcium Chloride</t>
-        </is>
-      </c>
-      <c r="P112" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q112" t="inlineStr"/>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q112" t="b">
+        <v>0</v>
+      </c>
       <c r="R112" t="inlineStr">
         <is>
           <t>Water Agent</t>
@@ -31684,15 +31701,17 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr"/>
+          <t>Sparge</t>
+        </is>
+      </c>
+      <c r="U112" t="b">
+        <v>1</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
@@ -31720,7 +31739,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
+          <t>new-ovmHGCc2JjuddQftQKRnRw2IqOPksF</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -31728,14 +31747,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
-        <v>3.62</v>
+        <v>0.34</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Calcium Chloride</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -31785,7 +31804,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
+          <t>new-tAM38RfHn8hFnmAABYZupbK1UzgFm1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -31793,14 +31812,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="n">
-        <v>6.4</v>
+        <v>3.62</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Gypsum (Calcium Sulfate)</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -31850,7 +31869,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
+          <t>new-yKxJxRIco7GpVVGCEKGJMSDpWPOLQm</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -31858,14 +31877,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="n">
-        <v>1.06</v>
+        <v>6.4</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Gypsum (Calcium Sulfate)</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -31915,7 +31934,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>new-TUfxqCta0ITj3uHT8vfAbVIfLtzqyA</t>
+          <t>new-aOlKF4nejroi8r6Rz4mz7rBbuj7Ht3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -31923,28 +31942,28 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
-        <v>2</v>
+        <v>1.06</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Protafloc</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>tbsp</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -31980,7 +31999,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>new-Xe5CxkyeaTwnbVay8pIU6ai8XycVKB</t>
+          <t>new-TUfxqCta0ITj3uHT8vfAbVIfLtzqyA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -31995,7 +32014,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Yeast Nutrient</t>
+          <t>Protafloc</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -32004,12 +32023,12 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>tsp</t>
+          <t>tbsp</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -32029,12 +32048,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -32042,70 +32061,50 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>default-2302b0</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
-        </is>
-      </c>
-      <c r="I118" t="n">
-        <v>1781339599069</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>new-Xe5CxkyeaTwnbVay8pIU6ai8XycVKB</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="b">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>94.5</v>
-      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Baking Soda (NaHCO3)</t>
-        </is>
-      </c>
-      <c r="Q118" t="b">
-        <v>0</v>
-      </c>
+          <t>Yeast Nutrient</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>tsp</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U118" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
       <c r="AA118" t="inlineStr"/>
@@ -32129,26 +32128,26 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-2302b0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
+          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
+          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1785061186542</v>
+        <v>1781339599069</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -32156,17 +32155,18 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>2.5</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
       <c r="M119" t="b">
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>40.5</v>
+        <v>94.5</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
+          <t>Baking Soda (NaHCO3)</t>
         </is>
       </c>
       <c r="Q119" t="b">
@@ -32213,45 +32213,44 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>default-4e9d62</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
+          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
+          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1704369577229</v>
+        <v>1785061186542</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
       <c r="M120" t="b">
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Epsom Salt (MgSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q120" t="b">
@@ -32275,9 +32274,6 @@
       <c r="U120" t="b">
         <v>1</v>
       </c>
-      <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
       <c r="AA120" t="inlineStr"/>
@@ -32301,45 +32297,45 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 459000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-4e9d62</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
+          <t>baUPFv7WEZjl8hB5Cj0fMBSpkrFQ3R</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
+          <t>{"_nanoseconds": 229000000, "_seconds": 1704369577}</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1785061185868</v>
+        <v>1704369577229</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.4</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="b">
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>936.7</v>
+        <v>0</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Epsom Salt (MgSO4)</t>
         </is>
       </c>
       <c r="Q121" t="b">
@@ -32363,6 +32359,9 @@
       <c r="U121" t="b">
         <v>1</v>
       </c>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr"/>
@@ -32386,26 +32385,26 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
+          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
+          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1785061187167</v>
+        <v>1785061185868</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -32413,20 +32412,18 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L122" t="n">
-        <v>80</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="b">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>340.5</v>
+        <v>936.7</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q122" t="b">
@@ -32439,7 +32436,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
@@ -32473,26 +32470,26 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
+          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
+          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1781339600221</v>
+        <v>1785061187167</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -32500,42 +32497,43 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>5</v>
-      </c>
-      <c r="L123" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L123" t="n">
+        <v>80</v>
+      </c>
       <c r="M123" t="b">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>33</v>
+        <v>340.5</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P123" t="n">
-        <v>15</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U123" t="b">
+        <v>1</v>
+      </c>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
       <c r="AA123" t="inlineStr"/>
@@ -32559,26 +32557,26 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
+          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
+          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1778997170065</v>
+        <v>1781339600221</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -32593,22 +32591,22 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
+          <t>Yeast Nutrients</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -32630,12 +32628,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Smash Mosaic</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -32645,26 +32643,26 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
+          <t>ntpZTYp6GFzhrk8IfC1bCJaKbHeIyI</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
+          <t>{"_nanoseconds": 65000000, "_seconds": 1778997170}</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1785061186542</v>
+        <v>1778997170065</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -32672,25 +32670,29 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="b">
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>40.5</v>
+        <v>0</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>10</v>
       </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -32700,12 +32702,10 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U125" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
       <c r="AA125" t="inlineStr"/>
@@ -32729,26 +32729,26 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
+          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
+          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1785061185868</v>
+        <v>1785061186542</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -32756,18 +32756,17 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L126" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="M126" t="b">
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>936.7</v>
+        <v>40.5</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q126" t="b">
@@ -32814,26 +32813,26 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
+          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
+          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1785061187167</v>
+        <v>1785061185868</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -32841,20 +32840,18 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" t="n">
-        <v>80</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
       <c r="M127" t="b">
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>340.5</v>
+        <v>936.7</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q127" t="b">
@@ -32867,7 +32864,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -32901,26 +32898,26 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
+          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
+          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1781339600221</v>
+        <v>1785061187167</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -32928,42 +32925,43 @@
         </is>
       </c>
       <c r="K128" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" t="n">
+        <v>80</v>
+      </c>
+      <c r="M128" t="b">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q128" t="b">
+        <v>0</v>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U128" t="b">
         <v>1</v>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="b">
-        <v>0</v>
-      </c>
-      <c r="N128" t="n">
-        <v>33</v>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P128" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q128" t="b">
-        <v>0</v>
-      </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr"/>
       <c r="Y128" t="inlineStr"/>
       <c r="Z128" t="inlineStr"/>
       <c r="AA128" t="inlineStr"/>
@@ -32987,26 +32985,26 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>hBAibaPvX0FHQT9ll1gxER4gHbbxIg</t>
+          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1785061187}</t>
+          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1785061187983</v>
+        <v>1781339600221</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -33021,22 +33019,22 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>-5</v>
+        <v>33</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
+          <t>Yeast Nutrients</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -33058,12 +33056,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Smash shoddy</t>
+          <t>Smash Mosaic</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -33073,26 +33071,26 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
+          <t>hBAibaPvX0FHQT9ll1gxER4gHbbxIg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1785061187}</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1785061186542</v>
+        <v>1785061187983</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -33100,25 +33098,29 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
       <c r="M130" t="b">
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>40.5</v>
+        <v>-5</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>10</v>
       </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -33128,12 +33130,10 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U130" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
       <c r="AA130" t="inlineStr"/>
@@ -33157,26 +33157,26 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
+          <t>Krt6pCjgS31xUqPji18XahSkMlPSpg</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
+          <t>{"_nanoseconds": 542000000, "_seconds": 1785061186}</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1785061185868</v>
+        <v>1785061186542</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -33184,18 +33184,17 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>3</v>
-      </c>
-      <c r="L131" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="M131" t="b">
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>936.7</v>
+        <v>40.5</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q131" t="b">
@@ -33242,26 +33241,26 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
+          <t>1eZxGCR6vlM3Yk5utOhCaPxCJgad8G</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
+          <t>{"_nanoseconds": 868000000, "_seconds": 1785061185}</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1785061187167</v>
+        <v>1785061185868</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -33269,20 +33268,18 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>2</v>
-      </c>
-      <c r="L132" t="n">
-        <v>80</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
       <c r="M132" t="b">
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>340.5</v>
+        <v>936.7</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q132" t="b">
@@ -33295,7 +33292,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -33329,26 +33326,26 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>default-yn1j28sf</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
+          <t>2K0l0yVaTOoSGIybTyu7f2OZzHqTjY</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
+          <t>{"_nanoseconds": 167000000, "_seconds": 1785061187}</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1781339600221</v>
+        <v>1785061187167</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -33356,42 +33353,43 @@
         </is>
       </c>
       <c r="K133" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" t="n">
+        <v>80</v>
+      </c>
+      <c r="M133" t="b">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q133" t="b">
+        <v>0</v>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U133" t="b">
         <v>1</v>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="b">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>33</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>Yeast Nutrients</t>
-        </is>
-      </c>
-      <c r="P133" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q133" t="b">
-        <v>0</v>
-      </c>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
       <c r="AA133" t="inlineStr"/>
@@ -33415,26 +33413,26 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-yn1j28sf</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>hBAibaPvX0FHQT9ll1gxER4gHbbxIg</t>
+          <t>92ChBNr2k0grfMSG7XIrynIVfyh02o</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1785061187}</t>
+          <t>{"_nanoseconds": 221000000, "_seconds": 1781339600}</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1785061187983</v>
+        <v>1781339600221</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -33449,22 +33447,22 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>-5</v>
+        <v>33</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
+          <t>Yeast Nutrients</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -33486,12 +33484,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Smash shoddy</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -33501,26 +33499,26 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>default-3b1827</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>vjR3TZSLVuLk8qB9CNQnCBEGksFtLx</t>
+          <t>hBAibaPvX0FHQT9ll1gxER4gHbbxIg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 652000000, "_seconds": 1786789729}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1785061187}</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1786789729652</v>
+        <v>1785061187983</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -33528,25 +33526,29 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
       <c r="M135" t="b">
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>38.5</v>
+        <v>-5</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Calcium Chloride (CaCl2)</t>
-        </is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>10</v>
       </c>
       <c r="Q135" t="b">
         <v>0</v>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Water Agent</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -33556,12 +33558,10 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>Mash</t>
-        </is>
-      </c>
-      <c r="U135" t="b">
-        <v>1</v>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
       <c r="AA135" t="inlineStr"/>
@@ -33585,26 +33585,26 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>default-1f88df</t>
+          <t>default-3b1827</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ZoNtSHVvqHcJXO4uTvjhGVWtnZpcPQ</t>
+          <t>vjR3TZSLVuLk8qB9CNQnCBEGksFtLx</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 135000000, "_seconds": 1786789729}</t>
+          <t>{"_nanoseconds": 652000000, "_seconds": 1786789729}</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1786789729135</v>
+        <v>1786789729652</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -33612,18 +33612,17 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>2</v>
-      </c>
-      <c r="L136" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="M136" t="b">
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>933.2</v>
+        <v>38.5</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Gypsum (CaSO4)</t>
+          <t>Calcium Chloride (CaCl2)</t>
         </is>
       </c>
       <c r="Q136" t="b">
@@ -33670,26 +33669,26 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>default-07adb1</t>
+          <t>default-1f88df</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>cUtlWL0SE56LvTXQN0VkwAWelrEQMz</t>
+          <t>ZoNtSHVvqHcJXO4uTvjhGVWtnZpcPQ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 122000000, "_seconds": 1786789730}</t>
+          <t>{"_nanoseconds": 135000000, "_seconds": 1786789729}</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1786789730122</v>
+        <v>1786789729135</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -33699,18 +33698,16 @@
       <c r="K137" t="n">
         <v>2</v>
       </c>
-      <c r="L137" t="n">
-        <v>80</v>
-      </c>
+      <c r="L137" t="inlineStr"/>
       <c r="M137" t="b">
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>338.5</v>
+        <v>933.2</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>Gypsum (CaSO4)</t>
         </is>
       </c>
       <c r="Q137" t="b">
@@ -33723,7 +33720,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
@@ -33757,26 +33754,26 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>default-5adf6e</t>
+          <t>default-07adb1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>oFUspzLYyic8X5KuHzZsHOacLKbJLs</t>
+          <t>cUtlWL0SE56LvTXQN0VkwAWelrEQMz</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 617000000, "_seconds": 1786789730}</t>
+          <t>{"_nanoseconds": 122000000, "_seconds": 1786789730}</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1786789730617</v>
+        <v>1786789730122</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -33784,42 +33781,43 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>5</v>
-      </c>
-      <c r="L138" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L138" t="n">
+        <v>80</v>
+      </c>
       <c r="M138" t="b">
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>-6</v>
+        <v>338.5</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Irish Moss</t>
-        </is>
-      </c>
-      <c r="P138" t="n">
-        <v>10</v>
+          <t>Lactic Acid</t>
+        </is>
       </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Water Agent</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>Boil</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr"/>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U138" t="b">
+        <v>1</v>
+      </c>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
       <c r="AA138" t="inlineStr"/>
@@ -33843,26 +33841,26 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>default-yn-wln1000</t>
+          <t>default-5adf6e</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>7OKC3E50keNLcUm8VGnqOX7zL97zpO</t>
+          <t>oFUspzLYyic8X5KuHzZsHOacLKbJLs</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 75000000, "_seconds": 1785061189}</t>
+          <t>{"_nanoseconds": 617000000, "_seconds": 1786789730}</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1785061189075</v>
+        <v>1786789730617</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -33870,18 +33868,18 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>0.76</v>
+        <v>5</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="b">
         <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>78</v>
+        <v>-6</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Yeast Nutrient (WLN1000)</t>
+          <t>Irish Moss</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -33892,7 +33890,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fining</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -33906,21 +33904,107 @@
         </is>
       </c>
       <c r="U139" t="inlineStr"/>
-      <c r="V139" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
-We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
-        </is>
-      </c>
+      <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
       <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Kalahari blond</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>default-yn-wln1000</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>7OKC3E50keNLcUm8VGnqOX7zL97zpO</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 75000000, "_seconds": 1785061189}</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>1785061189075</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="b">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>78</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Yeast Nutrient (WLN1000)</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q140" t="b">
+        <v>0</v>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
+We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB139"/>
+  <autoFilter ref="A1:AB140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$140</definedName>
@@ -2080,7 +2080,7 @@
         <v>22.7</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>12</v>
@@ -2108,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT87"/>
+  <dimension ref="A1:AT86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -11024,26 +11024,26 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 218000000, "_seconds": 1784057842}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>default-c4dd41c950d</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>AXp7oOluCAHfEYcypMwZBoIFWG2sY2</t>
+          <t>GOG6rzO2xrYYSto1fMsaU5lUVzV9v7</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 217000000, "_seconds": 1784057842}</t>
+          <t>{"_nanoseconds": 7000000, "_seconds": 1786789728}</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1784057842217</v>
+        <v>1786789728007</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -11051,10 +11051,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -11065,11 +11065,11 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2</v>
+        <v>11.4</v>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Swaen Lager</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE84" t="b">
@@ -11082,7 +11082,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>62.5</v>
+        <v>78.13</v>
       </c>
       <c r="AI84" t="n">
         <v>1.0368</v>
@@ -11126,26 +11126,26 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>GOG6rzO2xrYYSto1fMsaU5lUVzV9v7</t>
+          <t>vNwfSmBlJ1e4z5jdNJOlLtSxOILZid</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 7000000, "_seconds": 1786789728}</t>
+          <t>{"_nanoseconds": 15000000, "_seconds": 1785061182}</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1786789728007</v>
+        <v>1785061182015</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -11156,22 +11156,22 @@
         <v>0.5</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X85" t="b">
         <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>11.4</v>
+        <v>2.4</v>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE85" t="b">
@@ -11187,10 +11187,10 @@
         <v>15.63</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.0368</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ85" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="inlineStr">
@@ -11226,78 +11226,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>vNwfSmBlJ1e4z5jdNJOlLtSxOILZid</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 15000000, "_seconds": 1785061182}</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>1785061182015</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
+          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="P86" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.1</v>
+        <v>2.5380711</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Wheat)</t>
         </is>
       </c>
       <c r="X86" t="b">
         <v>0</v>
       </c>
-      <c r="Z86" t="n">
-        <v>2.4</v>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>10</v>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Torrefied Wheat</t>
         </is>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
+        </is>
+      </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>15.63</v>
+        <v>6.25</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.03588</v>
+        <v>1.038</v>
       </c>
       <c r="AJ86" t="n">
-        <v>78</v>
+        <v>82</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>10</v>
       </c>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
@@ -11312,115 +11317,8 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr"/>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Kalahari blond</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Fermentable</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="P87" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>2.5380711</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Base (Wheat)</t>
-        </is>
-      </c>
-      <c r="X87" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC87" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>Torrefied Wheat</t>
-        </is>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="AH87" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AI87" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="AJ87" t="n">
-        <v>82</v>
-      </c>
-      <c r="AK87" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Crisp</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr"/>
-      <c r="AP87" t="inlineStr"/>
-      <c r="AQ87" t="inlineStr"/>
-      <c r="AR87" t="inlineStr"/>
-      <c r="AS87" t="inlineStr"/>
-      <c r="AT87" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AT87"/>
+  <autoFilter ref="A1:AT86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1.047482398</v>
+        <v>1.046512226</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1.008</v>
@@ -2077,19 +2077,19 @@
         <v>5.12</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>18.6</v>
+        <v>22.77</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>57.9</v>
+        <v>60.5</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>70</v>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q84" t="n">
         <v>1.9</v>
@@ -11082,7 +11082,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>78.13</v>
+        <v>77.5</v>
       </c>
       <c r="AI84" t="n">
         <v>1.0368</v>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="Q85" t="n">
         <v>5.1</v>
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>15.63</v>
+        <v>16</v>
       </c>
       <c r="AI85" t="n">
         <v>1.03588</v>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11240,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="P86" t="n">
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI86" t="n">
         <v>1.038</v>
@@ -19018,7 +19018,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -19035,7 +19035,7 @@
         <v>6.3</v>
       </c>
       <c r="H77" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
         <v>3.5</v>
@@ -19047,7 +19047,7 @@
         <v>30</v>
       </c>
       <c r="Q77" t="n">
-        <v>16.6</v>
+        <v>15.6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -19144,13 +19144,13 @@
         <v>3.2</v>
       </c>
       <c r="H78" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -19242,13 +19242,13 @@
         <v>3.2</v>
       </c>
       <c r="H79" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -33473,7 +33473,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -33510,7 +33510,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M136" t="b">
         <v>0</v>
@@ -33557,7 +33557,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -33594,7 +33594,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>2</v>
+        <v>2.667</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="b">
@@ -33642,7 +33642,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -33679,7 +33679,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>2</v>
+        <v>2.667</v>
       </c>
       <c r="L138" t="n">
         <v>80</v>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -33766,7 +33766,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>5</v>
+        <v>6.667</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="b">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Kalahari blond 16 liter</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -33852,7 +33852,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>0.76</v>
+        <v>1.013</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="b">

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -14,11 +14,11 @@
     <sheet name="Misc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$79</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1674,19 +1674,19 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.048764437</v>
+        <v>1.047685263</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.009</v>
+        <v>1.01</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5.25</v>
+        <v>4.99</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>33.1</v>
+        <v>30.3</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>12</v>
@@ -1708,8 +1708,7 @@
 Larger portion pilsener malt
 Used American Pale Ale water profile 
 V2 with lax came out more like a blonde.
-For v3
-less malty (drop vienna) and even more whirlpool hops.</t>
+Future: less malty (drop vienna) and even more whirlpool hops.</t>
         </is>
       </c>
     </row>
@@ -2068,19 +2067,19 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1.046512226</v>
+        <v>1.0454136</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.008</v>
+        <v>1.007</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>5.12</v>
+        <v>4.99</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>16</v>
@@ -2096,8 +2095,72 @@
       </c>
       <c r="P25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>English Porter</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>All Grain</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ernst Gouws</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1.047801523</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dryer summer stout with whc heritage yeast.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P25"/>
+  <autoFilter ref="A1:P26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2108,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT86"/>
+  <dimension ref="A1:AT93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2127,7 +2190,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
@@ -9553,7 +9616,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q70" t="n">
         <v>1.9</v>
@@ -9584,7 +9647,7 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>87.23</v>
+        <v>73.02</v>
       </c>
       <c r="AI70" t="n">
         <v>1.0368</v>
@@ -9628,26 +9691,26 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -9655,42 +9718,25 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="P71" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="Q71" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S71" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U71" t="n">
-        <v>80</v>
-      </c>
-      <c r="V71" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X71" t="b">
         <v>0</v>
       </c>
-      <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE71" t="b">
@@ -9703,16 +9749,13 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>10.9</v>
+        <v>14.29</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ71" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr">
@@ -9750,26 +9793,26 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1781339589491</v>
+        <v>1781339591050</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -9777,48 +9820,64 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S72" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>80</v>
+      </c>
+      <c r="V72" t="n">
+        <v>80</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X72" t="b">
         <v>0</v>
       </c>
+      <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>1.36</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>1.87</v>
+        <v>11.11</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ72" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr">
@@ -9841,12 +9900,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9854,52 +9913,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="n">
-        <v>0</v>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1781339589491</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L73" t="n">
-        <v>3</v>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="P73" t="n">
-        <v>1.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.8527919</v>
-      </c>
-      <c r="S73" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X73" t="b">
         <v>0</v>
       </c>
-      <c r="Y73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>4.5</v>
+      <c r="Z73" t="n">
+        <v>1.36</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® Extra Pale</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE73" t="b">
@@ -9907,30 +9968,27 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>68.18000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.038</v>
+        <v>1.034</v>
       </c>
       <c r="AJ73" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK73" t="n">
-        <v>10.1</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
@@ -9964,7 +10022,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -9975,21 +10033,21 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="P74" t="n">
         <v>1.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.9593909</v>
+        <v>1.8527919</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X74" t="b">
@@ -10006,7 +10064,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Clear Choice Malt ® Extra Pale</t>
         </is>
       </c>
       <c r="AE74" t="b">
@@ -10014,7 +10072,7 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
@@ -10023,16 +10081,16 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>22.73</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ74" t="n">
-        <v>80</v>
+        <v>81.5</v>
       </c>
       <c r="AK74" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr">
@@ -10068,75 +10126,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>1706434202728</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2.10.5</t>
-        </is>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>3.9593909</v>
+      </c>
+      <c r="S75" t="n">
+        <v>50</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X75" t="b">
         <v>0</v>
       </c>
-      <c r="Z75" t="n">
-        <v>-2.29</v>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+        </is>
+      </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>6.82</v>
+        <v>22.73</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.036</v>
+        <v>1.037</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>9.6</v>
       </c>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
@@ -10147,9 +10213,7 @@
       <c r="AO75" t="inlineStr"/>
       <c r="AP75" t="inlineStr"/>
       <c r="AQ75" t="inlineStr"/>
-      <c r="AR75" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR75" t="inlineStr"/>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr"/>
     </row>
@@ -10171,108 +10235,73 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>default-4c1345c</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1712314604140</v>
+        <v>1706434202728</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
+          <t>2.10.5</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q76" t="n">
         <v>2</v>
       </c>
-      <c r="L76" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X76" t="b">
         <v>0</v>
       </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
       <c r="Z76" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>4</v>
+        <v>-2.29</v>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
-        </is>
-      </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>2.27</v>
+        <v>6.82</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
+        <v>1.036</v>
+      </c>
+      <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
@@ -10283,19 +10312,21 @@
       <c r="AO76" t="inlineStr"/>
       <c r="AP76" t="inlineStr"/>
       <c r="AQ76" t="inlineStr"/>
-      <c r="AR76" t="inlineStr"/>
+      <c r="AR76" t="b">
+        <v>0</v>
+      </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10303,69 +10334,110 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>default-4c1345c</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1712314604140</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>2</v>
+      </c>
       <c r="L77" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q77" t="n">
-        <v>3</v>
-      </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="X77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>4</v>
+      </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Pale Malt, Maris Otter</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
+        </is>
+      </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>100</v>
+        <v>2.27</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.03795</v>
+        <v>1.03</v>
       </c>
       <c r="AJ77" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
+        <v>65.2</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Maris Otter</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -10378,21 +10450,17 @@
       <c r="AQ77" t="inlineStr"/>
       <c r="AR77" t="inlineStr"/>
       <c r="AS77" t="inlineStr"/>
-      <c r="AT77" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="AT77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10400,78 +10468,69 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>1781339591476</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="n">
-        <v>2.4</v>
-      </c>
+        <v>13.18</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
-        <v>1.9</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X78" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>6.7</v>
-      </c>
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
-        </is>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
+          <t>Pale Malt, Maris Otter</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>78.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.0368</v>
+        <v>1.03795</v>
       </c>
       <c r="AJ78" t="n">
-        <v>80</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Maris Otter</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
@@ -10484,7 +10543,11 @@
       <c r="AQ78" t="inlineStr"/>
       <c r="AR78" t="inlineStr"/>
       <c r="AS78" t="inlineStr"/>
-      <c r="AT78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10504,26 +10567,26 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -10531,25 +10594,25 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X79" t="b">
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE79" t="b">
@@ -10562,13 +10625,13 @@
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>11.11</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ79" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="inlineStr">
@@ -10606,71 +10669,81 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>default-132c22b</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1772634460383</v>
+        <v>1781339591852</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M80" t="n">
-        <v>1.22</v>
+        <v>0.34</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>5.1</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Base (Vienna)</t>
+        </is>
       </c>
       <c r="X80" t="b">
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Sugar, Table (Sucrose)</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
       <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="AH80" t="n">
-        <v>6.86</v>
+        <v>11.11</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.046</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ80" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr"/>
@@ -10698,101 +10771,71 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-132c22b</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
+          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
+          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1785061180905</v>
+        <v>1772634460383</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.20.2</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="P81" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q81" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S81" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U81" t="n">
-        <v>80</v>
-      </c>
-      <c r="V81" t="n">
-        <v>80</v>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
       <c r="X81" t="b">
         <v>0</v>
       </c>
-      <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Sugar, Table (Sucrose)</t>
         </is>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
       <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
+      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="n">
-        <v>3.59</v>
+        <v>6.86</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.035</v>
+        <v>1.046</v>
       </c>
       <c r="AJ81" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>11.7</v>
+        <v>100</v>
       </c>
       <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
+      <c r="AM81" t="inlineStr"/>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr"/>
@@ -10805,12 +10848,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Smash Mosaic</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10820,26 +10863,26 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
+          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
+          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1785061181508</v>
+        <v>1785061180905</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -10847,25 +10890,42 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3</v>
+        <v>0.11</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
+      </c>
+      <c r="S82" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>80</v>
+      </c>
+      <c r="V82" t="n">
+        <v>80</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X82" t="b">
         <v>0</v>
       </c>
+      <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>4.4</v>
+        <v>2.19</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE82" t="b">
@@ -10878,13 +10938,16 @@
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>100</v>
+        <v>3.59</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.0368</v>
+        <v>1.035</v>
       </c>
       <c r="AJ82" t="n">
-        <v>80</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL82" t="inlineStr"/>
       <c r="AM82" t="inlineStr">
@@ -10907,12 +10970,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Smash shoddy</t>
+          <t>Smash Mosaic</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11009,12 +11072,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kalahari blond 16 liter</t>
+          <t>Smash shoddy</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11034,16 +11097,16 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>GOG6rzO2xrYYSto1fMsaU5lUVzV9v7</t>
+          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 7000000, "_seconds": 1786789728}</t>
+          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1786789728007</v>
+        <v>1785061181508</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -11051,7 +11114,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q84" t="n">
         <v>1.9</v>
@@ -11065,7 +11128,7 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
@@ -11082,7 +11145,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="AI84" t="n">
         <v>1.0368</v>
@@ -11126,26 +11189,26 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>vNwfSmBlJ1e4z5jdNJOlLtSxOILZid</t>
+          <t>GOG6rzO2xrYYSto1fMsaU5lUVzV9v7</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 15000000, "_seconds": 1785061182}</t>
+          <t>{"_nanoseconds": 7000000, "_seconds": 1786789728}</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1785061182015</v>
+        <v>1786789728007</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -11153,25 +11216,25 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.64</v>
+        <v>3.3</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X85" t="b">
         <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE85" t="b">
@@ -11184,13 +11247,13 @@
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>16</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ85" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="inlineStr">
@@ -11226,83 +11289,98 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="n">
-        <v>0</v>
+          <t>default-c454dca637a</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>8RBzx8WZSkSmbLLiWSJhSrf0Ak2Trz</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 681000000, "_seconds": 1788086444}</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1788086444681</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L86" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.5380711</v>
+        <v>6.6</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>80</v>
+      </c>
+      <c r="V86" t="n">
+        <v>80</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Base (Wheat)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X86" t="b">
         <v>0</v>
       </c>
-      <c r="Y86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>25</v>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="n">
+        <v>2.04</v>
       </c>
       <c r="AC86" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Torrefied Wheat</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
-        </is>
-      </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>6.5</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AI86" t="n">
-        <v>1.038</v>
+        <v>1.035</v>
       </c>
       <c r="AJ86" t="n">
-        <v>82</v>
+        <v>75.37</v>
       </c>
       <c r="AK86" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
@@ -11317,8 +11395,811 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Kalahari blond 16 liter</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2.5380711</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Base (Wheat)</t>
+        </is>
+      </c>
+      <c r="X87" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>Torrefied Wheat</t>
+        </is>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH87" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>82</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="inlineStr"/>
+      <c r="AR87" t="inlineStr"/>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>default-e6ba5b8</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1721546982714</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="P88" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>3.2994924</v>
+      </c>
+      <c r="S88" t="n">
+        <v>53</v>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X88" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>Finest Maris Otter® Ale Malt</t>
+        </is>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH88" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr"/>
+      <c r="AP88" t="inlineStr"/>
+      <c r="AQ88" t="inlineStr"/>
+      <c r="AR88" t="inlineStr"/>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1787844774}</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>RfTzDOwr83mMgEx7DXAJqSmiTnkaet</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1787844774}</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>1787844774014</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="P89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>2.5380711</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Base (Wheat)</t>
+        </is>
+      </c>
+      <c r="X89" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>Torrefied Wheat</t>
+        </is>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH89" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>82</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr"/>
+      <c r="AP89" t="inlineStr"/>
+      <c r="AQ89" t="inlineStr"/>
+      <c r="AR89" t="inlineStr"/>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1J9fe3tUex3oOKOPk0F51aZTCC6NvP</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1785061179}</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1785061179983</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>61</v>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X90" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>GoldSwaen Classic</t>
+        </is>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH90" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>73.9130435</v>
+      </c>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr"/>
+      <c r="AP90" t="inlineStr"/>
+      <c r="AQ90" t="inlineStr"/>
+      <c r="AR90" t="inlineStr"/>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>default-29dda1b5335</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>R3yyMXfk1baparTfJ2ej9HajPEgito</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 919000000, "_seconds": 1781339588}</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>1781339588919</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>329.949239</v>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X91" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>BlackSwaen Coffee</t>
+        </is>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH91" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>60.8695652</v>
+      </c>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr"/>
+      <c r="AP91" t="inlineStr"/>
+      <c r="AQ91" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="AR91" t="inlineStr"/>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>default-c3ff8bb88f9</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ou91CMOYwCNfTOIWjNXLjhWUBAxN7m</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 244000000, "_seconds": 1788086445}</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>1788086445244</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X92" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>Swaen Pilsner</t>
+        </is>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH92" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr"/>
+      <c r="AP92" t="inlineStr"/>
+      <c r="AQ92" t="inlineStr"/>
+      <c r="AR92" t="inlineStr"/>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 212000000, "_seconds": 1775499019}</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>default-c5e48c4</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>9mGQgdZMjKAOZQSjsXo7x5DVWTbPaC</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1777108185}</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>1777108185714</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>529.4416244</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X93" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>Chocolate Malt</t>
+        </is>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>Gives dry, toasty flavours to rich, dark beers</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>72</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr"/>
+      <c r="AP93" t="inlineStr"/>
+      <c r="AQ93" t="inlineStr"/>
+      <c r="AR93" t="inlineStr"/>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT86"/>
+  <autoFilter ref="A1:AT93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11329,7 +12210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP79"/>
+  <dimension ref="A1:AP81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -16640,7 +17521,7 @@
         <v>30</v>
       </c>
       <c r="Q53" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -16741,7 +17622,7 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -16811,11 +17692,11 @@
         <v>10</v>
       </c>
       <c r="H55" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -16885,11 +17766,11 @@
         <v>10</v>
       </c>
       <c r="H56" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -16961,11 +17842,11 @@
         <v>5.5</v>
       </c>
       <c r="H57" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -19047,7 +19928,7 @@
         <v>30</v>
       </c>
       <c r="Q77" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -19317,8 +20198,230 @@
         <v>45</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>default-southernaroma</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>4</v>
+      </c>
+      <c r="H80" t="n">
+        <v>30</v>
+      </c>
+      <c r="J80" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Southern Aroma</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Saaz, Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+        </is>
+      </c>
+      <c r="AJ80" t="n">
+        <v>1719746363473</v>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="AL80" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>default-southernaroma</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" t="n">
+        <v>20</v>
+      </c>
+      <c r="J81" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Southern Aroma</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Saaz, Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="Y81" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+        </is>
+      </c>
+      <c r="AJ81" t="n">
+        <v>1719746363473</v>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="AL81" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP79"/>
+  <autoFilter ref="A1:AP81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19329,7 +20432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL25"/>
+  <dimension ref="A1:AL26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -22155,7 +23258,11 @@
           <t>pkg</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use 7 or 8 grams. </t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -22169,8 +23276,112 @@
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Yeast</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>default-Nus0U2QXJCoeFdPx6G7BNazD19W04F</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>85</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>A British-style ale yeast that is characterized by high attenuation, low ester formation during fermentation, and high ABV tolerance. A good top-fermenting yeast strain that is a great choice for pale ales, ambers, porters, and stouts.
+Oxygenation and/or rehydration for generation 0 may be beneficial, but not necessary.</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>WHC Lab</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>14</v>
+      </c>
+      <c r="R26" t="n">
+        <v>85</v>
+      </c>
+      <c r="S26" t="n">
+        <v>22</v>
+      </c>
+      <c r="T26" t="n">
+        <v>78</v>
+      </c>
+      <c r="U26" t="n">
+        <v>18</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>WHC Old English</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Old English</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>pkg</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL25"/>
+  <autoFilter ref="A1:AL26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22181,7 +23392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB140"/>
+  <dimension ref="A1:AB147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -33901,8 +35112,605 @@
       <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr"/>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>default-2302b0</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>1781339599069</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>2</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="b">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Baking Soda (NaHCO3)</t>
+        </is>
+      </c>
+      <c r="Q141" t="b">
+        <v>0</v>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U141" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr"/>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>default-3b1827</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>hVBLHIBRmfjgeCufI6dYL7ohKfkror</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 760000000, "_seconds": 1788086587}</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1788086587760</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>2</v>
+      </c>
+      <c r="M142" t="b">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Calcium Chloride (CaCl2)</t>
+        </is>
+      </c>
+      <c r="Q142" t="b">
+        <v>0</v>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U142" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>default-1f88df</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>hOo044cGVkLCieJyI8rCtsPKtcdSbS</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 254000000, "_seconds": 1788086560}</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>1788086560254</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>2</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="b">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>931.5</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Gypsum (CaSO4)</t>
+        </is>
+      </c>
+      <c r="Q143" t="b">
+        <v>0</v>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U143" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>T70jwvYnCpjZXjrrMiRr0hkFY6tIYY</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 638000000, "_seconds": 1788087134}</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1788087134638</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L144" t="n">
+        <v>80</v>
+      </c>
+      <c r="M144" t="b">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>336</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q144" t="b">
+        <v>0</v>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U144" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 227000000, "_seconds": 1714216066}</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>default-6bc446</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>DtZ4WaKJ79LUfugEJi3A4PwhoDqCzG</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 940000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>1721546982940</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>2</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="b">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Biofine Clear</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q145" t="b">
+        <v>1</v>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Fining</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 312000000, "_seconds": 1697269078}</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>default-yn1j28sf</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>5dwZuz6McgWsQTyWei8G44K5IFAD5I</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1723974354}</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>1723974354144</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>2</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="b">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>-19</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Yeast Nutrients</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q146" t="b">
+        <v>0</v>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 320000000, "_seconds": 1787845020}</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>FxymQbqWfYaVaT8ypqgApwGcTjOAXm</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>8ohTm584SLfO1z9IbILXf1d0nQqtl4</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1788116824}</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1788116824014</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="b">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>ISY Enhabce</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB140"/>
+  <autoFilter ref="A1:AB147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>